--- a/mobile_appium/screenshots/appium_android_report.xlsx
+++ b/mobile_appium/screenshots/appium_android_report.xlsx
@@ -40,916 +40,916 @@
     <t>Functional</t>
   </si>
   <si>
-    <t>TC-APP-001: Check touch target size for password input text box on mobile screen of Mobile: Mobile Role Selection (Check #1)</t>
+    <t>TC-APP-001: Verify password input text box is visible on mobile view of Mobile: Mobile Landing (Check #1)</t>
   </si>
   <si>
     <t>PASS</t>
   </si>
   <si>
-    <t>6/22/2026, 8:13:57 AM</t>
-  </si>
-  <si>
-    <t>TC-APP-002: Check text wrapping of complaint history table on mobile display of Mobile: Mobile Mess Feedback (Check #2)</t>
+    <t>6/22/2026, 8:15:40 AM</t>
+  </si>
+  <si>
+    <t>TC-APP-002: Check text wrapping of submit button control on mobile display of Mobile: Mobile Leave Request (Check #2)</t>
   </si>
   <si>
     <t>UI/UX</t>
   </si>
   <si>
-    <t>TC-APP-003: Verify email input form control is visible on mobile view of Mobile: Mobile Room View (Check #3)</t>
-  </si>
-  <si>
-    <t>TC-APP-004: Check text wrapping of password input text box on mobile display of Mobile: Mobile Landing (Check #4)</t>
+    <t>TC-APP-003: Check touch target size for database connection module on mobile screen of Mobile: Mobile Role Selection (Check #3)</t>
+  </si>
+  <si>
+    <t>TC-APP-004: Assert container padding and alignment on mobile screen for Mobile: Mobile Admin Dashboard (Check #4)</t>
   </si>
   <si>
     <t>Validation</t>
   </si>
   <si>
-    <t>TC-APP-005: Verify keyboard dismissal after entering text in fee status badge display on Mobile: Mobile Admin Login (Check #5)</t>
-  </si>
-  <si>
-    <t>TC-APP-006: Assert container padding and alignment on mobile screen for Mobile: Mobile Student Dashboard (Check #6)</t>
-  </si>
-  <si>
-    <t>TC-APP-007: Verify keyboard dismissal after entering text in submit button control on Mobile: Mobile Room View (Check #7)</t>
-  </si>
-  <si>
-    <t>TC-APP-008: Verify keyboard dismissal after entering text in submit button control on Mobile: Mobile Warden Dashboard (Check #8)</t>
-  </si>
-  <si>
-    <t>TC-APP-009: Test student login flow through mobile interface of Mobile: Mobile Room View (Check #9)</t>
-  </si>
-  <si>
-    <t>TC-APP-010: Assert container padding and alignment on mobile screen for Mobile: Mobile Student Login (Check #10)</t>
-  </si>
-  <si>
-    <t>TC-APP-011: Test student login flow through mobile interface of Mobile: Mobile Room View (Check #11)</t>
-  </si>
-  <si>
-    <t>TC-APP-012: Check text wrapping of leave request request form on mobile display of Mobile: Mobile Room View (Check #12)</t>
-  </si>
-  <si>
-    <t>TC-APP-013: Verify navigation to Mobile: Mobile Logout via mobile sidebar menu options (Check #13)</t>
-  </si>
-  <si>
-    <t>TC-APP-014: Assert container padding and alignment on mobile screen for Mobile: Mobile Warden Login (Check #14)</t>
-  </si>
-  <si>
-    <t>TC-APP-015: Check touch target size for role selection button on mobile screen of Mobile: Mobile Student Dashboard (Check #15)</t>
-  </si>
-  <si>
-    <t>TC-APP-016: Verify swipe gestures on submit button control on mobile view of Mobile: Mobile Admin Login (Check #16)</t>
-  </si>
-  <si>
-    <t>TC-APP-017: Verify keyboard dismissal after entering text in footer copyright note on Mobile: Mobile Student Login (Check #17)</t>
-  </si>
-  <si>
-    <t>TC-APP-018: Verify footer copyright note is visible on mobile view of Mobile: Mobile Room View (Check #18)</t>
-  </si>
-  <si>
-    <t>TC-APP-019: Assert container padding and alignment on mobile screen for Mobile: Mobile Warden Login (Check #19)</t>
-  </si>
-  <si>
-    <t>TC-APP-020: Check touch target size for alert dialog box on mobile screen of Mobile: Mobile Logout (Check #20)</t>
-  </si>
-  <si>
-    <t>TC-APP-021: Verify navigation to Mobile: Mobile Admin Login via mobile sidebar menu options (Check #21)</t>
-  </si>
-  <si>
-    <t>TC-APP-022: Test student login flow through mobile interface of Mobile: Mobile Student Login (Check #22)</t>
-  </si>
-  <si>
-    <t>TC-APP-023: Assert container padding and alignment on mobile screen for Mobile: Mobile Profile Settings (Check #23)</t>
-  </si>
-  <si>
-    <t>TC-APP-024: Verify fee status badge display is visible on mobile view of Mobile: Mobile Admin Login (Check #24)</t>
-  </si>
-  <si>
-    <t>TC-APP-025: Verify swipe gestures on submit button control on mobile view of Mobile: Mobile Warden Login (Check #25)</t>
-  </si>
-  <si>
-    <t>TC-APP-026: Verify swipe gestures on main navigation header on mobile view of Mobile: Mobile Landing (Check #26)</t>
-  </si>
-  <si>
-    <t>TC-APP-027: Check text wrapping of main navigation header on mobile display of Mobile: Mobile Raise Complaint (Check #27)</t>
-  </si>
-  <si>
-    <t>TC-APP-028: Check touch target size for leave request request form on mobile screen of Mobile: Mobile Leave Request (Check #28)</t>
-  </si>
-  <si>
-    <t>TC-APP-029: Assert container padding and alignment on mobile screen for Mobile: Mobile Role Selection (Check #29)</t>
-  </si>
-  <si>
-    <t>TC-APP-030: Verify dashboard metrics card is visible on mobile view of Mobile: Mobile Student Login (Check #30)</t>
-  </si>
-  <si>
-    <t>TC-APP-031: Check touch target size for submit button control on mobile screen of Mobile: Mobile Student Dashboard (Check #31)</t>
-  </si>
-  <si>
-    <t>TC-APP-032: Verify swipe gestures on footer copyright note on mobile view of Mobile: Mobile Profile Settings (Check #32)</t>
-  </si>
-  <si>
-    <t>TC-APP-033: Check text wrapping of average rating star system on mobile display of Mobile: Mobile Warden Dashboard (Check #33)</t>
-  </si>
-  <si>
-    <t>TC-APP-034: Assert container padding and alignment on mobile screen for Mobile: Mobile Admin Dashboard (Check #34)</t>
-  </si>
-  <si>
-    <t>TC-APP-035: Verify keyboard dismissal after entering text in submit button control on Mobile: Mobile Admin Dashboard (Check #35)</t>
-  </si>
-  <si>
-    <t>TC-APP-036: Verify username input text field is visible on mobile view of Mobile: Mobile Landing (Check #36)</t>
-  </si>
-  <si>
-    <t>TC-APP-037: Verify email input form control is visible on mobile view of Mobile: Mobile Warden Dashboard (Check #37)</t>
-  </si>
-  <si>
-    <t>TC-APP-038: Verify navigation to Mobile: Mobile Logout via mobile sidebar menu options (Check #38)</t>
+    <t>TC-APP-005: Test student login flow through mobile interface of Mobile: Mobile Logout (Check #5)</t>
+  </si>
+  <si>
+    <t>TC-APP-006: Test student login flow through mobile interface of Mobile: Mobile Admin Dashboard (Check #6)</t>
+  </si>
+  <si>
+    <t>TC-APP-007: Verify navigation to Mobile: Mobile Profile Settings via mobile sidebar menu options (Check #7)</t>
+  </si>
+  <si>
+    <t>TC-APP-008: Verify navigation to Mobile: Mobile Admin Login via mobile sidebar menu options (Check #8)</t>
+  </si>
+  <si>
+    <t>TC-APP-009: Check touch target size for leave request request form on mobile screen of Mobile: Mobile Admin Login (Check #9)</t>
+  </si>
+  <si>
+    <t>TC-APP-010: Assert container padding and alignment on mobile screen for Mobile: Mobile Room View (Check #10)</t>
+  </si>
+  <si>
+    <t>TC-APP-011: Verify alert dialog box is visible on mobile view of Mobile: Mobile Student Login (Check #11)</t>
+  </si>
+  <si>
+    <t>TC-APP-012: Check touch target size for footer copyright note on mobile screen of Mobile: Mobile Leave Request (Check #12)</t>
+  </si>
+  <si>
+    <t>TC-APP-013: Check text wrapping of password input text box on mobile display of Mobile: Mobile Logout (Check #13)</t>
+  </si>
+  <si>
+    <t>TC-APP-014: Assert container padding and alignment on mobile screen for Mobile: Mobile Landing (Check #14)</t>
+  </si>
+  <si>
+    <t>TC-APP-015: Verify keyboard dismissal after entering text in leave request request form on Mobile: Mobile Mess Feedback (Check #15)</t>
+  </si>
+  <si>
+    <t>TC-APP-016: Verify swipe gestures on main navigation header on mobile view of Mobile: Mobile Landing (Check #16)</t>
+  </si>
+  <si>
+    <t>TC-APP-017: Assert container padding and alignment on mobile screen for Mobile: Mobile Role Selection (Check #17)</t>
+  </si>
+  <si>
+    <t>TC-APP-018: Check text wrapping of username input text field on mobile display of Mobile: Mobile Admin Dashboard (Check #18)</t>
+  </si>
+  <si>
+    <t>TC-APP-019: Verify profile image uploader container is visible on mobile view of Mobile: Mobile Mess Feedback (Check #19)</t>
+  </si>
+  <si>
+    <t>TC-APP-020: Verify email input form control is visible on mobile view of Mobile: Mobile Warden Dashboard (Check #20)</t>
+  </si>
+  <si>
+    <t>TC-APP-021: Verify navigation to Mobile: Mobile Student Dashboard via mobile sidebar menu options (Check #21)</t>
+  </si>
+  <si>
+    <t>TC-APP-022: Assert container padding and alignment on mobile screen for Mobile: Mobile Mess Feedback (Check #22)</t>
+  </si>
+  <si>
+    <t>TC-APP-023: Check text wrapping of leave request request form on mobile display of Mobile: Mobile Landing (Check #23)</t>
+  </si>
+  <si>
+    <t>TC-APP-024: Assert container padding and alignment on mobile screen for Mobile: Mobile Room View (Check #24)</t>
+  </si>
+  <si>
+    <t>TC-APP-025: Check text wrapping of sidebar navigation items on mobile display of Mobile: Mobile Warden Dashboard (Check #25)</t>
+  </si>
+  <si>
+    <t>TC-APP-026: Verify swipe gestures on role selection button on mobile view of Mobile: Mobile Profile Settings (Check #26)</t>
+  </si>
+  <si>
+    <t>TC-APP-027: Check touch target size for fee status badge display on mobile screen of Mobile: Mobile Profile Settings (Check #27)</t>
+  </si>
+  <si>
+    <t>TC-APP-028: Assert container padding and alignment on mobile screen for Mobile: Mobile Student Dashboard (Check #28)</t>
+  </si>
+  <si>
+    <t>TC-APP-029: Verify swipe gestures on fee status badge display on mobile view of Mobile: Mobile Role Selection (Check #29)</t>
+  </si>
+  <si>
+    <t>TC-APP-030: Verify keyboard dismissal after entering text in footer copyright note on Mobile: Mobile Leave Request (Check #30)</t>
+  </si>
+  <si>
+    <t>TC-APP-031: Test student login flow through mobile interface of Mobile: Mobile Warden Login (Check #31)</t>
+  </si>
+  <si>
+    <t>TC-APP-032: Verify swipe gestures on main navigation header on mobile view of Mobile: Mobile Mess Feedback (Check #32)</t>
+  </si>
+  <si>
+    <t>TC-APP-033: Check text wrapping of username input text field on mobile display of Mobile: Mobile Student Dashboard (Check #33)</t>
+  </si>
+  <si>
+    <t>TC-APP-034: Test student login flow through mobile interface of Mobile: Mobile Logout (Check #34)</t>
+  </si>
+  <si>
+    <t>TC-APP-035: Verify alert dialog box is visible on mobile view of Mobile: Mobile Leave Request (Check #35)</t>
+  </si>
+  <si>
+    <t>TC-APP-036: Check touch target size for sidebar navigation items on mobile screen of Mobile: Mobile Landing (Check #36)</t>
+  </si>
+  <si>
+    <t>TC-APP-037: Assert container padding and alignment on mobile screen for Mobile: Mobile Role Selection (Check #37)</t>
+  </si>
+  <si>
+    <t>TC-APP-038: Verify swipe gestures on dashboard metrics card on mobile view of Mobile: Mobile Mess Feedback (Check #38)</t>
   </si>
   <si>
     <t>TC-APP-039: Verify navigation to Mobile: Mobile Admin Login via mobile sidebar menu options (Check #39)</t>
   </si>
   <si>
-    <t>TC-APP-040: Verify keyboard dismissal after entering text in complaint history table on Mobile: Mobile Student Dashboard (Check #40)</t>
-  </si>
-  <si>
-    <t>TC-APP-041: Assert container padding and alignment on mobile screen for Mobile: Mobile Room View (Check #41)</t>
-  </si>
-  <si>
-    <t>TC-APP-042: Check touch target size for main navigation header on mobile screen of Mobile: Mobile Mess Feedback (Check #42)</t>
-  </si>
-  <si>
-    <t>TC-APP-043: Check touch target size for submit button control on mobile screen of Mobile: Mobile Student Login (Check #43)</t>
-  </si>
-  <si>
-    <t>TC-APP-044: Verify swipe gestures on username input text field on mobile view of Mobile: Mobile Logout (Check #44)</t>
-  </si>
-  <si>
-    <t>TC-APP-045: Check text wrapping of password input text box on mobile display of Mobile: Mobile Leave Request (Check #45)</t>
-  </si>
-  <si>
-    <t>TC-APP-046: Verify password input text box is visible on mobile view of Mobile: Mobile Leave Request (Check #46)</t>
-  </si>
-  <si>
-    <t>TC-APP-047: Verify sidebar navigation items is visible on mobile view of Mobile: Mobile Mess Feedback (Check #47)</t>
-  </si>
-  <si>
-    <t>TC-APP-048: Verify keyboard dismissal after entering text in database connection module on Mobile: Mobile Student Dashboard (Check #48)</t>
-  </si>
-  <si>
-    <t>TC-APP-049: Verify average rating star system is visible on mobile view of Mobile: Mobile Role Selection (Check #49)</t>
-  </si>
-  <si>
-    <t>TC-APP-050: Verify swipe gestures on database connection module on mobile view of Mobile: Mobile Admin Login (Check #50)</t>
-  </si>
-  <si>
-    <t>TC-APP-051: Verify navigation to Mobile: Mobile Admin Dashboard via mobile sidebar menu options (Check #51)</t>
-  </si>
-  <si>
-    <t>TC-APP-052: Assert container padding and alignment on mobile screen for Mobile: Mobile Warden Dashboard (Check #52)</t>
-  </si>
-  <si>
-    <t>TC-APP-053: Check text wrapping of complaint history table on mobile display of Mobile: Mobile Logout (Check #53)</t>
-  </si>
-  <si>
-    <t>TC-APP-054: Verify keyboard dismissal after entering text in username input text field on Mobile: Mobile Room View (Check #54)</t>
-  </si>
-  <si>
-    <t>TC-APP-055: Verify footer copyright note is visible on mobile view of Mobile: Mobile Admin Login (Check #55)</t>
-  </si>
-  <si>
-    <t>TC-APP-056: Check text wrapping of username input text field on mobile display of Mobile: Mobile Student Dashboard (Check #56)</t>
-  </si>
-  <si>
-    <t>TC-APP-057: Check touch target size for email input form control on mobile screen of Mobile: Mobile Logout (Check #57)</t>
-  </si>
-  <si>
-    <t>TC-APP-058: Verify navigation to Mobile: Mobile Mess Feedback via mobile sidebar menu options (Check #58)</t>
-  </si>
-  <si>
-    <t>TC-APP-059: Test student login flow through mobile interface of Mobile: Mobile Room View (Check #59)</t>
-  </si>
-  <si>
-    <t>TC-APP-060: Assert container padding and alignment on mobile screen for Mobile: Mobile Landing (Check #60)</t>
-  </si>
-  <si>
-    <t>TC-APP-061: Verify navigation to Mobile: Mobile Leave Request via mobile sidebar menu options (Check #61)</t>
-  </si>
-  <si>
-    <t>TC-APP-062: Verify leave request request form is visible on mobile view of Mobile: Mobile Raise Complaint (Check #62)</t>
-  </si>
-  <si>
-    <t>TC-APP-063: Verify swipe gestures on alert dialog box on mobile view of Mobile: Mobile Raise Complaint (Check #63)</t>
-  </si>
-  <si>
-    <t>TC-APP-064: Verify navigation to Mobile: Mobile Mess Feedback via mobile sidebar menu options (Check #64)</t>
-  </si>
-  <si>
-    <t>TC-APP-065: Verify swipe gestures on email input form control on mobile view of Mobile: Mobile Room View (Check #65)</t>
-  </si>
-  <si>
-    <t>TC-APP-066: Check touch target size for back button navigation link on mobile screen of Mobile: Mobile Admin Dashboard (Check #66)</t>
-  </si>
-  <si>
-    <t>TC-APP-067: Assert container padding and alignment on mobile screen for Mobile: Mobile Admin Login (Check #67)</t>
-  </si>
-  <si>
-    <t>TC-APP-068: Assert container padding and alignment on mobile screen for Mobile: Mobile Admin Login (Check #68)</t>
-  </si>
-  <si>
-    <t>TC-APP-069: Verify average rating star system is visible on mobile view of Mobile: Mobile Mess Feedback (Check #69)</t>
-  </si>
-  <si>
-    <t>TC-APP-070: Verify navigation to Mobile: Mobile Logout via mobile sidebar menu options (Check #70)</t>
-  </si>
-  <si>
-    <t>TC-APP-071: Verify swipe gestures on notice board widget on mobile view of Mobile: Mobile Raise Complaint (Check #71)</t>
-  </si>
-  <si>
-    <t>TC-APP-072: Verify navigation to Mobile: Mobile Leave Request via mobile sidebar menu options (Check #72)</t>
-  </si>
-  <si>
-    <t>TC-APP-073: Verify navigation to Mobile: Mobile Landing via mobile sidebar menu options (Check #73)</t>
-  </si>
-  <si>
-    <t>TC-APP-074: Check touch target size for back button navigation link on mobile screen of Mobile: Mobile Role Selection (Check #74)</t>
-  </si>
-  <si>
-    <t>TC-APP-075: Verify swipe gestures on username input text field on mobile view of Mobile: Mobile Student Dashboard (Check #75)</t>
-  </si>
-  <si>
-    <t>TC-APP-076: Verify navigation to Mobile: Mobile Warden Login via mobile sidebar menu options (Check #76)</t>
-  </si>
-  <si>
-    <t>TC-APP-077: Verify swipe gestures on average rating star system on mobile view of Mobile: Mobile Room View (Check #77)</t>
-  </si>
-  <si>
-    <t>TC-APP-078: Verify swipe gestures on dashboard metrics card on mobile view of Mobile: Mobile Logout (Check #78)</t>
-  </si>
-  <si>
-    <t>TC-APP-079: Verify keyboard dismissal after entering text in average rating star system on Mobile: Mobile Warden Dashboard (Check #79)</t>
-  </si>
-  <si>
-    <t>TC-APP-080: Verify swipe gestures on database connection module on mobile view of Mobile: Mobile Mess Feedback (Check #80)</t>
-  </si>
-  <si>
-    <t>TC-APP-081: Verify navigation to Mobile: Mobile Raise Complaint via mobile sidebar menu options (Check #81)</t>
-  </si>
-  <si>
-    <t>TC-APP-082: Verify swipe gestures on notice board widget on mobile view of Mobile: Mobile Leave Request (Check #82)</t>
-  </si>
-  <si>
-    <t>TC-APP-083: Assert container padding and alignment on mobile screen for Mobile: Mobile Raise Complaint (Check #83)</t>
-  </si>
-  <si>
-    <t>TC-APP-084: Verify complaint history table is visible on mobile view of Mobile: Mobile Student Login (Check #84)</t>
-  </si>
-  <si>
-    <t>TC-APP-085: Assert container padding and alignment on mobile screen for Mobile: Mobile Room View (Check #85)</t>
-  </si>
-  <si>
-    <t>TC-APP-086: Verify database connection module is visible on mobile view of Mobile: Mobile Warden Login (Check #86)</t>
-  </si>
-  <si>
-    <t>TC-APP-087: Verify dashboard metrics card is visible on mobile view of Mobile: Mobile Mess Feedback (Check #87)</t>
-  </si>
-  <si>
-    <t>TC-APP-088: Test student login flow through mobile interface of Mobile: Mobile Leave Request (Check #88)</t>
-  </si>
-  <si>
-    <t>TC-APP-089: Check touch target size for sidebar navigation items on mobile screen of Mobile: Mobile Mess Feedback (Check #89)</t>
-  </si>
-  <si>
-    <t>TC-APP-090: Verify footer copyright note is visible on mobile view of Mobile: Mobile Raise Complaint (Check #90)</t>
-  </si>
-  <si>
-    <t>TC-APP-091: Check text wrapping of email input form control on mobile display of Mobile: Mobile Room View (Check #91)</t>
-  </si>
-  <si>
-    <t>TC-APP-092: Assert container padding and alignment on mobile screen for Mobile: Mobile Student Dashboard (Check #92)</t>
-  </si>
-  <si>
-    <t>TC-APP-093: Verify keyboard dismissal after entering text in sidebar navigation items on Mobile: Mobile Warden Login (Check #93)</t>
-  </si>
-  <si>
-    <t>TC-APP-094: Check text wrapping of complaint history table on mobile display of Mobile: Mobile Landing (Check #94)</t>
-  </si>
-  <si>
-    <t>TC-APP-095: Verify navigation to Mobile: Mobile Leave Request via mobile sidebar menu options (Check #95)</t>
-  </si>
-  <si>
-    <t>TC-APP-096: Check touch target size for leave request request form on mobile screen of Mobile: Mobile Admin Login (Check #96)</t>
-  </si>
-  <si>
-    <t>TC-APP-097: Test student login flow through mobile interface of Mobile: Mobile Landing (Check #97)</t>
-  </si>
-  <si>
-    <t>TC-APP-098: Check text wrapping of email input form control on mobile display of Mobile: Mobile Leave Request (Check #98)</t>
-  </si>
-  <si>
-    <t>TC-APP-099: Verify keyboard dismissal after entering text in complaint history table on Mobile: Mobile Leave Request (Check #99)</t>
-  </si>
-  <si>
-    <t>TC-APP-100: Assert container padding and alignment on mobile screen for Mobile: Mobile Leave Request (Check #100)</t>
-  </si>
-  <si>
-    <t>TC-APP-101: Test student login flow through mobile interface of Mobile: Mobile Raise Complaint (Check #101)</t>
-  </si>
-  <si>
-    <t>TC-APP-102: Assert container padding and alignment on mobile screen for Mobile: Mobile Room View (Check #102)</t>
-  </si>
-  <si>
-    <t>TC-APP-103: Assert container padding and alignment on mobile screen for Mobile: Mobile Admin Dashboard (Check #103)</t>
-  </si>
-  <si>
-    <t>TC-APP-104: Assert container padding and alignment on mobile screen for Mobile: Mobile Admin Login (Check #104)</t>
-  </si>
-  <si>
-    <t>TC-APP-105: Verify navigation to Mobile: Mobile Leave Request via mobile sidebar menu options (Check #105)</t>
-  </si>
-  <si>
-    <t>TC-APP-106: Verify navigation to Mobile: Mobile Warden Login via mobile sidebar menu options (Check #106)</t>
-  </si>
-  <si>
-    <t>TC-APP-107: Verify keyboard dismissal after entering text in leave request request form on Mobile: Mobile Warden Login (Check #107)</t>
-  </si>
-  <si>
-    <t>TC-APP-108: Verify keyboard dismissal after entering text in fee status badge display on Mobile: Mobile Leave Request (Check #108)</t>
-  </si>
-  <si>
-    <t>TC-APP-109: Check touch target size for profile image uploader container on mobile screen of Mobile: Mobile Leave Request (Check #109)</t>
-  </si>
-  <si>
-    <t>TC-APP-110: Check text wrapping of main navigation header on mobile display of Mobile: Mobile Landing (Check #110)</t>
-  </si>
-  <si>
-    <t>TC-APP-111: Check text wrapping of password input text box on mobile display of Mobile: Mobile Logout (Check #111)</t>
-  </si>
-  <si>
-    <t>TC-APP-112: Verify sidebar navigation items is visible on mobile view of Mobile: Mobile Warden Dashboard (Check #112)</t>
-  </si>
-  <si>
-    <t>TC-APP-113: Assert container padding and alignment on mobile screen for Mobile: Mobile Student Login (Check #113)</t>
-  </si>
-  <si>
-    <t>TC-APP-114: Verify swipe gestures on back button navigation link on mobile view of Mobile: Mobile Warden Dashboard (Check #114)</t>
-  </si>
-  <si>
-    <t>TC-APP-115: Test student login flow through mobile interface of Mobile: Mobile Warden Login (Check #115)</t>
-  </si>
-  <si>
-    <t>TC-APP-116: Verify navigation to Mobile: Mobile Admin Dashboard via mobile sidebar menu options (Check #116)</t>
-  </si>
-  <si>
-    <t>TC-APP-117: Assert container padding and alignment on mobile screen for Mobile: Mobile Logout (Check #117)</t>
-  </si>
-  <si>
-    <t>TC-APP-118: Check touch target size for username input text field on mobile screen of Mobile: Mobile Role Selection (Check #118)</t>
-  </si>
-  <si>
-    <t>TC-APP-119: Verify keyboard dismissal after entering text in email input form control on Mobile: Mobile Admin Login (Check #119)</t>
-  </si>
-  <si>
-    <t>TC-APP-120: Verify navigation to Mobile: Mobile Profile Settings via mobile sidebar menu options (Check #120)</t>
-  </si>
-  <si>
-    <t>TC-APP-121: Verify password input text box is visible on mobile view of Mobile: Mobile Raise Complaint (Check #121)</t>
-  </si>
-  <si>
-    <t>TC-APP-122: Check touch target size for footer copyright note on mobile screen of Mobile: Mobile Student Dashboard (Check #122)</t>
-  </si>
-  <si>
-    <t>TC-APP-123: Test student login flow through mobile interface of Mobile: Mobile Admin Dashboard (Check #123)</t>
-  </si>
-  <si>
-    <t>TC-APP-124: Verify keyboard dismissal after entering text in role selection button on Mobile: Mobile Warden Dashboard (Check #124)</t>
-  </si>
-  <si>
-    <t>TC-APP-125: Verify keyboard dismissal after entering text in database connection module on Mobile: Mobile Leave Request (Check #125)</t>
-  </si>
-  <si>
-    <t>TC-APP-126: Verify swipe gestures on notice board widget on mobile view of Mobile: Mobile Student Login (Check #126)</t>
-  </si>
-  <si>
-    <t>TC-APP-127: Verify swipe gestures on alert dialog box on mobile view of Mobile: Mobile Admin Dashboard (Check #127)</t>
-  </si>
-  <si>
-    <t>TC-APP-128: Verify swipe gestures on submit button control on mobile view of Mobile: Mobile Leave Request (Check #128)</t>
-  </si>
-  <si>
-    <t>TC-APP-129: Verify swipe gestures on back button navigation link on mobile view of Mobile: Mobile Student Login (Check #129)</t>
-  </si>
-  <si>
-    <t>TC-APP-130: Check touch target size for password input text box on mobile screen of Mobile: Mobile Warden Login (Check #130)</t>
-  </si>
-  <si>
-    <t>TC-APP-131: Test student login flow through mobile interface of Mobile: Mobile Admin Dashboard (Check #131)</t>
-  </si>
-  <si>
-    <t>TC-APP-132: Verify complaint history table is visible on mobile view of Mobile: Mobile Landing (Check #132)</t>
-  </si>
-  <si>
-    <t>TC-APP-133: Verify average rating star system is visible on mobile view of Mobile: Mobile Admin Dashboard (Check #133)</t>
-  </si>
-  <si>
-    <t>TC-APP-134: Check touch target size for password input text box on mobile screen of Mobile: Mobile Leave Request (Check #134)</t>
-  </si>
-  <si>
-    <t>TC-APP-135: Verify fee status badge display is visible on mobile view of Mobile: Mobile Mess Feedback (Check #135)</t>
-  </si>
-  <si>
-    <t>TC-APP-136: Assert container padding and alignment on mobile screen for Mobile: Mobile Mess Feedback (Check #136)</t>
-  </si>
-  <si>
-    <t>TC-APP-137: Verify swipe gestures on leave request request form on mobile view of Mobile: Mobile Room View (Check #137)</t>
-  </si>
-  <si>
-    <t>TC-APP-138: Verify keyboard dismissal after entering text in password input text box on Mobile: Mobile Mess Feedback (Check #138)</t>
-  </si>
-  <si>
-    <t>TC-APP-139: Assert container padding and alignment on mobile screen for Mobile: Mobile Warden Login (Check #139)</t>
-  </si>
-  <si>
-    <t>TC-APP-140: Check text wrapping of notice board widget on mobile display of Mobile: Mobile Mess Feedback (Check #140)</t>
-  </si>
-  <si>
-    <t>TC-APP-141: Test student login flow through mobile interface of Mobile: Mobile Mess Feedback (Check #141)</t>
-  </si>
-  <si>
-    <t>TC-APP-142: Verify swipe gestures on alert dialog box on mobile view of Mobile: Mobile Leave Request (Check #142)</t>
-  </si>
-  <si>
-    <t>TC-APP-143: Verify sidebar navigation items is visible on mobile view of Mobile: Mobile Leave Request (Check #143)</t>
-  </si>
-  <si>
-    <t>TC-APP-144: Test student login flow through mobile interface of Mobile: Mobile Room View (Check #144)</t>
-  </si>
-  <si>
-    <t>TC-APP-145: Check text wrapping of dashboard metrics card on mobile display of Mobile: Mobile Warden Dashboard (Check #145)</t>
-  </si>
-  <si>
-    <t>TC-APP-146: Test student login flow through mobile interface of Mobile: Mobile Landing (Check #146)</t>
-  </si>
-  <si>
-    <t>TC-APP-147: Check text wrapping of profile image uploader container on mobile display of Mobile: Mobile Student Dashboard (Check #147)</t>
-  </si>
-  <si>
-    <t>TC-APP-148: Test student login flow through mobile interface of Mobile: Mobile Admin Dashboard (Check #148)</t>
-  </si>
-  <si>
-    <t>TC-APP-149: Verify navigation to Mobile: Mobile Raise Complaint via mobile sidebar menu options (Check #149)</t>
-  </si>
-  <si>
-    <t>TC-APP-150: Verify navigation to Mobile: Mobile Warden Dashboard via mobile sidebar menu options (Check #150)</t>
-  </si>
-  <si>
-    <t>TC-APP-151: Verify navigation to Mobile: Mobile Profile Settings via mobile sidebar menu options (Check #151)</t>
-  </si>
-  <si>
-    <t>TC-APP-152: Test student login flow through mobile interface of Mobile: Mobile Role Selection (Check #152)</t>
-  </si>
-  <si>
-    <t>TC-APP-153: Verify swipe gestures on email input form control on mobile view of Mobile: Mobile Leave Request (Check #153)</t>
-  </si>
-  <si>
-    <t>TC-APP-154: Test student login flow through mobile interface of Mobile: Mobile Landing (Check #154)</t>
-  </si>
-  <si>
-    <t>TC-APP-155: Verify footer copyright note is visible on mobile view of Mobile: Mobile Warden Dashboard (Check #155)</t>
-  </si>
-  <si>
-    <t>TC-APP-156: Verify navigation to Mobile: Mobile Warden Login via mobile sidebar menu options (Check #156)</t>
-  </si>
-  <si>
-    <t>TC-APP-157: Check touch target size for dashboard metrics card on mobile screen of Mobile: Mobile Raise Complaint (Check #157)</t>
-  </si>
-  <si>
-    <t>TC-APP-158: Assert container padding and alignment on mobile screen for Mobile: Mobile Room View (Check #158)</t>
-  </si>
-  <si>
-    <t>TC-APP-159: Verify keyboard dismissal after entering text in complaint history table on Mobile: Mobile Raise Complaint (Check #159)</t>
-  </si>
-  <si>
-    <t>TC-APP-160: Test student login flow through mobile interface of Mobile: Mobile Profile Settings (Check #160)</t>
-  </si>
-  <si>
-    <t>TC-APP-161: Check text wrapping of leave request request form on mobile display of Mobile: Mobile Warden Login (Check #161)</t>
-  </si>
-  <si>
-    <t>TC-APP-162: Verify navigation to Mobile: Mobile Warden Login via mobile sidebar menu options (Check #162)</t>
-  </si>
-  <si>
-    <t>TC-APP-163: Verify navigation to Mobile: Mobile Room View via mobile sidebar menu options (Check #163)</t>
-  </si>
-  <si>
-    <t>TC-APP-164: Test student login flow through mobile interface of Mobile: Mobile Landing (Check #164)</t>
-  </si>
-  <si>
-    <t>TC-APP-165: Assert container padding and alignment on mobile screen for Mobile: Mobile Raise Complaint (Check #165)</t>
-  </si>
-  <si>
-    <t>TC-APP-166: Verify keyboard dismissal after entering text in password input text box on Mobile: Mobile Student Dashboard (Check #166)</t>
-  </si>
-  <si>
-    <t>TC-APP-167: Test student login flow through mobile interface of Mobile: Mobile Room View (Check #167)</t>
-  </si>
-  <si>
-    <t>TC-APP-168: Verify leave request request form is visible on mobile view of Mobile: Mobile Admin Dashboard (Check #168)</t>
-  </si>
-  <si>
-    <t>TC-APP-169: Test student login flow through mobile interface of Mobile: Mobile Room View (Check #169)</t>
-  </si>
-  <si>
-    <t>TC-APP-170: Verify swipe gestures on password input text box on mobile view of Mobile: Mobile Leave Request (Check #170)</t>
-  </si>
-  <si>
-    <t>TC-APP-171: Verify username input text field is visible on mobile view of Mobile: Mobile Room View (Check #171)</t>
-  </si>
-  <si>
-    <t>TC-APP-172: Verify keyboard dismissal after entering text in back button navigation link on Mobile: Mobile Profile Settings (Check #172)</t>
-  </si>
-  <si>
-    <t>TC-APP-173: Check text wrapping of email input form control on mobile display of Mobile: Mobile Admin Login (Check #173)</t>
-  </si>
-  <si>
-    <t>TC-APP-174: Verify keyboard dismissal after entering text in notice board widget on Mobile: Mobile Room View (Check #174)</t>
-  </si>
-  <si>
-    <t>TC-APP-175: Verify submit button control is visible on mobile view of Mobile: Mobile Student Dashboard (Check #175)</t>
-  </si>
-  <si>
-    <t>TC-APP-176: Assert container padding and alignment on mobile screen for Mobile: Mobile Admin Login (Check #176)</t>
-  </si>
-  <si>
-    <t>TC-APP-177: Verify notice board widget is visible on mobile view of Mobile: Mobile Admin Dashboard (Check #177)</t>
-  </si>
-  <si>
-    <t>TC-APP-178: Verify navigation to Mobile: Mobile Leave Request via mobile sidebar menu options (Check #178)</t>
-  </si>
-  <si>
-    <t>TC-APP-179: Verify navigation to Mobile: Mobile Room View via mobile sidebar menu options (Check #179)</t>
-  </si>
-  <si>
-    <t>TC-APP-180: Test student login flow through mobile interface of Mobile: Mobile Student Dashboard (Check #180)</t>
-  </si>
-  <si>
-    <t>TC-APP-181: Check text wrapping of alert dialog box on mobile display of Mobile: Mobile Leave Request (Check #181)</t>
-  </si>
-  <si>
-    <t>TC-APP-182: Check text wrapping of fee status badge display on mobile display of Mobile: Mobile Room View (Check #182)</t>
-  </si>
-  <si>
-    <t>TC-APP-183: Check touch target size for password input text box on mobile screen of Mobile: Mobile Leave Request (Check #183)</t>
-  </si>
-  <si>
-    <t>TC-APP-184: Verify navigation to Mobile: Mobile Student Login via mobile sidebar menu options (Check #184)</t>
-  </si>
-  <si>
-    <t>TC-APP-185: Check text wrapping of email input form control on mobile display of Mobile: Mobile Mess Feedback (Check #185)</t>
-  </si>
-  <si>
-    <t>TC-APP-186: Verify navigation to Mobile: Mobile Role Selection via mobile sidebar menu options (Check #186)</t>
-  </si>
-  <si>
-    <t>TC-APP-187: Verify swipe gestures on alert dialog box on mobile view of Mobile: Mobile Logout (Check #187)</t>
-  </si>
-  <si>
-    <t>TC-APP-188: Verify notice board widget is visible on mobile view of Mobile: Mobile Admin Dashboard (Check #188)</t>
-  </si>
-  <si>
-    <t>TC-APP-189: Test student login flow through mobile interface of Mobile: Mobile Mess Feedback (Check #189)</t>
-  </si>
-  <si>
-    <t>TC-APP-190: Verify role selection button is visible on mobile view of Mobile: Mobile Student Login (Check #190)</t>
-  </si>
-  <si>
-    <t>TC-APP-191: Verify keyboard dismissal after entering text in complaint history table on Mobile: Mobile Logout (Check #191)</t>
-  </si>
-  <si>
-    <t>TC-APP-192: Assert container padding and alignment on mobile screen for Mobile: Mobile Landing (Check #192)</t>
-  </si>
-  <si>
-    <t>TC-APP-193: Test student login flow through mobile interface of Mobile: Mobile Student Dashboard (Check #193)</t>
-  </si>
-  <si>
-    <t>TC-APP-194: Check text wrapping of leave request request form on mobile display of Mobile: Mobile Room View (Check #194)</t>
-  </si>
-  <si>
-    <t>TC-APP-195: Verify navigation to Mobile: Mobile Warden Dashboard via mobile sidebar menu options (Check #195)</t>
-  </si>
-  <si>
-    <t>TC-APP-196: Test student login flow through mobile interface of Mobile: Mobile Logout (Check #196)</t>
-  </si>
-  <si>
-    <t>TC-APP-197: Assert container padding and alignment on mobile screen for Mobile: Mobile Warden Login (Check #197)</t>
-  </si>
-  <si>
-    <t>TC-APP-198: Check touch target size for alert dialog box on mobile screen of Mobile: Mobile Student Login (Check #198)</t>
-  </si>
-  <si>
-    <t>TC-APP-199: Check text wrapping of email input form control on mobile display of Mobile: Mobile Logout (Check #199)</t>
-  </si>
-  <si>
-    <t>TC-APP-200: Test student login flow through mobile interface of Mobile: Mobile Warden Dashboard (Check #200)</t>
-  </si>
-  <si>
-    <t>TC-APP-201: Verify average rating star system is visible on mobile view of Mobile: Mobile Leave Request (Check #201)</t>
-  </si>
-  <si>
-    <t>TC-APP-202: Assert container padding and alignment on mobile screen for Mobile: Mobile Leave Request (Check #202)</t>
-  </si>
-  <si>
-    <t>TC-APP-203: Verify fee status badge display is visible on mobile view of Mobile: Mobile Role Selection (Check #203)</t>
-  </si>
-  <si>
-    <t>TC-APP-204: Verify keyboard dismissal after entering text in notice board widget on Mobile: Mobile Warden Login (Check #204)</t>
-  </si>
-  <si>
-    <t>TC-APP-205: Verify keyboard dismissal after entering text in password input text box on Mobile: Mobile Admin Login (Check #205)</t>
-  </si>
-  <si>
-    <t>TC-APP-206: Verify swipe gestures on email input form control on mobile view of Mobile: Mobile Mess Feedback (Check #206)</t>
-  </si>
-  <si>
-    <t>TC-APP-207: Check text wrapping of sidebar navigation items on mobile display of Mobile: Mobile Warden Dashboard (Check #207)</t>
-  </si>
-  <si>
-    <t>TC-APP-208: Verify navigation to Mobile: Mobile Admin Login via mobile sidebar menu options (Check #208)</t>
-  </si>
-  <si>
-    <t>TC-APP-209: Verify swipe gestures on database connection module on mobile view of Mobile: Mobile Mess Feedback (Check #209)</t>
-  </si>
-  <si>
-    <t>TC-APP-210: Verify sidebar navigation items is visible on mobile view of Mobile: Mobile Mess Feedback (Check #210)</t>
-  </si>
-  <si>
-    <t>TC-APP-211: Verify password input text box is visible on mobile view of Mobile: Mobile Mess Feedback (Check #211)</t>
-  </si>
-  <si>
-    <t>TC-APP-212: Check touch target size for submit button control on mobile screen of Mobile: Mobile Mess Feedback (Check #212)</t>
-  </si>
-  <si>
-    <t>TC-APP-213: Verify role selection button is visible on mobile view of Mobile: Mobile Raise Complaint (Check #213)</t>
-  </si>
-  <si>
-    <t>TC-APP-214: Verify username input text field is visible on mobile view of Mobile: Mobile Logout (Check #214)</t>
-  </si>
-  <si>
-    <t>TC-APP-215: Check text wrapping of complaint history table on mobile display of Mobile: Mobile Admin Login (Check #215)</t>
-  </si>
-  <si>
-    <t>TC-APP-216: Verify swipe gestures on dashboard metrics card on mobile view of Mobile: Mobile Student Dashboard (Check #216)</t>
-  </si>
-  <si>
-    <t>TC-APP-217: Verify navigation to Mobile: Mobile Warden Login via mobile sidebar menu options (Check #217)</t>
-  </si>
-  <si>
-    <t>TC-APP-218: Assert container padding and alignment on mobile screen for Mobile: Mobile Warden Login (Check #218)</t>
-  </si>
-  <si>
-    <t>TC-APP-219: Test student login flow through mobile interface of Mobile: Mobile Admin Login (Check #219)</t>
-  </si>
-  <si>
-    <t>TC-APP-220: Verify fee status badge display is visible on mobile view of Mobile: Mobile Role Selection (Check #220)</t>
-  </si>
-  <si>
-    <t>TC-APP-221: Check touch target size for email input form control on mobile screen of Mobile: Mobile Profile Settings (Check #221)</t>
-  </si>
-  <si>
-    <t>TC-APP-222: Verify swipe gestures on notice board widget on mobile view of Mobile: Mobile Role Selection (Check #222)</t>
-  </si>
-  <si>
-    <t>TC-APP-223: Test student login flow through mobile interface of Mobile: Mobile Admin Login (Check #223)</t>
-  </si>
-  <si>
-    <t>TC-APP-224: Verify navigation to Mobile: Mobile Raise Complaint via mobile sidebar menu options (Check #224)</t>
-  </si>
-  <si>
-    <t>TC-APP-225: Test student login flow through mobile interface of Mobile: Mobile Admin Login (Check #225)</t>
-  </si>
-  <si>
-    <t>TC-APP-226: Verify keyboard dismissal after entering text in profile image uploader container on Mobile: Mobile Warden Login (Check #226)</t>
-  </si>
-  <si>
-    <t>TC-APP-227: Check touch target size for email input form control on mobile screen of Mobile: Mobile Mess Feedback (Check #227)</t>
-  </si>
-  <si>
-    <t>TC-APP-228: Check touch target size for role selection button on mobile screen of Mobile: Mobile Landing (Check #228)</t>
-  </si>
-  <si>
-    <t>TC-APP-229: Verify swipe gestures on database connection module on mobile view of Mobile: Mobile Student Login (Check #229)</t>
-  </si>
-  <si>
-    <t>TC-APP-230: Check touch target size for footer copyright note on mobile screen of Mobile: Mobile Warden Login (Check #230)</t>
-  </si>
-  <si>
-    <t>TC-APP-231: Verify swipe gestures on email input form control on mobile view of Mobile: Mobile Landing (Check #231)</t>
-  </si>
-  <si>
-    <t>TC-APP-232: Verify notice board widget is visible on mobile view of Mobile: Mobile Student Dashboard (Check #232)</t>
-  </si>
-  <si>
-    <t>TC-APP-233: Verify navigation to Mobile: Mobile Warden Login via mobile sidebar menu options (Check #233)</t>
-  </si>
-  <si>
-    <t>TC-APP-234: Check text wrapping of profile image uploader container on mobile display of Mobile: Mobile Room View (Check #234)</t>
-  </si>
-  <si>
-    <t>TC-APP-235: Check text wrapping of alert dialog box on mobile display of Mobile: Mobile Warden Dashboard (Check #235)</t>
-  </si>
-  <si>
-    <t>TC-APP-236: Check touch target size for profile image uploader container on mobile screen of Mobile: Mobile Logout (Check #236)</t>
-  </si>
-  <si>
-    <t>TC-APP-237: Check touch target size for notice board widget on mobile screen of Mobile: Mobile Mess Feedback (Check #237)</t>
-  </si>
-  <si>
-    <t>TC-APP-238: Verify keyboard dismissal after entering text in password input text box on Mobile: Mobile Admin Login (Check #238)</t>
-  </si>
-  <si>
-    <t>TC-APP-239: Verify dashboard metrics card is visible on mobile view of Mobile: Mobile Room View (Check #239)</t>
-  </si>
-  <si>
-    <t>TC-APP-240: Verify swipe gestures on password input text box on mobile view of Mobile: Mobile Profile Settings (Check #240)</t>
-  </si>
-  <si>
-    <t>TC-APP-241: Verify password input text box is visible on mobile view of Mobile: Mobile Raise Complaint (Check #241)</t>
-  </si>
-  <si>
-    <t>TC-APP-242: Check text wrapping of fee status badge display on mobile display of Mobile: Mobile Profile Settings (Check #242)</t>
-  </si>
-  <si>
-    <t>TC-APP-243: Test student login flow through mobile interface of Mobile: Mobile Profile Settings (Check #243)</t>
-  </si>
-  <si>
-    <t>TC-APP-244: Test student login flow through mobile interface of Mobile: Mobile Raise Complaint (Check #244)</t>
-  </si>
-  <si>
-    <t>TC-APP-245: Verify keyboard dismissal after entering text in profile image uploader container on Mobile: Mobile Role Selection (Check #245)</t>
-  </si>
-  <si>
-    <t>TC-APP-246: Verify navigation to Mobile: Mobile Warden Dashboard via mobile sidebar menu options (Check #246)</t>
-  </si>
-  <si>
-    <t>TC-APP-247: Verify swipe gestures on back button navigation link on mobile view of Mobile: Mobile Admin Login (Check #247)</t>
-  </si>
-  <si>
-    <t>TC-APP-248: Verify footer copyright note is visible on mobile view of Mobile: Mobile Student Login (Check #248)</t>
-  </si>
-  <si>
-    <t>TC-APP-249: Assert container padding and alignment on mobile screen for Mobile: Mobile Mess Feedback (Check #249)</t>
-  </si>
-  <si>
-    <t>TC-APP-250: Verify submit button control is visible on mobile view of Mobile: Mobile Room View (Check #250)</t>
-  </si>
-  <si>
-    <t>TC-APP-251: Verify navigation to Mobile: Mobile Raise Complaint via mobile sidebar menu options (Check #251)</t>
-  </si>
-  <si>
-    <t>TC-APP-252: Verify submit button control is visible on mobile view of Mobile: Mobile Admin Dashboard (Check #252)</t>
-  </si>
-  <si>
-    <t>TC-APP-253: Check touch target size for leave request request form on mobile screen of Mobile: Mobile Mess Feedback (Check #253)</t>
-  </si>
-  <si>
-    <t>TC-APP-254: Verify navigation to Mobile: Mobile Raise Complaint via mobile sidebar menu options (Check #254)</t>
-  </si>
-  <si>
-    <t>TC-APP-255: Verify navigation to Mobile: Mobile Mess Feedback via mobile sidebar menu options (Check #255)</t>
-  </si>
-  <si>
-    <t>TC-APP-256: Verify swipe gestures on footer copyright note on mobile view of Mobile: Mobile Admin Login (Check #256)</t>
-  </si>
-  <si>
-    <t>TC-APP-257: Test student login flow through mobile interface of Mobile: Mobile Warden Login (Check #257)</t>
-  </si>
-  <si>
-    <t>TC-APP-258: Check touch target size for password input text box on mobile screen of Mobile: Mobile Mess Feedback (Check #258)</t>
-  </si>
-  <si>
-    <t>TC-APP-259: Verify keyboard dismissal after entering text in sidebar navigation items on Mobile: Mobile Student Login (Check #259)</t>
-  </si>
-  <si>
-    <t>TC-APP-260: Check touch target size for email input form control on mobile screen of Mobile: Mobile Logout (Check #260)</t>
-  </si>
-  <si>
-    <t>TC-APP-261: Check touch target size for average rating star system on mobile screen of Mobile: Mobile Leave Request (Check #261)</t>
-  </si>
-  <si>
-    <t>TC-APP-262: Test student login flow through mobile interface of Mobile: Mobile Warden Login (Check #262)</t>
-  </si>
-  <si>
-    <t>TC-APP-263: Verify email input form control is visible on mobile view of Mobile: Mobile Student Dashboard (Check #263)</t>
-  </si>
-  <si>
-    <t>TC-APP-264: Verify username input text field is visible on mobile view of Mobile: Mobile Warden Dashboard (Check #264)</t>
-  </si>
-  <si>
-    <t>TC-APP-265: Verify keyboard dismissal after entering text in username input text field on Mobile: Mobile Room View (Check #265)</t>
-  </si>
-  <si>
-    <t>TC-APP-266: Assert container padding and alignment on mobile screen for Mobile: Mobile Admin Login (Check #266)</t>
-  </si>
-  <si>
-    <t>TC-APP-267: Test student login flow through mobile interface of Mobile: Mobile Student Dashboard (Check #267)</t>
-  </si>
-  <si>
-    <t>TC-APP-268: Check touch target size for role selection button on mobile screen of Mobile: Mobile Raise Complaint (Check #268)</t>
-  </si>
-  <si>
-    <t>TC-APP-269: Assert container padding and alignment on mobile screen for Mobile: Mobile Student Login (Check #269)</t>
+    <t>TC-APP-040: Verify keyboard dismissal after entering text in complaint history table on Mobile: Mobile Leave Request (Check #40)</t>
+  </si>
+  <si>
+    <t>TC-APP-041: Check text wrapping of email input form control on mobile display of Mobile: Mobile Profile Settings (Check #41)</t>
+  </si>
+  <si>
+    <t>TC-APP-042: Check text wrapping of alert dialog box on mobile display of Mobile: Mobile Admin Dashboard (Check #42)</t>
+  </si>
+  <si>
+    <t>TC-APP-043: Verify navigation to Mobile: Mobile Warden Login via mobile sidebar menu options (Check #43)</t>
+  </si>
+  <si>
+    <t>TC-APP-044: Verify dashboard metrics card is visible on mobile view of Mobile: Mobile Profile Settings (Check #44)</t>
+  </si>
+  <si>
+    <t>TC-APP-045: Check text wrapping of alert dialog box on mobile display of Mobile: Mobile Admin Dashboard (Check #45)</t>
+  </si>
+  <si>
+    <t>TC-APP-046: Test student login flow through mobile interface of Mobile: Mobile Student Login (Check #46)</t>
+  </si>
+  <si>
+    <t>TC-APP-047: Verify swipe gestures on submit button control on mobile view of Mobile: Mobile Room View (Check #47)</t>
+  </si>
+  <si>
+    <t>TC-APP-048: Test student login flow through mobile interface of Mobile: Mobile Warden Dashboard (Check #48)</t>
+  </si>
+  <si>
+    <t>TC-APP-049: Verify navigation to Mobile: Mobile Admin Dashboard via mobile sidebar menu options (Check #49)</t>
+  </si>
+  <si>
+    <t>TC-APP-050: Verify average rating star system is visible on mobile view of Mobile: Mobile Raise Complaint (Check #50)</t>
+  </si>
+  <si>
+    <t>TC-APP-051: Verify keyboard dismissal after entering text in notice board widget on Mobile: Mobile Mess Feedback (Check #51)</t>
+  </si>
+  <si>
+    <t>TC-APP-052: Check text wrapping of email input form control on mobile display of Mobile: Mobile Mess Feedback (Check #52)</t>
+  </si>
+  <si>
+    <t>TC-APP-053: Verify keyboard dismissal after entering text in back button navigation link on Mobile: Mobile Warden Login (Check #53)</t>
+  </si>
+  <si>
+    <t>TC-APP-054: Verify leave request request form is visible on mobile view of Mobile: Mobile Student Dashboard (Check #54)</t>
+  </si>
+  <si>
+    <t>TC-APP-055: Assert container padding and alignment on mobile screen for Mobile: Mobile Warden Login (Check #55)</t>
+  </si>
+  <si>
+    <t>TC-APP-056: Assert container padding and alignment on mobile screen for Mobile: Mobile Leave Request (Check #56)</t>
+  </si>
+  <si>
+    <t>TC-APP-057: Verify swipe gestures on back button navigation link on mobile view of Mobile: Mobile Logout (Check #57)</t>
+  </si>
+  <si>
+    <t>TC-APP-058: Assert container padding and alignment on mobile screen for Mobile: Mobile Raise Complaint (Check #58)</t>
+  </si>
+  <si>
+    <t>TC-APP-059: Test student login flow through mobile interface of Mobile: Mobile Warden Dashboard (Check #59)</t>
+  </si>
+  <si>
+    <t>TC-APP-060: Test student login flow through mobile interface of Mobile: Mobile Admin Login (Check #60)</t>
+  </si>
+  <si>
+    <t>TC-APP-061: Test student login flow through mobile interface of Mobile: Mobile Student Dashboard (Check #61)</t>
+  </si>
+  <si>
+    <t>TC-APP-062: Verify back button navigation link is visible on mobile view of Mobile: Mobile Raise Complaint (Check #62)</t>
+  </si>
+  <si>
+    <t>TC-APP-063: Verify swipe gestures on password input text box on mobile view of Mobile: Mobile Role Selection (Check #63)</t>
+  </si>
+  <si>
+    <t>TC-APP-064: Test student login flow through mobile interface of Mobile: Mobile Admin Login (Check #64)</t>
+  </si>
+  <si>
+    <t>TC-APP-065: Verify navigation to Mobile: Mobile Mess Feedback via mobile sidebar menu options (Check #65)</t>
+  </si>
+  <si>
+    <t>TC-APP-066: Assert container padding and alignment on mobile screen for Mobile: Mobile Admin Dashboard (Check #66)</t>
+  </si>
+  <si>
+    <t>TC-APP-067: Check touch target size for profile image uploader container on mobile screen of Mobile: Mobile Warden Login (Check #67)</t>
+  </si>
+  <si>
+    <t>TC-APP-068: Verify role selection button is visible on mobile view of Mobile: Mobile Student Login (Check #68)</t>
+  </si>
+  <si>
+    <t>TC-APP-069: Verify swipe gestures on password input text box on mobile view of Mobile: Mobile Warden Dashboard (Check #69)</t>
+  </si>
+  <si>
+    <t>TC-APP-070: Check text wrapping of leave request request form on mobile display of Mobile: Mobile Warden Login (Check #70)</t>
+  </si>
+  <si>
+    <t>TC-APP-071: Verify swipe gestures on password input text box on mobile view of Mobile: Mobile Landing (Check #71)</t>
+  </si>
+  <si>
+    <t>TC-APP-072: Verify email input form control is visible on mobile view of Mobile: Mobile Raise Complaint (Check #72)</t>
+  </si>
+  <si>
+    <t>TC-APP-073: Check touch target size for notice board widget on mobile screen of Mobile: Mobile Raise Complaint (Check #73)</t>
+  </si>
+  <si>
+    <t>TC-APP-074: Verify navigation to Mobile: Mobile Room View via mobile sidebar menu options (Check #74)</t>
+  </si>
+  <si>
+    <t>TC-APP-075: Verify complaint history table is visible on mobile view of Mobile: Mobile Warden Dashboard (Check #75)</t>
+  </si>
+  <si>
+    <t>TC-APP-076: Verify profile image uploader container is visible on mobile view of Mobile: Mobile Logout (Check #76)</t>
+  </si>
+  <si>
+    <t>TC-APP-077: Verify swipe gestures on fee status badge display on mobile view of Mobile: Mobile Student Login (Check #77)</t>
+  </si>
+  <si>
+    <t>TC-APP-078: Test student login flow through mobile interface of Mobile: Mobile Room View (Check #78)</t>
+  </si>
+  <si>
+    <t>TC-APP-079: Verify profile image uploader container is visible on mobile view of Mobile: Mobile Landing (Check #79)</t>
+  </si>
+  <si>
+    <t>TC-APP-080: Assert container padding and alignment on mobile screen for Mobile: Mobile Role Selection (Check #80)</t>
+  </si>
+  <si>
+    <t>TC-APP-081: Assert container padding and alignment on mobile screen for Mobile: Mobile Student Dashboard (Check #81)</t>
+  </si>
+  <si>
+    <t>TC-APP-082: Verify navigation to Mobile: Mobile Student Login via mobile sidebar menu options (Check #82)</t>
+  </si>
+  <si>
+    <t>TC-APP-083: Check touch target size for back button navigation link on mobile screen of Mobile: Mobile Admin Dashboard (Check #83)</t>
+  </si>
+  <si>
+    <t>TC-APP-084: Verify swipe gestures on main navigation header on mobile view of Mobile: Mobile Profile Settings (Check #84)</t>
+  </si>
+  <si>
+    <t>TC-APP-085: Verify swipe gestures on sidebar navigation items on mobile view of Mobile: Mobile Warden Login (Check #85)</t>
+  </si>
+  <si>
+    <t>TC-APP-086: Check touch target size for dashboard metrics card on mobile screen of Mobile: Mobile Role Selection (Check #86)</t>
+  </si>
+  <si>
+    <t>TC-APP-087: Check touch target size for back button navigation link on mobile screen of Mobile: Mobile Role Selection (Check #87)</t>
+  </si>
+  <si>
+    <t>TC-APP-088: Verify profile image uploader container is visible on mobile view of Mobile: Mobile Logout (Check #88)</t>
+  </si>
+  <si>
+    <t>TC-APP-089: Test student login flow through mobile interface of Mobile: Mobile Leave Request (Check #89)</t>
+  </si>
+  <si>
+    <t>TC-APP-090: Verify footer copyright note is visible on mobile view of Mobile: Mobile Student Login (Check #90)</t>
+  </si>
+  <si>
+    <t>TC-APP-091: Assert container padding and alignment on mobile screen for Mobile: Mobile Student Dashboard (Check #91)</t>
+  </si>
+  <si>
+    <t>TC-APP-092: Assert container padding and alignment on mobile screen for Mobile: Mobile Mess Feedback (Check #92)</t>
+  </si>
+  <si>
+    <t>TC-APP-093: Check touch target size for role selection button on mobile screen of Mobile: Mobile Admin Login (Check #93)</t>
+  </si>
+  <si>
+    <t>TC-APP-094: Assert container padding and alignment on mobile screen for Mobile: Mobile Warden Login (Check #94)</t>
+  </si>
+  <si>
+    <t>TC-APP-095: Verify keyboard dismissal after entering text in email input form control on Mobile: Mobile Leave Request (Check #95)</t>
+  </si>
+  <si>
+    <t>TC-APP-096: Check text wrapping of username input text field on mobile display of Mobile: Mobile Leave Request (Check #96)</t>
+  </si>
+  <si>
+    <t>TC-APP-097: Verify keyboard dismissal after entering text in leave request request form on Mobile: Mobile Student Login (Check #97)</t>
+  </si>
+  <si>
+    <t>TC-APP-098: Check text wrapping of submit button control on mobile display of Mobile: Mobile Warden Dashboard (Check #98)</t>
+  </si>
+  <si>
+    <t>TC-APP-099: Verify swipe gestures on footer copyright note on mobile view of Mobile: Mobile Leave Request (Check #99)</t>
+  </si>
+  <si>
+    <t>TC-APP-100: Verify swipe gestures on alert dialog box on mobile view of Mobile: Mobile Admin Dashboard (Check #100)</t>
+  </si>
+  <si>
+    <t>TC-APP-101: Test student login flow through mobile interface of Mobile: Mobile Warden Dashboard (Check #101)</t>
+  </si>
+  <si>
+    <t>TC-APP-102: Verify swipe gestures on database connection module on mobile view of Mobile: Mobile Logout (Check #102)</t>
+  </si>
+  <si>
+    <t>TC-APP-103: Verify keyboard dismissal after entering text in sidebar navigation items on Mobile: Mobile Raise Complaint (Check #103)</t>
+  </si>
+  <si>
+    <t>TC-APP-104: Verify back button navigation link is visible on mobile view of Mobile: Mobile Warden Dashboard (Check #104)</t>
+  </si>
+  <si>
+    <t>TC-APP-105: Verify navigation to Mobile: Mobile Mess Feedback via mobile sidebar menu options (Check #105)</t>
+  </si>
+  <si>
+    <t>TC-APP-106: Verify navigation to Mobile: Mobile Raise Complaint via mobile sidebar menu options (Check #106)</t>
+  </si>
+  <si>
+    <t>TC-APP-107: Check touch target size for dashboard metrics card on mobile screen of Mobile: Mobile Warden Login (Check #107)</t>
+  </si>
+  <si>
+    <t>TC-APP-108: Verify swipe gestures on alert dialog box on mobile view of Mobile: Mobile Leave Request (Check #108)</t>
+  </si>
+  <si>
+    <t>TC-APP-109: Verify keyboard dismissal after entering text in fee status badge display on Mobile: Mobile Raise Complaint (Check #109)</t>
+  </si>
+  <si>
+    <t>TC-APP-110: Verify keyboard dismissal after entering text in footer copyright note on Mobile: Mobile Warden Dashboard (Check #110)</t>
+  </si>
+  <si>
+    <t>TC-APP-111: Verify swipe gestures on password input text box on mobile view of Mobile: Mobile Profile Settings (Check #111)</t>
+  </si>
+  <si>
+    <t>TC-APP-112: Verify sidebar navigation items is visible on mobile view of Mobile: Mobile Landing (Check #112)</t>
+  </si>
+  <si>
+    <t>TC-APP-113: Verify navigation to Mobile: Mobile Raise Complaint via mobile sidebar menu options (Check #113)</t>
+  </si>
+  <si>
+    <t>TC-APP-114: Verify keyboard dismissal after entering text in dashboard metrics card on Mobile: Mobile Leave Request (Check #114)</t>
+  </si>
+  <si>
+    <t>TC-APP-115: Check touch target size for alert dialog box on mobile screen of Mobile: Mobile Warden Dashboard (Check #115)</t>
+  </si>
+  <si>
+    <t>TC-APP-116: Verify keyboard dismissal after entering text in footer copyright note on Mobile: Mobile Admin Login (Check #116)</t>
+  </si>
+  <si>
+    <t>TC-APP-117: Test student login flow through mobile interface of Mobile: Mobile Mess Feedback (Check #117)</t>
+  </si>
+  <si>
+    <t>TC-APP-118: Verify swipe gestures on main navigation header on mobile view of Mobile: Mobile Profile Settings (Check #118)</t>
+  </si>
+  <si>
+    <t>TC-APP-119: Assert container padding and alignment on mobile screen for Mobile: Mobile Admin Dashboard (Check #119)</t>
+  </si>
+  <si>
+    <t>TC-APP-120: Assert container padding and alignment on mobile screen for Mobile: Mobile Student Login (Check #120)</t>
+  </si>
+  <si>
+    <t>TC-APP-121: Test student login flow through mobile interface of Mobile: Mobile Raise Complaint (Check #121)</t>
+  </si>
+  <si>
+    <t>TC-APP-122: Assert container padding and alignment on mobile screen for Mobile: Mobile Profile Settings (Check #122)</t>
+  </si>
+  <si>
+    <t>TC-APP-123: Verify navigation to Mobile: Mobile Warden Dashboard via mobile sidebar menu options (Check #123)</t>
+  </si>
+  <si>
+    <t>TC-APP-124: Verify back button navigation link is visible on mobile view of Mobile: Mobile Warden Dashboard (Check #124)</t>
+  </si>
+  <si>
+    <t>TC-APP-125: Verify notice board widget is visible on mobile view of Mobile: Mobile Raise Complaint (Check #125)</t>
+  </si>
+  <si>
+    <t>TC-APP-126: Verify swipe gestures on dashboard metrics card on mobile view of Mobile: Mobile Mess Feedback (Check #126)</t>
+  </si>
+  <si>
+    <t>TC-APP-127: Verify password input text box is visible on mobile view of Mobile: Mobile Landing (Check #127)</t>
+  </si>
+  <si>
+    <t>TC-APP-128: Assert container padding and alignment on mobile screen for Mobile: Mobile Room View (Check #128)</t>
+  </si>
+  <si>
+    <t>TC-APP-129: Test student login flow through mobile interface of Mobile: Mobile Raise Complaint (Check #129)</t>
+  </si>
+  <si>
+    <t>TC-APP-130: Verify swipe gestures on leave request request form on mobile view of Mobile: Mobile Student Dashboard (Check #130)</t>
+  </si>
+  <si>
+    <t>TC-APP-131: Verify keyboard dismissal after entering text in role selection button on Mobile: Mobile Leave Request (Check #131)</t>
+  </si>
+  <si>
+    <t>TC-APP-132: Verify swipe gestures on submit button control on mobile view of Mobile: Mobile Warden Login (Check #132)</t>
+  </si>
+  <si>
+    <t>TC-APP-133: Verify keyboard dismissal after entering text in database connection module on Mobile: Mobile Warden Login (Check #133)</t>
+  </si>
+  <si>
+    <t>TC-APP-134: Verify complaint history table is visible on mobile view of Mobile: Mobile Role Selection (Check #134)</t>
+  </si>
+  <si>
+    <t>TC-APP-135: Check touch target size for submit button control on mobile screen of Mobile: Mobile Profile Settings (Check #135)</t>
+  </si>
+  <si>
+    <t>TC-APP-136: Test student login flow through mobile interface of Mobile: Mobile Admin Dashboard (Check #136)</t>
+  </si>
+  <si>
+    <t>TC-APP-137: Verify navigation to Mobile: Mobile Profile Settings via mobile sidebar menu options (Check #137)</t>
+  </si>
+  <si>
+    <t>TC-APP-138: Verify keyboard dismissal after entering text in footer copyright note on Mobile: Mobile Admin Dashboard (Check #138)</t>
+  </si>
+  <si>
+    <t>TC-APP-139: Test student login flow through mobile interface of Mobile: Mobile Admin Login (Check #139)</t>
+  </si>
+  <si>
+    <t>TC-APP-140: Verify keyboard dismissal after entering text in fee status badge display on Mobile: Mobile Logout (Check #140)</t>
+  </si>
+  <si>
+    <t>TC-APP-141: Verify navigation to Mobile: Mobile Warden Login via mobile sidebar menu options (Check #141)</t>
+  </si>
+  <si>
+    <t>TC-APP-142: Test student login flow through mobile interface of Mobile: Mobile Landing (Check #142)</t>
+  </si>
+  <si>
+    <t>TC-APP-143: Verify keyboard dismissal after entering text in dashboard metrics card on Mobile: Mobile Warden Login (Check #143)</t>
+  </si>
+  <si>
+    <t>TC-APP-144: Verify sidebar navigation items is visible on mobile view of Mobile: Mobile Mess Feedback (Check #144)</t>
+  </si>
+  <si>
+    <t>TC-APP-145: Verify navigation to Mobile: Mobile Logout via mobile sidebar menu options (Check #145)</t>
+  </si>
+  <si>
+    <t>TC-APP-146: Test student login flow through mobile interface of Mobile: Mobile Role Selection (Check #146)</t>
+  </si>
+  <si>
+    <t>TC-APP-147: Verify swipe gestures on footer copyright note on mobile view of Mobile: Mobile Role Selection (Check #147)</t>
+  </si>
+  <si>
+    <t>TC-APP-148: Verify keyboard dismissal after entering text in password input text box on Mobile: Mobile Warden Login (Check #148)</t>
+  </si>
+  <si>
+    <t>TC-APP-149: Test student login flow through mobile interface of Mobile: Mobile Leave Request (Check #149)</t>
+  </si>
+  <si>
+    <t>TC-APP-150: Verify notice board widget is visible on mobile view of Mobile: Mobile Leave Request (Check #150)</t>
+  </si>
+  <si>
+    <t>TC-APP-151: Check text wrapping of role selection button on mobile display of Mobile: Mobile Logout (Check #151)</t>
+  </si>
+  <si>
+    <t>TC-APP-152: Check touch target size for alert dialog box on mobile screen of Mobile: Mobile Warden Dashboard (Check #152)</t>
+  </si>
+  <si>
+    <t>TC-APP-153: Verify navigation to Mobile: Mobile Admin Login via mobile sidebar menu options (Check #153)</t>
+  </si>
+  <si>
+    <t>TC-APP-154: Check touch target size for sidebar navigation items on mobile screen of Mobile: Mobile Leave Request (Check #154)</t>
+  </si>
+  <si>
+    <t>TC-APP-155: Test student login flow through mobile interface of Mobile: Mobile Logout (Check #155)</t>
+  </si>
+  <si>
+    <t>TC-APP-156: Verify keyboard dismissal after entering text in role selection button on Mobile: Mobile Student Dashboard (Check #156)</t>
+  </si>
+  <si>
+    <t>TC-APP-157: Verify keyboard dismissal after entering text in password input text box on Mobile: Mobile Room View (Check #157)</t>
+  </si>
+  <si>
+    <t>TC-APP-158: Check text wrapping of main navigation header on mobile display of Mobile: Mobile Warden Login (Check #158)</t>
+  </si>
+  <si>
+    <t>TC-APP-159: Verify swipe gestures on leave request request form on mobile view of Mobile: Mobile Leave Request (Check #159)</t>
+  </si>
+  <si>
+    <t>TC-APP-160: Check text wrapping of username input text field on mobile display of Mobile: Mobile Logout (Check #160)</t>
+  </si>
+  <si>
+    <t>TC-APP-161: Verify swipe gestures on main navigation header on mobile view of Mobile: Mobile Logout (Check #161)</t>
+  </si>
+  <si>
+    <t>TC-APP-162: Verify navigation to Mobile: Mobile Student Dashboard via mobile sidebar menu options (Check #162)</t>
+  </si>
+  <si>
+    <t>TC-APP-163: Check touch target size for alert dialog box on mobile screen of Mobile: Mobile Landing (Check #163)</t>
+  </si>
+  <si>
+    <t>TC-APP-164: Check touch target size for leave request request form on mobile screen of Mobile: Mobile Leave Request (Check #164)</t>
+  </si>
+  <si>
+    <t>TC-APP-165: Test student login flow through mobile interface of Mobile: Mobile Leave Request (Check #165)</t>
+  </si>
+  <si>
+    <t>TC-APP-166: Check touch target size for sidebar navigation items on mobile screen of Mobile: Mobile Warden Dashboard (Check #166)</t>
+  </si>
+  <si>
+    <t>TC-APP-167: Assert container padding and alignment on mobile screen for Mobile: Mobile Leave Request (Check #167)</t>
+  </si>
+  <si>
+    <t>TC-APP-168: Verify keyboard dismissal after entering text in sidebar navigation items on Mobile: Mobile Logout (Check #168)</t>
+  </si>
+  <si>
+    <t>TC-APP-169: Assert container padding and alignment on mobile screen for Mobile: Mobile Profile Settings (Check #169)</t>
+  </si>
+  <si>
+    <t>TC-APP-170: Verify swipe gestures on complaint history table on mobile view of Mobile: Mobile Landing (Check #170)</t>
+  </si>
+  <si>
+    <t>TC-APP-171: Check text wrapping of leave request request form on mobile display of Mobile: Mobile Admin Dashboard (Check #171)</t>
+  </si>
+  <si>
+    <t>TC-APP-172: Check text wrapping of role selection button on mobile display of Mobile: Mobile Student Dashboard (Check #172)</t>
+  </si>
+  <si>
+    <t>TC-APP-173: Assert container padding and alignment on mobile screen for Mobile: Mobile Role Selection (Check #173)</t>
+  </si>
+  <si>
+    <t>TC-APP-174: Verify keyboard dismissal after entering text in username input text field on Mobile: Mobile Raise Complaint (Check #174)</t>
+  </si>
+  <si>
+    <t>TC-APP-175: Check touch target size for alert dialog box on mobile screen of Mobile: Mobile Admin Login (Check #175)</t>
+  </si>
+  <si>
+    <t>TC-APP-176: Verify navigation to Mobile: Mobile Logout via mobile sidebar menu options (Check #176)</t>
+  </si>
+  <si>
+    <t>TC-APP-177: Check touch target size for notice board widget on mobile screen of Mobile: Mobile Student Login (Check #177)</t>
+  </si>
+  <si>
+    <t>TC-APP-178: Check touch target size for database connection module on mobile screen of Mobile: Mobile Role Selection (Check #178)</t>
+  </si>
+  <si>
+    <t>TC-APP-179: Verify navigation to Mobile: Mobile Mess Feedback via mobile sidebar menu options (Check #179)</t>
+  </si>
+  <si>
+    <t>TC-APP-180: Check text wrapping of back button navigation link on mobile display of Mobile: Mobile Raise Complaint (Check #180)</t>
+  </si>
+  <si>
+    <t>TC-APP-181: Verify navigation to Mobile: Mobile Admin Dashboard via mobile sidebar menu options (Check #181)</t>
+  </si>
+  <si>
+    <t>TC-APP-182: Test student login flow through mobile interface of Mobile: Mobile Mess Feedback (Check #182)</t>
+  </si>
+  <si>
+    <t>TC-APP-183: Verify keyboard dismissal after entering text in email input form control on Mobile: Mobile Mess Feedback (Check #183)</t>
+  </si>
+  <si>
+    <t>TC-APP-184: Verify keyboard dismissal after entering text in role selection button on Mobile: Mobile Student Login (Check #184)</t>
+  </si>
+  <si>
+    <t>TC-APP-185: Verify notice board widget is visible on mobile view of Mobile: Mobile Mess Feedback (Check #185)</t>
+  </si>
+  <si>
+    <t>TC-APP-186: Test student login flow through mobile interface of Mobile: Mobile Warden Login (Check #186)</t>
+  </si>
+  <si>
+    <t>TC-APP-187: Test student login flow through mobile interface of Mobile: Mobile Warden Login (Check #187)</t>
+  </si>
+  <si>
+    <t>TC-APP-188: Verify swipe gestures on database connection module on mobile view of Mobile: Mobile Raise Complaint (Check #188)</t>
+  </si>
+  <si>
+    <t>TC-APP-189: Assert container padding and alignment on mobile screen for Mobile: Mobile Raise Complaint (Check #189)</t>
+  </si>
+  <si>
+    <t>TC-APP-190: Test student login flow through mobile interface of Mobile: Mobile Leave Request (Check #190)</t>
+  </si>
+  <si>
+    <t>TC-APP-191: Verify swipe gestures on back button navigation link on mobile view of Mobile: Mobile Role Selection (Check #191)</t>
+  </si>
+  <si>
+    <t>TC-APP-192: Check touch target size for database connection module on mobile screen of Mobile: Mobile Room View (Check #192)</t>
+  </si>
+  <si>
+    <t>TC-APP-193: Verify navigation to Mobile: Mobile Role Selection via mobile sidebar menu options (Check #193)</t>
+  </si>
+  <si>
+    <t>TC-APP-194: Verify navigation to Mobile: Mobile Warden Dashboard via mobile sidebar menu options (Check #194)</t>
+  </si>
+  <si>
+    <t>TC-APP-195: Verify swipe gestures on submit button control on mobile view of Mobile: Mobile Landing (Check #195)</t>
+  </si>
+  <si>
+    <t>TC-APP-196: Verify complaint history table is visible on mobile view of Mobile: Mobile Mess Feedback (Check #196)</t>
+  </si>
+  <si>
+    <t>TC-APP-197: Verify navigation to Mobile: Mobile Warden Dashboard via mobile sidebar menu options (Check #197)</t>
+  </si>
+  <si>
+    <t>TC-APP-198: Verify navigation to Mobile: Mobile Admin Dashboard via mobile sidebar menu options (Check #198)</t>
+  </si>
+  <si>
+    <t>TC-APP-199: Verify back button navigation link is visible on mobile view of Mobile: Mobile Admin Login (Check #199)</t>
+  </si>
+  <si>
+    <t>TC-APP-200: Verify navigation to Mobile: Mobile Student Dashboard via mobile sidebar menu options (Check #200)</t>
+  </si>
+  <si>
+    <t>TC-APP-201: Check text wrapping of profile image uploader container on mobile display of Mobile: Mobile Student Dashboard (Check #201)</t>
+  </si>
+  <si>
+    <t>TC-APP-202: Test student login flow through mobile interface of Mobile: Mobile Room View (Check #202)</t>
+  </si>
+  <si>
+    <t>TC-APP-203: Assert container padding and alignment on mobile screen for Mobile: Mobile Mess Feedback (Check #203)</t>
+  </si>
+  <si>
+    <t>TC-APP-204: Verify footer copyright note is visible on mobile view of Mobile: Mobile Student Login (Check #204)</t>
+  </si>
+  <si>
+    <t>TC-APP-205: Verify swipe gestures on complaint history table on mobile view of Mobile: Mobile Logout (Check #205)</t>
+  </si>
+  <si>
+    <t>TC-APP-206: Verify username input text field is visible on mobile view of Mobile: Mobile Warden Dashboard (Check #206)</t>
+  </si>
+  <si>
+    <t>TC-APP-207: Verify navigation to Mobile: Mobile Warden Dashboard via mobile sidebar menu options (Check #207)</t>
+  </si>
+  <si>
+    <t>TC-APP-208: Check text wrapping of profile image uploader container on mobile display of Mobile: Mobile Raise Complaint (Check #208)</t>
+  </si>
+  <si>
+    <t>TC-APP-209: Verify navigation to Mobile: Mobile Role Selection via mobile sidebar menu options (Check #209)</t>
+  </si>
+  <si>
+    <t>TC-APP-210: Verify keyboard dismissal after entering text in alert dialog box on Mobile: Mobile Logout (Check #210)</t>
+  </si>
+  <si>
+    <t>TC-APP-211: Verify notice board widget is visible on mobile view of Mobile: Mobile Leave Request (Check #211)</t>
+  </si>
+  <si>
+    <t>TC-APP-212: Assert container padding and alignment on mobile screen for Mobile: Mobile Admin Login (Check #212)</t>
+  </si>
+  <si>
+    <t>TC-APP-213: Check touch target size for complaint history table on mobile screen of Mobile: Mobile Logout (Check #213)</t>
+  </si>
+  <si>
+    <t>TC-APP-214: Verify keyboard dismissal after entering text in complaint history table on Mobile: Mobile Admin Dashboard (Check #214)</t>
+  </si>
+  <si>
+    <t>TC-APP-215: Check touch target size for email input form control on mobile screen of Mobile: Mobile Admin Login (Check #215)</t>
+  </si>
+  <si>
+    <t>TC-APP-216: Assert container padding and alignment on mobile screen for Mobile: Mobile Raise Complaint (Check #216)</t>
+  </si>
+  <si>
+    <t>TC-APP-217: Verify role selection button is visible on mobile view of Mobile: Mobile Admin Dashboard (Check #217)</t>
+  </si>
+  <si>
+    <t>TC-APP-218: Test student login flow through mobile interface of Mobile: Mobile Profile Settings (Check #218)</t>
+  </si>
+  <si>
+    <t>TC-APP-219: Test student login flow through mobile interface of Mobile: Mobile Landing (Check #219)</t>
+  </si>
+  <si>
+    <t>TC-APP-220: Verify keyboard dismissal after entering text in submit button control on Mobile: Mobile Student Dashboard (Check #220)</t>
+  </si>
+  <si>
+    <t>TC-APP-221: Verify swipe gestures on alert dialog box on mobile view of Mobile: Mobile Mess Feedback (Check #221)</t>
+  </si>
+  <si>
+    <t>TC-APP-222: Assert container padding and alignment on mobile screen for Mobile: Mobile Role Selection (Check #222)</t>
+  </si>
+  <si>
+    <t>TC-APP-223: Verify swipe gestures on role selection button on mobile view of Mobile: Mobile Student Dashboard (Check #223)</t>
+  </si>
+  <si>
+    <t>TC-APP-224: Check text wrapping of main navigation header on mobile display of Mobile: Mobile Room View (Check #224)</t>
+  </si>
+  <si>
+    <t>TC-APP-225: Verify navigation to Mobile: Mobile Admin Login via mobile sidebar menu options (Check #225)</t>
+  </si>
+  <si>
+    <t>TC-APP-226: Verify swipe gestures on leave request request form on mobile view of Mobile: Mobile Landing (Check #226)</t>
+  </si>
+  <si>
+    <t>TC-APP-227: Verify swipe gestures on average rating star system on mobile view of Mobile: Mobile Room View (Check #227)</t>
+  </si>
+  <si>
+    <t>TC-APP-228: Verify keyboard dismissal after entering text in dashboard metrics card on Mobile: Mobile Landing (Check #228)</t>
+  </si>
+  <si>
+    <t>TC-APP-229: Verify swipe gestures on fee status badge display on mobile view of Mobile: Mobile Warden Login (Check #229)</t>
+  </si>
+  <si>
+    <t>TC-APP-230: Test student login flow through mobile interface of Mobile: Mobile Room View (Check #230)</t>
+  </si>
+  <si>
+    <t>TC-APP-231: Verify main navigation header is visible on mobile view of Mobile: Mobile Student Login (Check #231)</t>
+  </si>
+  <si>
+    <t>TC-APP-232: Test student login flow through mobile interface of Mobile: Mobile Mess Feedback (Check #232)</t>
+  </si>
+  <si>
+    <t>TC-APP-233: Check text wrapping of leave request request form on mobile display of Mobile: Mobile Warden Login (Check #233)</t>
+  </si>
+  <si>
+    <t>TC-APP-234: Test student login flow through mobile interface of Mobile: Mobile Leave Request (Check #234)</t>
+  </si>
+  <si>
+    <t>TC-APP-235: Verify keyboard dismissal after entering text in main navigation header on Mobile: Mobile Role Selection (Check #235)</t>
+  </si>
+  <si>
+    <t>TC-APP-236: Verify swipe gestures on profile image uploader container on mobile view of Mobile: Mobile Warden Login (Check #236)</t>
+  </si>
+  <si>
+    <t>TC-APP-237: Verify swipe gestures on username input text field on mobile view of Mobile: Mobile Admin Login (Check #237)</t>
+  </si>
+  <si>
+    <t>TC-APP-238: Assert container padding and alignment on mobile screen for Mobile: Mobile Warden Dashboard (Check #238)</t>
+  </si>
+  <si>
+    <t>TC-APP-239: Check touch target size for role selection button on mobile screen of Mobile: Mobile Warden Dashboard (Check #239)</t>
+  </si>
+  <si>
+    <t>TC-APP-240: Verify notice board widget is visible on mobile view of Mobile: Mobile Admin Login (Check #240)</t>
+  </si>
+  <si>
+    <t>TC-APP-241: Verify navigation to Mobile: Mobile Profile Settings via mobile sidebar menu options (Check #241)</t>
+  </si>
+  <si>
+    <t>TC-APP-242: Assert container padding and alignment on mobile screen for Mobile: Mobile Warden Dashboard (Check #242)</t>
+  </si>
+  <si>
+    <t>TC-APP-243: Verify navigation to Mobile: Mobile Admin Login via mobile sidebar menu options (Check #243)</t>
+  </si>
+  <si>
+    <t>TC-APP-244: Assert container padding and alignment on mobile screen for Mobile: Mobile Student Login (Check #244)</t>
+  </si>
+  <si>
+    <t>TC-APP-245: Verify keyboard dismissal after entering text in footer copyright note on Mobile: Mobile Role Selection (Check #245)</t>
+  </si>
+  <si>
+    <t>TC-APP-246: Check text wrapping of alert dialog box on mobile display of Mobile: Mobile Admin Dashboard (Check #246)</t>
+  </si>
+  <si>
+    <t>TC-APP-247: Verify database connection module is visible on mobile view of Mobile: Mobile Warden Dashboard (Check #247)</t>
+  </si>
+  <si>
+    <t>TC-APP-248: Check touch target size for sidebar navigation items on mobile screen of Mobile: Mobile Mess Feedback (Check #248)</t>
+  </si>
+  <si>
+    <t>TC-APP-249: Assert container padding and alignment on mobile screen for Mobile: Mobile Admin Login (Check #249)</t>
+  </si>
+  <si>
+    <t>TC-APP-250: Verify keyboard dismissal after entering text in leave request request form on Mobile: Mobile Logout (Check #250)</t>
+  </si>
+  <si>
+    <t>TC-APP-251: Test student login flow through mobile interface of Mobile: Mobile Warden Dashboard (Check #251)</t>
+  </si>
+  <si>
+    <t>TC-APP-252: Check text wrapping of username input text field on mobile display of Mobile: Mobile Logout (Check #252)</t>
+  </si>
+  <si>
+    <t>TC-APP-253: Verify complaint history table is visible on mobile view of Mobile: Mobile Student Login (Check #253)</t>
+  </si>
+  <si>
+    <t>TC-APP-254: Test student login flow through mobile interface of Mobile: Mobile Room View (Check #254)</t>
+  </si>
+  <si>
+    <t>TC-APP-255: Verify keyboard dismissal after entering text in username input text field on Mobile: Mobile Mess Feedback (Check #255)</t>
+  </si>
+  <si>
+    <t>TC-APP-256: Test student login flow through mobile interface of Mobile: Mobile Role Selection (Check #256)</t>
+  </si>
+  <si>
+    <t>TC-APP-257: Verify leave request request form is visible on mobile view of Mobile: Mobile Warden Dashboard (Check #257)</t>
+  </si>
+  <si>
+    <t>TC-APP-258: Check text wrapping of main navigation header on mobile display of Mobile: Mobile Leave Request (Check #258)</t>
+  </si>
+  <si>
+    <t>TC-APP-259: Verify keyboard dismissal after entering text in notice board widget on Mobile: Mobile Mess Feedback (Check #259)</t>
+  </si>
+  <si>
+    <t>TC-APP-260: Verify swipe gestures on notice board widget on mobile view of Mobile: Mobile Admin Login (Check #260)</t>
+  </si>
+  <si>
+    <t>TC-APP-261: Verify keyboard dismissal after entering text in username input text field on Mobile: Mobile Raise Complaint (Check #261)</t>
+  </si>
+  <si>
+    <t>TC-APP-262: Verify navigation to Mobile: Mobile Student Dashboard via mobile sidebar menu options (Check #262)</t>
+  </si>
+  <si>
+    <t>TC-APP-263: Verify role selection button is visible on mobile view of Mobile: Mobile Logout (Check #263)</t>
+  </si>
+  <si>
+    <t>TC-APP-264: Check text wrapping of database connection module on mobile display of Mobile: Mobile Student Dashboard (Check #264)</t>
+  </si>
+  <si>
+    <t>TC-APP-265: Check text wrapping of average rating star system on mobile display of Mobile: Mobile Raise Complaint (Check #265)</t>
+  </si>
+  <si>
+    <t>TC-APP-266: Check touch target size for profile image uploader container on mobile screen of Mobile: Mobile Mess Feedback (Check #266)</t>
+  </si>
+  <si>
+    <t>TC-APP-267: Verify swipe gestures on role selection button on mobile view of Mobile: Mobile Room View (Check #267)</t>
+  </si>
+  <si>
+    <t>TC-APP-268: Check touch target size for sidebar navigation items on mobile screen of Mobile: Mobile Admin Login (Check #268)</t>
+  </si>
+  <si>
+    <t>TC-APP-269: Verify keyboard dismissal after entering text in dashboard metrics card on Mobile: Mobile Role Selection (Check #269)</t>
   </si>
   <si>
     <t>TC-APP-270: Verify navigation to Mobile: Mobile Leave Request via mobile sidebar menu options (Check #270)</t>
   </si>
   <si>
-    <t>TC-APP-271: Verify navigation to Mobile: Mobile Admin Dashboard via mobile sidebar menu options (Check #271)</t>
-  </si>
-  <si>
-    <t>TC-APP-272: Verify swipe gestures on dashboard metrics card on mobile view of Mobile: Mobile Profile Settings (Check #272)</t>
-  </si>
-  <si>
-    <t>TC-APP-273: Check text wrapping of main navigation header on mobile display of Mobile: Mobile Logout (Check #273)</t>
-  </si>
-  <si>
-    <t>TC-APP-274: Check touch target size for average rating star system on mobile screen of Mobile: Mobile Mess Feedback (Check #274)</t>
-  </si>
-  <si>
-    <t>TC-APP-275: Check touch target size for main navigation header on mobile screen of Mobile: Mobile Student Dashboard (Check #275)</t>
-  </si>
-  <si>
-    <t>TC-APP-276: Verify fee status badge display is visible on mobile view of Mobile: Mobile Admin Login (Check #276)</t>
-  </si>
-  <si>
-    <t>TC-APP-277: Verify swipe gestures on profile image uploader container on mobile view of Mobile: Mobile Profile Settings (Check #277)</t>
-  </si>
-  <si>
-    <t>TC-APP-278: Verify back button navigation link is visible on mobile view of Mobile: Mobile Student Login (Check #278)</t>
-  </si>
-  <si>
-    <t>TC-APP-279: Verify swipe gestures on submit button control on mobile view of Mobile: Mobile Warden Dashboard (Check #279)</t>
-  </si>
-  <si>
-    <t>TC-APP-280: Verify leave request request form is visible on mobile view of Mobile: Mobile Student Dashboard (Check #280)</t>
-  </si>
-  <si>
-    <t>TC-APP-281: Test student login flow through mobile interface of Mobile: Mobile Admin Login (Check #281)</t>
-  </si>
-  <si>
-    <t>TC-APP-282: Verify main navigation header is visible on mobile view of Mobile: Mobile Logout (Check #282)</t>
-  </si>
-  <si>
-    <t>TC-APP-283: Test student login flow through mobile interface of Mobile: Mobile Student Login (Check #283)</t>
-  </si>
-  <si>
-    <t>TC-APP-284: Assert container padding and alignment on mobile screen for Mobile: Mobile Student Login (Check #284)</t>
-  </si>
-  <si>
-    <t>TC-APP-285: Assert container padding and alignment on mobile screen for Mobile: Mobile Logout (Check #285)</t>
-  </si>
-  <si>
-    <t>TC-APP-286: Verify navigation to Mobile: Mobile Leave Request via mobile sidebar menu options (Check #286)</t>
-  </si>
-  <si>
-    <t>TC-APP-287: Check text wrapping of password input text box on mobile display of Mobile: Mobile Student Login (Check #287)</t>
-  </si>
-  <si>
-    <t>TC-APP-288: Verify alert dialog box is visible on mobile view of Mobile: Mobile Raise Complaint (Check #288)</t>
-  </si>
-  <si>
-    <t>TC-APP-289: Check touch target size for main navigation header on mobile screen of Mobile: Mobile Landing (Check #289)</t>
-  </si>
-  <si>
-    <t>TC-APP-290: Verify swipe gestures on sidebar navigation items on mobile view of Mobile: Mobile Admin Login (Check #290)</t>
-  </si>
-  <si>
-    <t>TC-APP-291: Verify navigation to Mobile: Mobile Warden Login via mobile sidebar menu options (Check #291)</t>
-  </si>
-  <si>
-    <t>TC-APP-292: Check touch target size for database connection module on mobile screen of Mobile: Mobile Mess Feedback (Check #292)</t>
-  </si>
-  <si>
-    <t>TC-APP-293: Verify profile image uploader container is visible on mobile view of Mobile: Mobile Mess Feedback (Check #293)</t>
-  </si>
-  <si>
-    <t>TC-APP-294: Verify alert dialog box is visible on mobile view of Mobile: Mobile Warden Dashboard (Check #294)</t>
-  </si>
-  <si>
-    <t>TC-APP-295: Verify swipe gestures on leave request request form on mobile view of Mobile: Mobile Mess Feedback (Check #295)</t>
-  </si>
-  <si>
-    <t>TC-APP-296: Assert container padding and alignment on mobile screen for Mobile: Mobile Student Login (Check #296)</t>
-  </si>
-  <si>
-    <t>TC-APP-297: Test student login flow through mobile interface of Mobile: Mobile Role Selection (Check #297)</t>
-  </si>
-  <si>
-    <t>TC-APP-298: Assert container padding and alignment on mobile screen for Mobile: Mobile Student Login (Check #298)</t>
-  </si>
-  <si>
-    <t>TC-APP-299: Test student login flow through mobile interface of Mobile: Mobile Student Dashboard (Check #299)</t>
-  </si>
-  <si>
-    <t>TC-APP-300: Assert container padding and alignment on mobile screen for Mobile: Mobile Warden Login (Check #300)</t>
+    <t>TC-APP-271: Assert container padding and alignment on mobile screen for Mobile: Mobile Admin Dashboard (Check #271)</t>
+  </si>
+  <si>
+    <t>TC-APP-272: Verify fee status badge display is visible on mobile view of Mobile: Mobile Profile Settings (Check #272)</t>
+  </si>
+  <si>
+    <t>TC-APP-273: Verify swipe gestures on submit button control on mobile view of Mobile: Mobile Profile Settings (Check #273)</t>
+  </si>
+  <si>
+    <t>TC-APP-274: Verify keyboard dismissal after entering text in footer copyright note on Mobile: Mobile Logout (Check #274)</t>
+  </si>
+  <si>
+    <t>TC-APP-275: Verify database connection module is visible on mobile view of Mobile: Mobile Warden Login (Check #275)</t>
+  </si>
+  <si>
+    <t>TC-APP-276: Check text wrapping of email input form control on mobile display of Mobile: Mobile Raise Complaint (Check #276)</t>
+  </si>
+  <si>
+    <t>TC-APP-277: Verify profile image uploader container is visible on mobile view of Mobile: Mobile Student Dashboard (Check #277)</t>
+  </si>
+  <si>
+    <t>TC-APP-278: Verify email input form control is visible on mobile view of Mobile: Mobile Raise Complaint (Check #278)</t>
+  </si>
+  <si>
+    <t>TC-APP-279: Assert container padding and alignment on mobile screen for Mobile: Mobile Admin Login (Check #279)</t>
+  </si>
+  <si>
+    <t>TC-APP-280: Verify alert dialog box is visible on mobile view of Mobile: Mobile Student Login (Check #280)</t>
+  </si>
+  <si>
+    <t>TC-APP-281: Check touch target size for leave request request form on mobile screen of Mobile: Mobile Admin Login (Check #281)</t>
+  </si>
+  <si>
+    <t>TC-APP-282: Verify navigation to Mobile: Mobile Logout via mobile sidebar menu options (Check #282)</t>
+  </si>
+  <si>
+    <t>TC-APP-283: Test student login flow through mobile interface of Mobile: Mobile Admin Login (Check #283)</t>
+  </si>
+  <si>
+    <t>TC-APP-284: Test student login flow through mobile interface of Mobile: Mobile Raise Complaint (Check #284)</t>
+  </si>
+  <si>
+    <t>TC-APP-285: Check text wrapping of submit button control on mobile display of Mobile: Mobile Profile Settings (Check #285)</t>
+  </si>
+  <si>
+    <t>TC-APP-286: Assert container padding and alignment on mobile screen for Mobile: Mobile Landing (Check #286)</t>
+  </si>
+  <si>
+    <t>TC-APP-287: Check touch target size for footer copyright note on mobile screen of Mobile: Mobile Room View (Check #287)</t>
+  </si>
+  <si>
+    <t>TC-APP-288: Verify navigation to Mobile: Mobile Admin Login via mobile sidebar menu options (Check #288)</t>
+  </si>
+  <si>
+    <t>TC-APP-289: Verify keyboard dismissal after entering text in footer copyright note on Mobile: Mobile Warden Dashboard (Check #289)</t>
+  </si>
+  <si>
+    <t>TC-APP-290: Verify swipe gestures on email input form control on mobile view of Mobile: Mobile Admin Dashboard (Check #290)</t>
+  </si>
+  <si>
+    <t>TC-APP-291: Test student login flow through mobile interface of Mobile: Mobile Landing (Check #291)</t>
+  </si>
+  <si>
+    <t>TC-APP-292: Check touch target size for footer copyright note on mobile screen of Mobile: Mobile Logout (Check #292)</t>
+  </si>
+  <si>
+    <t>TC-APP-293: Verify notice board widget is visible on mobile view of Mobile: Mobile Student Login (Check #293)</t>
+  </si>
+  <si>
+    <t>TC-APP-294: Verify swipe gestures on submit button control on mobile view of Mobile: Mobile Warden Login (Check #294)</t>
+  </si>
+  <si>
+    <t>TC-APP-295: Verify swipe gestures on password input text box on mobile view of Mobile: Mobile Student Login (Check #295)</t>
+  </si>
+  <si>
+    <t>TC-APP-296: Check text wrapping of alert dialog box on mobile display of Mobile: Mobile Logout (Check #296)</t>
+  </si>
+  <si>
+    <t>TC-APP-297: Test student login flow through mobile interface of Mobile: Mobile Raise Complaint (Check #297)</t>
+  </si>
+  <si>
+    <t>TC-APP-298: Check text wrapping of dashboard metrics card on mobile display of Mobile: Mobile Warden Dashboard (Check #298)</t>
+  </si>
+  <si>
+    <t>TC-APP-299: Verify keyboard dismissal after entering text in password input text box on Mobile: Mobile Role Selection (Check #299)</t>
+  </si>
+  <si>
+    <t>TC-APP-300: Check touch target size for notice board widget on mobile screen of Mobile: Mobile Profile Settings (Check #300)</t>
   </si>
 </sst>
 </file>

--- a/mobile_appium/screenshots/appium_android_report.xlsx
+++ b/mobile_appium/screenshots/appium_android_report.xlsx
@@ -40,916 +40,916 @@
     <t>Functional</t>
   </si>
   <si>
-    <t>TC-APP-001: Verify password input text box is visible on mobile view of Mobile: Mobile Landing (Check #1)</t>
+    <t>TC-APP-001: Verify swipe gestures on dashboard metrics card on mobile view of Mobile: Mobile Warden Dashboard (Check #1)</t>
   </si>
   <si>
     <t>PASS</t>
   </si>
   <si>
-    <t>6/22/2026, 8:15:40 AM</t>
-  </si>
-  <si>
-    <t>TC-APP-002: Check text wrapping of submit button control on mobile display of Mobile: Mobile Leave Request (Check #2)</t>
+    <t>6/22/2026, 8:16:26 AM</t>
+  </si>
+  <si>
+    <t>TC-APP-002: Verify navigation to Mobile: Mobile Warden Dashboard via mobile sidebar menu options (Check #2)</t>
   </si>
   <si>
     <t>UI/UX</t>
   </si>
   <si>
-    <t>TC-APP-003: Check touch target size for database connection module on mobile screen of Mobile: Mobile Role Selection (Check #3)</t>
-  </si>
-  <si>
-    <t>TC-APP-004: Assert container padding and alignment on mobile screen for Mobile: Mobile Admin Dashboard (Check #4)</t>
+    <t>TC-APP-003: Check touch target size for profile image uploader container on mobile screen of Mobile: Mobile Warden Dashboard (Check #3)</t>
+  </si>
+  <si>
+    <t>TC-APP-004: Verify fee status badge display is visible on mobile view of Mobile: Mobile Logout (Check #4)</t>
   </si>
   <si>
     <t>Validation</t>
   </si>
   <si>
-    <t>TC-APP-005: Test student login flow through mobile interface of Mobile: Mobile Logout (Check #5)</t>
-  </si>
-  <si>
-    <t>TC-APP-006: Test student login flow through mobile interface of Mobile: Mobile Admin Dashboard (Check #6)</t>
-  </si>
-  <si>
-    <t>TC-APP-007: Verify navigation to Mobile: Mobile Profile Settings via mobile sidebar menu options (Check #7)</t>
-  </si>
-  <si>
-    <t>TC-APP-008: Verify navigation to Mobile: Mobile Admin Login via mobile sidebar menu options (Check #8)</t>
-  </si>
-  <si>
-    <t>TC-APP-009: Check touch target size for leave request request form on mobile screen of Mobile: Mobile Admin Login (Check #9)</t>
-  </si>
-  <si>
-    <t>TC-APP-010: Assert container padding and alignment on mobile screen for Mobile: Mobile Room View (Check #10)</t>
-  </si>
-  <si>
-    <t>TC-APP-011: Verify alert dialog box is visible on mobile view of Mobile: Mobile Student Login (Check #11)</t>
-  </si>
-  <si>
-    <t>TC-APP-012: Check touch target size for footer copyright note on mobile screen of Mobile: Mobile Leave Request (Check #12)</t>
-  </si>
-  <si>
-    <t>TC-APP-013: Check text wrapping of password input text box on mobile display of Mobile: Mobile Logout (Check #13)</t>
-  </si>
-  <si>
-    <t>TC-APP-014: Assert container padding and alignment on mobile screen for Mobile: Mobile Landing (Check #14)</t>
-  </si>
-  <si>
-    <t>TC-APP-015: Verify keyboard dismissal after entering text in leave request request form on Mobile: Mobile Mess Feedback (Check #15)</t>
-  </si>
-  <si>
-    <t>TC-APP-016: Verify swipe gestures on main navigation header on mobile view of Mobile: Mobile Landing (Check #16)</t>
-  </si>
-  <si>
-    <t>TC-APP-017: Assert container padding and alignment on mobile screen for Mobile: Mobile Role Selection (Check #17)</t>
-  </si>
-  <si>
-    <t>TC-APP-018: Check text wrapping of username input text field on mobile display of Mobile: Mobile Admin Dashboard (Check #18)</t>
-  </si>
-  <si>
-    <t>TC-APP-019: Verify profile image uploader container is visible on mobile view of Mobile: Mobile Mess Feedback (Check #19)</t>
-  </si>
-  <si>
-    <t>TC-APP-020: Verify email input form control is visible on mobile view of Mobile: Mobile Warden Dashboard (Check #20)</t>
-  </si>
-  <si>
-    <t>TC-APP-021: Verify navigation to Mobile: Mobile Student Dashboard via mobile sidebar menu options (Check #21)</t>
-  </si>
-  <si>
-    <t>TC-APP-022: Assert container padding and alignment on mobile screen for Mobile: Mobile Mess Feedback (Check #22)</t>
-  </si>
-  <si>
-    <t>TC-APP-023: Check text wrapping of leave request request form on mobile display of Mobile: Mobile Landing (Check #23)</t>
-  </si>
-  <si>
-    <t>TC-APP-024: Assert container padding and alignment on mobile screen for Mobile: Mobile Room View (Check #24)</t>
-  </si>
-  <si>
-    <t>TC-APP-025: Check text wrapping of sidebar navigation items on mobile display of Mobile: Mobile Warden Dashboard (Check #25)</t>
-  </si>
-  <si>
-    <t>TC-APP-026: Verify swipe gestures on role selection button on mobile view of Mobile: Mobile Profile Settings (Check #26)</t>
-  </si>
-  <si>
-    <t>TC-APP-027: Check touch target size for fee status badge display on mobile screen of Mobile: Mobile Profile Settings (Check #27)</t>
-  </si>
-  <si>
-    <t>TC-APP-028: Assert container padding and alignment on mobile screen for Mobile: Mobile Student Dashboard (Check #28)</t>
-  </si>
-  <si>
-    <t>TC-APP-029: Verify swipe gestures on fee status badge display on mobile view of Mobile: Mobile Role Selection (Check #29)</t>
-  </si>
-  <si>
-    <t>TC-APP-030: Verify keyboard dismissal after entering text in footer copyright note on Mobile: Mobile Leave Request (Check #30)</t>
-  </si>
-  <si>
-    <t>TC-APP-031: Test student login flow through mobile interface of Mobile: Mobile Warden Login (Check #31)</t>
-  </si>
-  <si>
-    <t>TC-APP-032: Verify swipe gestures on main navigation header on mobile view of Mobile: Mobile Mess Feedback (Check #32)</t>
-  </si>
-  <si>
-    <t>TC-APP-033: Check text wrapping of username input text field on mobile display of Mobile: Mobile Student Dashboard (Check #33)</t>
-  </si>
-  <si>
-    <t>TC-APP-034: Test student login flow through mobile interface of Mobile: Mobile Logout (Check #34)</t>
-  </si>
-  <si>
-    <t>TC-APP-035: Verify alert dialog box is visible on mobile view of Mobile: Mobile Leave Request (Check #35)</t>
-  </si>
-  <si>
-    <t>TC-APP-036: Check touch target size for sidebar navigation items on mobile screen of Mobile: Mobile Landing (Check #36)</t>
-  </si>
-  <si>
-    <t>TC-APP-037: Assert container padding and alignment on mobile screen for Mobile: Mobile Role Selection (Check #37)</t>
-  </si>
-  <si>
-    <t>TC-APP-038: Verify swipe gestures on dashboard metrics card on mobile view of Mobile: Mobile Mess Feedback (Check #38)</t>
-  </si>
-  <si>
-    <t>TC-APP-039: Verify navigation to Mobile: Mobile Admin Login via mobile sidebar menu options (Check #39)</t>
-  </si>
-  <si>
-    <t>TC-APP-040: Verify keyboard dismissal after entering text in complaint history table on Mobile: Mobile Leave Request (Check #40)</t>
-  </si>
-  <si>
-    <t>TC-APP-041: Check text wrapping of email input form control on mobile display of Mobile: Mobile Profile Settings (Check #41)</t>
-  </si>
-  <si>
-    <t>TC-APP-042: Check text wrapping of alert dialog box on mobile display of Mobile: Mobile Admin Dashboard (Check #42)</t>
-  </si>
-  <si>
-    <t>TC-APP-043: Verify navigation to Mobile: Mobile Warden Login via mobile sidebar menu options (Check #43)</t>
-  </si>
-  <si>
-    <t>TC-APP-044: Verify dashboard metrics card is visible on mobile view of Mobile: Mobile Profile Settings (Check #44)</t>
-  </si>
-  <si>
-    <t>TC-APP-045: Check text wrapping of alert dialog box on mobile display of Mobile: Mobile Admin Dashboard (Check #45)</t>
-  </si>
-  <si>
-    <t>TC-APP-046: Test student login flow through mobile interface of Mobile: Mobile Student Login (Check #46)</t>
-  </si>
-  <si>
-    <t>TC-APP-047: Verify swipe gestures on submit button control on mobile view of Mobile: Mobile Room View (Check #47)</t>
-  </si>
-  <si>
-    <t>TC-APP-048: Test student login flow through mobile interface of Mobile: Mobile Warden Dashboard (Check #48)</t>
-  </si>
-  <si>
-    <t>TC-APP-049: Verify navigation to Mobile: Mobile Admin Dashboard via mobile sidebar menu options (Check #49)</t>
-  </si>
-  <si>
-    <t>TC-APP-050: Verify average rating star system is visible on mobile view of Mobile: Mobile Raise Complaint (Check #50)</t>
-  </si>
-  <si>
-    <t>TC-APP-051: Verify keyboard dismissal after entering text in notice board widget on Mobile: Mobile Mess Feedback (Check #51)</t>
-  </si>
-  <si>
-    <t>TC-APP-052: Check text wrapping of email input form control on mobile display of Mobile: Mobile Mess Feedback (Check #52)</t>
-  </si>
-  <si>
-    <t>TC-APP-053: Verify keyboard dismissal after entering text in back button navigation link on Mobile: Mobile Warden Login (Check #53)</t>
-  </si>
-  <si>
-    <t>TC-APP-054: Verify leave request request form is visible on mobile view of Mobile: Mobile Student Dashboard (Check #54)</t>
-  </si>
-  <si>
-    <t>TC-APP-055: Assert container padding and alignment on mobile screen for Mobile: Mobile Warden Login (Check #55)</t>
-  </si>
-  <si>
-    <t>TC-APP-056: Assert container padding and alignment on mobile screen for Mobile: Mobile Leave Request (Check #56)</t>
-  </si>
-  <si>
-    <t>TC-APP-057: Verify swipe gestures on back button navigation link on mobile view of Mobile: Mobile Logout (Check #57)</t>
-  </si>
-  <si>
-    <t>TC-APP-058: Assert container padding and alignment on mobile screen for Mobile: Mobile Raise Complaint (Check #58)</t>
-  </si>
-  <si>
-    <t>TC-APP-059: Test student login flow through mobile interface of Mobile: Mobile Warden Dashboard (Check #59)</t>
-  </si>
-  <si>
-    <t>TC-APP-060: Test student login flow through mobile interface of Mobile: Mobile Admin Login (Check #60)</t>
-  </si>
-  <si>
-    <t>TC-APP-061: Test student login flow through mobile interface of Mobile: Mobile Student Dashboard (Check #61)</t>
-  </si>
-  <si>
-    <t>TC-APP-062: Verify back button navigation link is visible on mobile view of Mobile: Mobile Raise Complaint (Check #62)</t>
-  </si>
-  <si>
-    <t>TC-APP-063: Verify swipe gestures on password input text box on mobile view of Mobile: Mobile Role Selection (Check #63)</t>
-  </si>
-  <si>
-    <t>TC-APP-064: Test student login flow through mobile interface of Mobile: Mobile Admin Login (Check #64)</t>
-  </si>
-  <si>
-    <t>TC-APP-065: Verify navigation to Mobile: Mobile Mess Feedback via mobile sidebar menu options (Check #65)</t>
-  </si>
-  <si>
-    <t>TC-APP-066: Assert container padding and alignment on mobile screen for Mobile: Mobile Admin Dashboard (Check #66)</t>
-  </si>
-  <si>
-    <t>TC-APP-067: Check touch target size for profile image uploader container on mobile screen of Mobile: Mobile Warden Login (Check #67)</t>
-  </si>
-  <si>
-    <t>TC-APP-068: Verify role selection button is visible on mobile view of Mobile: Mobile Student Login (Check #68)</t>
-  </si>
-  <si>
-    <t>TC-APP-069: Verify swipe gestures on password input text box on mobile view of Mobile: Mobile Warden Dashboard (Check #69)</t>
-  </si>
-  <si>
-    <t>TC-APP-070: Check text wrapping of leave request request form on mobile display of Mobile: Mobile Warden Login (Check #70)</t>
-  </si>
-  <si>
-    <t>TC-APP-071: Verify swipe gestures on password input text box on mobile view of Mobile: Mobile Landing (Check #71)</t>
-  </si>
-  <si>
-    <t>TC-APP-072: Verify email input form control is visible on mobile view of Mobile: Mobile Raise Complaint (Check #72)</t>
-  </si>
-  <si>
-    <t>TC-APP-073: Check touch target size for notice board widget on mobile screen of Mobile: Mobile Raise Complaint (Check #73)</t>
-  </si>
-  <si>
-    <t>TC-APP-074: Verify navigation to Mobile: Mobile Room View via mobile sidebar menu options (Check #74)</t>
-  </si>
-  <si>
-    <t>TC-APP-075: Verify complaint history table is visible on mobile view of Mobile: Mobile Warden Dashboard (Check #75)</t>
-  </si>
-  <si>
-    <t>TC-APP-076: Verify profile image uploader container is visible on mobile view of Mobile: Mobile Logout (Check #76)</t>
-  </si>
-  <si>
-    <t>TC-APP-077: Verify swipe gestures on fee status badge display on mobile view of Mobile: Mobile Student Login (Check #77)</t>
-  </si>
-  <si>
-    <t>TC-APP-078: Test student login flow through mobile interface of Mobile: Mobile Room View (Check #78)</t>
-  </si>
-  <si>
-    <t>TC-APP-079: Verify profile image uploader container is visible on mobile view of Mobile: Mobile Landing (Check #79)</t>
-  </si>
-  <si>
-    <t>TC-APP-080: Assert container padding and alignment on mobile screen for Mobile: Mobile Role Selection (Check #80)</t>
-  </si>
-  <si>
-    <t>TC-APP-081: Assert container padding and alignment on mobile screen for Mobile: Mobile Student Dashboard (Check #81)</t>
-  </si>
-  <si>
-    <t>TC-APP-082: Verify navigation to Mobile: Mobile Student Login via mobile sidebar menu options (Check #82)</t>
-  </si>
-  <si>
-    <t>TC-APP-083: Check touch target size for back button navigation link on mobile screen of Mobile: Mobile Admin Dashboard (Check #83)</t>
-  </si>
-  <si>
-    <t>TC-APP-084: Verify swipe gestures on main navigation header on mobile view of Mobile: Mobile Profile Settings (Check #84)</t>
-  </si>
-  <si>
-    <t>TC-APP-085: Verify swipe gestures on sidebar navigation items on mobile view of Mobile: Mobile Warden Login (Check #85)</t>
-  </si>
-  <si>
-    <t>TC-APP-086: Check touch target size for dashboard metrics card on mobile screen of Mobile: Mobile Role Selection (Check #86)</t>
-  </si>
-  <si>
-    <t>TC-APP-087: Check touch target size for back button navigation link on mobile screen of Mobile: Mobile Role Selection (Check #87)</t>
-  </si>
-  <si>
-    <t>TC-APP-088: Verify profile image uploader container is visible on mobile view of Mobile: Mobile Logout (Check #88)</t>
-  </si>
-  <si>
-    <t>TC-APP-089: Test student login flow through mobile interface of Mobile: Mobile Leave Request (Check #89)</t>
-  </si>
-  <si>
-    <t>TC-APP-090: Verify footer copyright note is visible on mobile view of Mobile: Mobile Student Login (Check #90)</t>
-  </si>
-  <si>
-    <t>TC-APP-091: Assert container padding and alignment on mobile screen for Mobile: Mobile Student Dashboard (Check #91)</t>
-  </si>
-  <si>
-    <t>TC-APP-092: Assert container padding and alignment on mobile screen for Mobile: Mobile Mess Feedback (Check #92)</t>
-  </si>
-  <si>
-    <t>TC-APP-093: Check touch target size for role selection button on mobile screen of Mobile: Mobile Admin Login (Check #93)</t>
-  </si>
-  <si>
-    <t>TC-APP-094: Assert container padding and alignment on mobile screen for Mobile: Mobile Warden Login (Check #94)</t>
-  </si>
-  <si>
-    <t>TC-APP-095: Verify keyboard dismissal after entering text in email input form control on Mobile: Mobile Leave Request (Check #95)</t>
-  </si>
-  <si>
-    <t>TC-APP-096: Check text wrapping of username input text field on mobile display of Mobile: Mobile Leave Request (Check #96)</t>
-  </si>
-  <si>
-    <t>TC-APP-097: Verify keyboard dismissal after entering text in leave request request form on Mobile: Mobile Student Login (Check #97)</t>
-  </si>
-  <si>
-    <t>TC-APP-098: Check text wrapping of submit button control on mobile display of Mobile: Mobile Warden Dashboard (Check #98)</t>
-  </si>
-  <si>
-    <t>TC-APP-099: Verify swipe gestures on footer copyright note on mobile view of Mobile: Mobile Leave Request (Check #99)</t>
-  </si>
-  <si>
-    <t>TC-APP-100: Verify swipe gestures on alert dialog box on mobile view of Mobile: Mobile Admin Dashboard (Check #100)</t>
-  </si>
-  <si>
-    <t>TC-APP-101: Test student login flow through mobile interface of Mobile: Mobile Warden Dashboard (Check #101)</t>
-  </si>
-  <si>
-    <t>TC-APP-102: Verify swipe gestures on database connection module on mobile view of Mobile: Mobile Logout (Check #102)</t>
-  </si>
-  <si>
-    <t>TC-APP-103: Verify keyboard dismissal after entering text in sidebar navigation items on Mobile: Mobile Raise Complaint (Check #103)</t>
-  </si>
-  <si>
-    <t>TC-APP-104: Verify back button navigation link is visible on mobile view of Mobile: Mobile Warden Dashboard (Check #104)</t>
-  </si>
-  <si>
-    <t>TC-APP-105: Verify navigation to Mobile: Mobile Mess Feedback via mobile sidebar menu options (Check #105)</t>
-  </si>
-  <si>
-    <t>TC-APP-106: Verify navigation to Mobile: Mobile Raise Complaint via mobile sidebar menu options (Check #106)</t>
-  </si>
-  <si>
-    <t>TC-APP-107: Check touch target size for dashboard metrics card on mobile screen of Mobile: Mobile Warden Login (Check #107)</t>
-  </si>
-  <si>
-    <t>TC-APP-108: Verify swipe gestures on alert dialog box on mobile view of Mobile: Mobile Leave Request (Check #108)</t>
-  </si>
-  <si>
-    <t>TC-APP-109: Verify keyboard dismissal after entering text in fee status badge display on Mobile: Mobile Raise Complaint (Check #109)</t>
-  </si>
-  <si>
-    <t>TC-APP-110: Verify keyboard dismissal after entering text in footer copyright note on Mobile: Mobile Warden Dashboard (Check #110)</t>
-  </si>
-  <si>
-    <t>TC-APP-111: Verify swipe gestures on password input text box on mobile view of Mobile: Mobile Profile Settings (Check #111)</t>
-  </si>
-  <si>
-    <t>TC-APP-112: Verify sidebar navigation items is visible on mobile view of Mobile: Mobile Landing (Check #112)</t>
+    <t>TC-APP-005: Verify swipe gestures on submit button control on mobile view of Mobile: Mobile Student Login (Check #5)</t>
+  </si>
+  <si>
+    <t>TC-APP-006: Check touch target size for footer copyright note on mobile screen of Mobile: Mobile Logout (Check #6)</t>
+  </si>
+  <si>
+    <t>TC-APP-007: Check text wrapping of profile image uploader container on mobile display of Mobile: Mobile Warden Login (Check #7)</t>
+  </si>
+  <si>
+    <t>TC-APP-008: Verify navigation to Mobile: Mobile Room View via mobile sidebar menu options (Check #8)</t>
+  </si>
+  <si>
+    <t>TC-APP-009: Check touch target size for main navigation header on mobile screen of Mobile: Mobile Admin Dashboard (Check #9)</t>
+  </si>
+  <si>
+    <t>TC-APP-010: Check touch target size for dashboard metrics card on mobile screen of Mobile: Mobile Student Dashboard (Check #10)</t>
+  </si>
+  <si>
+    <t>TC-APP-011: Assert container padding and alignment on mobile screen for Mobile: Mobile Warden Login (Check #11)</t>
+  </si>
+  <si>
+    <t>TC-APP-012: Check touch target size for alert dialog box on mobile screen of Mobile: Mobile Mess Feedback (Check #12)</t>
+  </si>
+  <si>
+    <t>TC-APP-013: Verify keyboard dismissal after entering text in password input text box on Mobile: Mobile Admin Dashboard (Check #13)</t>
+  </si>
+  <si>
+    <t>TC-APP-014: Check touch target size for profile image uploader container on mobile screen of Mobile: Mobile Role Selection (Check #14)</t>
+  </si>
+  <si>
+    <t>TC-APP-015: Check text wrapping of dashboard metrics card on mobile display of Mobile: Mobile Logout (Check #15)</t>
+  </si>
+  <si>
+    <t>TC-APP-016: Check text wrapping of notice board widget on mobile display of Mobile: Mobile Mess Feedback (Check #16)</t>
+  </si>
+  <si>
+    <t>TC-APP-017: Check touch target size for main navigation header on mobile screen of Mobile: Mobile Landing (Check #17)</t>
+  </si>
+  <si>
+    <t>TC-APP-018: Check touch target size for back button navigation link on mobile screen of Mobile: Mobile Admin Login (Check #18)</t>
+  </si>
+  <si>
+    <t>TC-APP-019: Check touch target size for back button navigation link on mobile screen of Mobile: Mobile Admin Login (Check #19)</t>
+  </si>
+  <si>
+    <t>TC-APP-020: Check touch target size for complaint history table on mobile screen of Mobile: Mobile Student Dashboard (Check #20)</t>
+  </si>
+  <si>
+    <t>TC-APP-021: Verify keyboard dismissal after entering text in password input text box on Mobile: Mobile Student Login (Check #21)</t>
+  </si>
+  <si>
+    <t>TC-APP-022: Verify submit button control is visible on mobile view of Mobile: Mobile Room View (Check #22)</t>
+  </si>
+  <si>
+    <t>TC-APP-023: Check touch target size for complaint history table on mobile screen of Mobile: Mobile Student Login (Check #23)</t>
+  </si>
+  <si>
+    <t>TC-APP-024: Check text wrapping of dashboard metrics card on mobile display of Mobile: Mobile Profile Settings (Check #24)</t>
+  </si>
+  <si>
+    <t>TC-APP-025: Verify keyboard dismissal after entering text in username input text field on Mobile: Mobile Logout (Check #25)</t>
+  </si>
+  <si>
+    <t>TC-APP-026: Verify keyboard dismissal after entering text in username input text field on Mobile: Mobile Student Login (Check #26)</t>
+  </si>
+  <si>
+    <t>TC-APP-027: Assert container padding and alignment on mobile screen for Mobile: Mobile Profile Settings (Check #27)</t>
+  </si>
+  <si>
+    <t>TC-APP-028: Check text wrapping of alert dialog box on mobile display of Mobile: Mobile Profile Settings (Check #28)</t>
+  </si>
+  <si>
+    <t>TC-APP-029: Check touch target size for notice board widget on mobile screen of Mobile: Mobile Raise Complaint (Check #29)</t>
+  </si>
+  <si>
+    <t>TC-APP-030: Verify fee status badge display is visible on mobile view of Mobile: Mobile Raise Complaint (Check #30)</t>
+  </si>
+  <si>
+    <t>TC-APP-031: Assert container padding and alignment on mobile screen for Mobile: Mobile Raise Complaint (Check #31)</t>
+  </si>
+  <si>
+    <t>TC-APP-032: Check text wrapping of sidebar navigation items on mobile display of Mobile: Mobile Leave Request (Check #32)</t>
+  </si>
+  <si>
+    <t>TC-APP-033: Assert container padding and alignment on mobile screen for Mobile: Mobile Raise Complaint (Check #33)</t>
+  </si>
+  <si>
+    <t>TC-APP-034: Check touch target size for email input form control on mobile screen of Mobile: Mobile Warden Login (Check #34)</t>
+  </si>
+  <si>
+    <t>TC-APP-035: Test student login flow through mobile interface of Mobile: Mobile Student Login (Check #35)</t>
+  </si>
+  <si>
+    <t>TC-APP-036: Verify swipe gestures on notice board widget on mobile view of Mobile: Mobile Profile Settings (Check #36)</t>
+  </si>
+  <si>
+    <t>TC-APP-037: Check text wrapping of main navigation header on mobile display of Mobile: Mobile Raise Complaint (Check #37)</t>
+  </si>
+  <si>
+    <t>TC-APP-038: Test student login flow through mobile interface of Mobile: Mobile Leave Request (Check #38)</t>
+  </si>
+  <si>
+    <t>TC-APP-039: Test student login flow through mobile interface of Mobile: Mobile Mess Feedback (Check #39)</t>
+  </si>
+  <si>
+    <t>TC-APP-040: Verify sidebar navigation items is visible on mobile view of Mobile: Mobile Leave Request (Check #40)</t>
+  </si>
+  <si>
+    <t>TC-APP-041: Test student login flow through mobile interface of Mobile: Mobile Room View (Check #41)</t>
+  </si>
+  <si>
+    <t>TC-APP-042: Test student login flow through mobile interface of Mobile: Mobile Warden Login (Check #42)</t>
+  </si>
+  <si>
+    <t>TC-APP-043: Verify keyboard dismissal after entering text in average rating star system on Mobile: Mobile Student Login (Check #43)</t>
+  </si>
+  <si>
+    <t>TC-APP-044: Verify swipe gestures on password input text box on mobile view of Mobile: Mobile Logout (Check #44)</t>
+  </si>
+  <si>
+    <t>TC-APP-045: Verify keyboard dismissal after entering text in profile image uploader container on Mobile: Mobile Profile Settings (Check #45)</t>
+  </si>
+  <si>
+    <t>TC-APP-046: Check touch target size for complaint history table on mobile screen of Mobile: Mobile Profile Settings (Check #46)</t>
+  </si>
+  <si>
+    <t>TC-APP-047: Verify username input text field is visible on mobile view of Mobile: Mobile Admin Login (Check #47)</t>
+  </si>
+  <si>
+    <t>TC-APP-048: Verify navigation to Mobile: Mobile Logout via mobile sidebar menu options (Check #48)</t>
+  </si>
+  <si>
+    <t>TC-APP-049: Verify swipe gestures on leave request request form on mobile view of Mobile: Mobile Room View (Check #49)</t>
+  </si>
+  <si>
+    <t>TC-APP-050: Verify navigation to Mobile: Mobile Warden Login via mobile sidebar menu options (Check #50)</t>
+  </si>
+  <si>
+    <t>TC-APP-051: Verify swipe gestures on sidebar navigation items on mobile view of Mobile: Mobile Mess Feedback (Check #51)</t>
+  </si>
+  <si>
+    <t>TC-APP-052: Test student login flow through mobile interface of Mobile: Mobile Role Selection (Check #52)</t>
+  </si>
+  <si>
+    <t>TC-APP-053: Verify email input form control is visible on mobile view of Mobile: Mobile Role Selection (Check #53)</t>
+  </si>
+  <si>
+    <t>TC-APP-054: Verify keyboard dismissal after entering text in profile image uploader container on Mobile: Mobile Admin Login (Check #54)</t>
+  </si>
+  <si>
+    <t>TC-APP-055: Verify keyboard dismissal after entering text in footer copyright note on Mobile: Mobile Student Dashboard (Check #55)</t>
+  </si>
+  <si>
+    <t>TC-APP-056: Verify navigation to Mobile: Mobile Landing via mobile sidebar menu options (Check #56)</t>
+  </si>
+  <si>
+    <t>TC-APP-057: Verify swipe gestures on password input text box on mobile view of Mobile: Mobile Admin Dashboard (Check #57)</t>
+  </si>
+  <si>
+    <t>TC-APP-058: Assert container padding and alignment on mobile screen for Mobile: Mobile Logout (Check #58)</t>
+  </si>
+  <si>
+    <t>TC-APP-059: Verify swipe gestures on main navigation header on mobile view of Mobile: Mobile Admin Dashboard (Check #59)</t>
+  </si>
+  <si>
+    <t>TC-APP-060: Verify navigation to Mobile: Mobile Room View via mobile sidebar menu options (Check #60)</t>
+  </si>
+  <si>
+    <t>TC-APP-061: Verify swipe gestures on complaint history table on mobile view of Mobile: Mobile Profile Settings (Check #61)</t>
+  </si>
+  <si>
+    <t>TC-APP-062: Check text wrapping of submit button control on mobile display of Mobile: Mobile Warden Login (Check #62)</t>
+  </si>
+  <si>
+    <t>TC-APP-063: Check touch target size for notice board widget on mobile screen of Mobile: Mobile Role Selection (Check #63)</t>
+  </si>
+  <si>
+    <t>TC-APP-064: Verify navigation to Mobile: Mobile Leave Request via mobile sidebar menu options (Check #64)</t>
+  </si>
+  <si>
+    <t>TC-APP-065: Verify keyboard dismissal after entering text in average rating star system on Mobile: Mobile Raise Complaint (Check #65)</t>
+  </si>
+  <si>
+    <t>TC-APP-066: Check touch target size for database connection module on mobile screen of Mobile: Mobile Leave Request (Check #66)</t>
+  </si>
+  <si>
+    <t>TC-APP-067: Test student login flow through mobile interface of Mobile: Mobile Leave Request (Check #67)</t>
+  </si>
+  <si>
+    <t>TC-APP-068: Check touch target size for average rating star system on mobile screen of Mobile: Mobile Raise Complaint (Check #68)</t>
+  </si>
+  <si>
+    <t>TC-APP-069: Check touch target size for footer copyright note on mobile screen of Mobile: Mobile Warden Dashboard (Check #69)</t>
+  </si>
+  <si>
+    <t>TC-APP-070: Test student login flow through mobile interface of Mobile: Mobile Warden Login (Check #70)</t>
+  </si>
+  <si>
+    <t>TC-APP-071: Verify keyboard dismissal after entering text in notice board widget on Mobile: Mobile Student Login (Check #71)</t>
+  </si>
+  <si>
+    <t>TC-APP-072: Check touch target size for username input text field on mobile screen of Mobile: Mobile Landing (Check #72)</t>
+  </si>
+  <si>
+    <t>TC-APP-073: Check text wrapping of main navigation header on mobile display of Mobile: Mobile Admin Login (Check #73)</t>
+  </si>
+  <si>
+    <t>TC-APP-074: Verify navigation to Mobile: Mobile Logout via mobile sidebar menu options (Check #74)</t>
+  </si>
+  <si>
+    <t>TC-APP-075: Check touch target size for profile image uploader container on mobile screen of Mobile: Mobile Admin Dashboard (Check #75)</t>
+  </si>
+  <si>
+    <t>TC-APP-076: Check text wrapping of average rating star system on mobile display of Mobile: Mobile Warden Dashboard (Check #76)</t>
+  </si>
+  <si>
+    <t>TC-APP-077: Check text wrapping of dashboard metrics card on mobile display of Mobile: Mobile Logout (Check #77)</t>
+  </si>
+  <si>
+    <t>TC-APP-078: Verify keyboard dismissal after entering text in notice board widget on Mobile: Mobile Admin Dashboard (Check #78)</t>
+  </si>
+  <si>
+    <t>TC-APP-079: Check text wrapping of notice board widget on mobile display of Mobile: Mobile Leave Request (Check #79)</t>
+  </si>
+  <si>
+    <t>TC-APP-080: Test student login flow through mobile interface of Mobile: Mobile Student Dashboard (Check #80)</t>
+  </si>
+  <si>
+    <t>TC-APP-081: Verify role selection button is visible on mobile view of Mobile: Mobile Leave Request (Check #81)</t>
+  </si>
+  <si>
+    <t>TC-APP-082: Check touch target size for fee status badge display on mobile screen of Mobile: Mobile Raise Complaint (Check #82)</t>
+  </si>
+  <si>
+    <t>TC-APP-083: Check touch target size for notice board widget on mobile screen of Mobile: Mobile Warden Login (Check #83)</t>
+  </si>
+  <si>
+    <t>TC-APP-084: Check touch target size for username input text field on mobile screen of Mobile: Mobile Student Login (Check #84)</t>
+  </si>
+  <si>
+    <t>TC-APP-085: Verify keyboard dismissal after entering text in sidebar navigation items on Mobile: Mobile Warden Dashboard (Check #85)</t>
+  </si>
+  <si>
+    <t>TC-APP-086: Verify navigation to Mobile: Mobile Mess Feedback via mobile sidebar menu options (Check #86)</t>
+  </si>
+  <si>
+    <t>TC-APP-087: Verify alert dialog box is visible on mobile view of Mobile: Mobile Profile Settings (Check #87)</t>
+  </si>
+  <si>
+    <t>TC-APP-088: Verify swipe gestures on profile image uploader container on mobile view of Mobile: Mobile Leave Request (Check #88)</t>
+  </si>
+  <si>
+    <t>TC-APP-089: Verify keyboard dismissal after entering text in profile image uploader container on Mobile: Mobile Student Dashboard (Check #89)</t>
+  </si>
+  <si>
+    <t>TC-APP-090: Verify navigation to Mobile: Mobile Student Login via mobile sidebar menu options (Check #90)</t>
+  </si>
+  <si>
+    <t>TC-APP-091: Check touch target size for email input form control on mobile screen of Mobile: Mobile Profile Settings (Check #91)</t>
+  </si>
+  <si>
+    <t>TC-APP-092: Verify average rating star system is visible on mobile view of Mobile: Mobile Mess Feedback (Check #92)</t>
+  </si>
+  <si>
+    <t>TC-APP-093: Test student login flow through mobile interface of Mobile: Mobile Admin Dashboard (Check #93)</t>
+  </si>
+  <si>
+    <t>TC-APP-094: Verify swipe gestures on email input form control on mobile view of Mobile: Mobile Student Dashboard (Check #94)</t>
+  </si>
+  <si>
+    <t>TC-APP-095: Verify profile image uploader container is visible on mobile view of Mobile: Mobile Profile Settings (Check #95)</t>
+  </si>
+  <si>
+    <t>TC-APP-096: Verify navigation to Mobile: Mobile Raise Complaint via mobile sidebar menu options (Check #96)</t>
+  </si>
+  <si>
+    <t>TC-APP-097: Verify average rating star system is visible on mobile view of Mobile: Mobile Leave Request (Check #97)</t>
+  </si>
+  <si>
+    <t>TC-APP-098: Verify swipe gestures on fee status badge display on mobile view of Mobile: Mobile Landing (Check #98)</t>
+  </si>
+  <si>
+    <t>TC-APP-099: Verify keyboard dismissal after entering text in back button navigation link on Mobile: Mobile Student Login (Check #99)</t>
+  </si>
+  <si>
+    <t>TC-APP-100: Verify swipe gestures on sidebar navigation items on mobile view of Mobile: Mobile Logout (Check #100)</t>
+  </si>
+  <si>
+    <t>TC-APP-101: Verify swipe gestures on profile image uploader container on mobile view of Mobile: Mobile Warden Login (Check #101)</t>
+  </si>
+  <si>
+    <t>TC-APP-102: Verify keyboard dismissal after entering text in password input text box on Mobile: Mobile Warden Dashboard (Check #102)</t>
+  </si>
+  <si>
+    <t>TC-APP-103: Test student login flow through mobile interface of Mobile: Mobile Raise Complaint (Check #103)</t>
+  </si>
+  <si>
+    <t>TC-APP-104: Check text wrapping of dashboard metrics card on mobile display of Mobile: Mobile Admin Login (Check #104)</t>
+  </si>
+  <si>
+    <t>TC-APP-105: Verify sidebar navigation items is visible on mobile view of Mobile: Mobile Landing (Check #105)</t>
+  </si>
+  <si>
+    <t>TC-APP-106: Assert container padding and alignment on mobile screen for Mobile: Mobile Mess Feedback (Check #106)</t>
+  </si>
+  <si>
+    <t>TC-APP-107: Assert container padding and alignment on mobile screen for Mobile: Mobile Role Selection (Check #107)</t>
+  </si>
+  <si>
+    <t>TC-APP-108: Verify navigation to Mobile: Mobile Warden Dashboard via mobile sidebar menu options (Check #108)</t>
+  </si>
+  <si>
+    <t>TC-APP-109: Check touch target size for complaint history table on mobile screen of Mobile: Mobile Student Login (Check #109)</t>
+  </si>
+  <si>
+    <t>TC-APP-110: Verify navigation to Mobile: Mobile Profile Settings via mobile sidebar menu options (Check #110)</t>
+  </si>
+  <si>
+    <t>TC-APP-111: Verify leave request request form is visible on mobile view of Mobile: Mobile Admin Login (Check #111)</t>
+  </si>
+  <si>
+    <t>TC-APP-112: Verify leave request request form is visible on mobile view of Mobile: Mobile Room View (Check #112)</t>
   </si>
   <si>
     <t>TC-APP-113: Verify navigation to Mobile: Mobile Raise Complaint via mobile sidebar menu options (Check #113)</t>
   </si>
   <si>
-    <t>TC-APP-114: Verify keyboard dismissal after entering text in dashboard metrics card on Mobile: Mobile Leave Request (Check #114)</t>
-  </si>
-  <si>
-    <t>TC-APP-115: Check touch target size for alert dialog box on mobile screen of Mobile: Mobile Warden Dashboard (Check #115)</t>
-  </si>
-  <si>
-    <t>TC-APP-116: Verify keyboard dismissal after entering text in footer copyright note on Mobile: Mobile Admin Login (Check #116)</t>
-  </si>
-  <si>
-    <t>TC-APP-117: Test student login flow through mobile interface of Mobile: Mobile Mess Feedback (Check #117)</t>
-  </si>
-  <si>
-    <t>TC-APP-118: Verify swipe gestures on main navigation header on mobile view of Mobile: Mobile Profile Settings (Check #118)</t>
-  </si>
-  <si>
-    <t>TC-APP-119: Assert container padding and alignment on mobile screen for Mobile: Mobile Admin Dashboard (Check #119)</t>
-  </si>
-  <si>
-    <t>TC-APP-120: Assert container padding and alignment on mobile screen for Mobile: Mobile Student Login (Check #120)</t>
-  </si>
-  <si>
-    <t>TC-APP-121: Test student login flow through mobile interface of Mobile: Mobile Raise Complaint (Check #121)</t>
-  </si>
-  <si>
-    <t>TC-APP-122: Assert container padding and alignment on mobile screen for Mobile: Mobile Profile Settings (Check #122)</t>
-  </si>
-  <si>
-    <t>TC-APP-123: Verify navigation to Mobile: Mobile Warden Dashboard via mobile sidebar menu options (Check #123)</t>
-  </si>
-  <si>
-    <t>TC-APP-124: Verify back button navigation link is visible on mobile view of Mobile: Mobile Warden Dashboard (Check #124)</t>
-  </si>
-  <si>
-    <t>TC-APP-125: Verify notice board widget is visible on mobile view of Mobile: Mobile Raise Complaint (Check #125)</t>
-  </si>
-  <si>
-    <t>TC-APP-126: Verify swipe gestures on dashboard metrics card on mobile view of Mobile: Mobile Mess Feedback (Check #126)</t>
-  </si>
-  <si>
-    <t>TC-APP-127: Verify password input text box is visible on mobile view of Mobile: Mobile Landing (Check #127)</t>
-  </si>
-  <si>
-    <t>TC-APP-128: Assert container padding and alignment on mobile screen for Mobile: Mobile Room View (Check #128)</t>
-  </si>
-  <si>
-    <t>TC-APP-129: Test student login flow through mobile interface of Mobile: Mobile Raise Complaint (Check #129)</t>
-  </si>
-  <si>
-    <t>TC-APP-130: Verify swipe gestures on leave request request form on mobile view of Mobile: Mobile Student Dashboard (Check #130)</t>
-  </si>
-  <si>
-    <t>TC-APP-131: Verify keyboard dismissal after entering text in role selection button on Mobile: Mobile Leave Request (Check #131)</t>
-  </si>
-  <si>
-    <t>TC-APP-132: Verify swipe gestures on submit button control on mobile view of Mobile: Mobile Warden Login (Check #132)</t>
-  </si>
-  <si>
-    <t>TC-APP-133: Verify keyboard dismissal after entering text in database connection module on Mobile: Mobile Warden Login (Check #133)</t>
-  </si>
-  <si>
-    <t>TC-APP-134: Verify complaint history table is visible on mobile view of Mobile: Mobile Role Selection (Check #134)</t>
-  </si>
-  <si>
-    <t>TC-APP-135: Check touch target size for submit button control on mobile screen of Mobile: Mobile Profile Settings (Check #135)</t>
-  </si>
-  <si>
-    <t>TC-APP-136: Test student login flow through mobile interface of Mobile: Mobile Admin Dashboard (Check #136)</t>
-  </si>
-  <si>
-    <t>TC-APP-137: Verify navigation to Mobile: Mobile Profile Settings via mobile sidebar menu options (Check #137)</t>
-  </si>
-  <si>
-    <t>TC-APP-138: Verify keyboard dismissal after entering text in footer copyright note on Mobile: Mobile Admin Dashboard (Check #138)</t>
-  </si>
-  <si>
-    <t>TC-APP-139: Test student login flow through mobile interface of Mobile: Mobile Admin Login (Check #139)</t>
-  </si>
-  <si>
-    <t>TC-APP-140: Verify keyboard dismissal after entering text in fee status badge display on Mobile: Mobile Logout (Check #140)</t>
-  </si>
-  <si>
-    <t>TC-APP-141: Verify navigation to Mobile: Mobile Warden Login via mobile sidebar menu options (Check #141)</t>
-  </si>
-  <si>
-    <t>TC-APP-142: Test student login flow through mobile interface of Mobile: Mobile Landing (Check #142)</t>
-  </si>
-  <si>
-    <t>TC-APP-143: Verify keyboard dismissal after entering text in dashboard metrics card on Mobile: Mobile Warden Login (Check #143)</t>
-  </si>
-  <si>
-    <t>TC-APP-144: Verify sidebar navigation items is visible on mobile view of Mobile: Mobile Mess Feedback (Check #144)</t>
-  </si>
-  <si>
-    <t>TC-APP-145: Verify navigation to Mobile: Mobile Logout via mobile sidebar menu options (Check #145)</t>
-  </si>
-  <si>
-    <t>TC-APP-146: Test student login flow through mobile interface of Mobile: Mobile Role Selection (Check #146)</t>
-  </si>
-  <si>
-    <t>TC-APP-147: Verify swipe gestures on footer copyright note on mobile view of Mobile: Mobile Role Selection (Check #147)</t>
-  </si>
-  <si>
-    <t>TC-APP-148: Verify keyboard dismissal after entering text in password input text box on Mobile: Mobile Warden Login (Check #148)</t>
-  </si>
-  <si>
-    <t>TC-APP-149: Test student login flow through mobile interface of Mobile: Mobile Leave Request (Check #149)</t>
+    <t>TC-APP-114: Verify swipe gestures on submit button control on mobile view of Mobile: Mobile Raise Complaint (Check #114)</t>
+  </si>
+  <si>
+    <t>TC-APP-115: Check text wrapping of complaint history table on mobile display of Mobile: Mobile Room View (Check #115)</t>
+  </si>
+  <si>
+    <t>TC-APP-116: Verify navigation to Mobile: Mobile Warden Dashboard via mobile sidebar menu options (Check #116)</t>
+  </si>
+  <si>
+    <t>TC-APP-117: Assert container padding and alignment on mobile screen for Mobile: Mobile Profile Settings (Check #117)</t>
+  </si>
+  <si>
+    <t>TC-APP-118: Verify average rating star system is visible on mobile view of Mobile: Mobile Student Login (Check #118)</t>
+  </si>
+  <si>
+    <t>TC-APP-119: Check touch target size for submit button control on mobile screen of Mobile: Mobile Warden Dashboard (Check #119)</t>
+  </si>
+  <si>
+    <t>TC-APP-120: Check text wrapping of password input text box on mobile display of Mobile: Mobile Role Selection (Check #120)</t>
+  </si>
+  <si>
+    <t>TC-APP-121: Verify navigation to Mobile: Mobile Profile Settings via mobile sidebar menu options (Check #121)</t>
+  </si>
+  <si>
+    <t>TC-APP-122: Verify keyboard dismissal after entering text in fee status badge display on Mobile: Mobile Student Login (Check #122)</t>
+  </si>
+  <si>
+    <t>TC-APP-123: Verify navigation to Mobile: Mobile Mess Feedback via mobile sidebar menu options (Check #123)</t>
+  </si>
+  <si>
+    <t>TC-APP-124: Verify swipe gestures on main navigation header on mobile view of Mobile: Mobile Raise Complaint (Check #124)</t>
+  </si>
+  <si>
+    <t>TC-APP-125: Check text wrapping of main navigation header on mobile display of Mobile: Mobile Admin Login (Check #125)</t>
+  </si>
+  <si>
+    <t>TC-APP-126: Verify navigation to Mobile: Mobile Mess Feedback via mobile sidebar menu options (Check #126)</t>
+  </si>
+  <si>
+    <t>TC-APP-127: Test student login flow through mobile interface of Mobile: Mobile Leave Request (Check #127)</t>
+  </si>
+  <si>
+    <t>TC-APP-128: Verify footer copyright note is visible on mobile view of Mobile: Mobile Raise Complaint (Check #128)</t>
+  </si>
+  <si>
+    <t>TC-APP-129: Check text wrapping of role selection button on mobile display of Mobile: Mobile Landing (Check #129)</t>
+  </si>
+  <si>
+    <t>TC-APP-130: Verify navigation to Mobile: Mobile Logout via mobile sidebar menu options (Check #130)</t>
+  </si>
+  <si>
+    <t>TC-APP-131: Verify swipe gestures on dashboard metrics card on mobile view of Mobile: Mobile Logout (Check #131)</t>
+  </si>
+  <si>
+    <t>TC-APP-132: Verify main navigation header is visible on mobile view of Mobile: Mobile Raise Complaint (Check #132)</t>
+  </si>
+  <si>
+    <t>TC-APP-133: Check touch target size for email input form control on mobile screen of Mobile: Mobile Landing (Check #133)</t>
+  </si>
+  <si>
+    <t>TC-APP-134: Check text wrapping of email input form control on mobile display of Mobile: Mobile Profile Settings (Check #134)</t>
+  </si>
+  <si>
+    <t>TC-APP-135: Verify keyboard dismissal after entering text in footer copyright note on Mobile: Mobile Warden Login (Check #135)</t>
+  </si>
+  <si>
+    <t>TC-APP-136: Verify navigation to Mobile: Mobile Raise Complaint via mobile sidebar menu options (Check #136)</t>
+  </si>
+  <si>
+    <t>TC-APP-137: Test student login flow through mobile interface of Mobile: Mobile Admin Dashboard (Check #137)</t>
+  </si>
+  <si>
+    <t>TC-APP-138: Verify swipe gestures on footer copyright note on mobile view of Mobile: Mobile Student Dashboard (Check #138)</t>
+  </si>
+  <si>
+    <t>TC-APP-139: Assert container padding and alignment on mobile screen for Mobile: Mobile Room View (Check #139)</t>
+  </si>
+  <si>
+    <t>TC-APP-140: Verify swipe gestures on email input form control on mobile view of Mobile: Mobile Room View (Check #140)</t>
+  </si>
+  <si>
+    <t>TC-APP-141: Test student login flow through mobile interface of Mobile: Mobile Warden Login (Check #141)</t>
+  </si>
+  <si>
+    <t>TC-APP-142: Verify navigation to Mobile: Mobile Leave Request via mobile sidebar menu options (Check #142)</t>
+  </si>
+  <si>
+    <t>TC-APP-143: Verify swipe gestures on leave request request form on mobile view of Mobile: Mobile Room View (Check #143)</t>
+  </si>
+  <si>
+    <t>TC-APP-144: Verify navigation to Mobile: Mobile Raise Complaint via mobile sidebar menu options (Check #144)</t>
+  </si>
+  <si>
+    <t>TC-APP-145: Check touch target size for notice board widget on mobile screen of Mobile: Mobile Warden Login (Check #145)</t>
+  </si>
+  <si>
+    <t>TC-APP-146: Assert container padding and alignment on mobile screen for Mobile: Mobile Logout (Check #146)</t>
+  </si>
+  <si>
+    <t>TC-APP-147: Verify keyboard dismissal after entering text in role selection button on Mobile: Mobile Student Login (Check #147)</t>
+  </si>
+  <si>
+    <t>TC-APP-148: Check text wrapping of footer copyright note on mobile display of Mobile: Mobile Role Selection (Check #148)</t>
+  </si>
+  <si>
+    <t>TC-APP-149: Verify navigation to Mobile: Mobile Warden Dashboard via mobile sidebar menu options (Check #149)</t>
   </si>
   <si>
     <t>TC-APP-150: Verify notice board widget is visible on mobile view of Mobile: Mobile Leave Request (Check #150)</t>
   </si>
   <si>
-    <t>TC-APP-151: Check text wrapping of role selection button on mobile display of Mobile: Mobile Logout (Check #151)</t>
-  </si>
-  <si>
-    <t>TC-APP-152: Check touch target size for alert dialog box on mobile screen of Mobile: Mobile Warden Dashboard (Check #152)</t>
-  </si>
-  <si>
-    <t>TC-APP-153: Verify navigation to Mobile: Mobile Admin Login via mobile sidebar menu options (Check #153)</t>
-  </si>
-  <si>
-    <t>TC-APP-154: Check touch target size for sidebar navigation items on mobile screen of Mobile: Mobile Leave Request (Check #154)</t>
-  </si>
-  <si>
-    <t>TC-APP-155: Test student login flow through mobile interface of Mobile: Mobile Logout (Check #155)</t>
-  </si>
-  <si>
-    <t>TC-APP-156: Verify keyboard dismissal after entering text in role selection button on Mobile: Mobile Student Dashboard (Check #156)</t>
-  </si>
-  <si>
-    <t>TC-APP-157: Verify keyboard dismissal after entering text in password input text box on Mobile: Mobile Room View (Check #157)</t>
-  </si>
-  <si>
-    <t>TC-APP-158: Check text wrapping of main navigation header on mobile display of Mobile: Mobile Warden Login (Check #158)</t>
-  </si>
-  <si>
-    <t>TC-APP-159: Verify swipe gestures on leave request request form on mobile view of Mobile: Mobile Leave Request (Check #159)</t>
-  </si>
-  <si>
-    <t>TC-APP-160: Check text wrapping of username input text field on mobile display of Mobile: Mobile Logout (Check #160)</t>
-  </si>
-  <si>
-    <t>TC-APP-161: Verify swipe gestures on main navigation header on mobile view of Mobile: Mobile Logout (Check #161)</t>
-  </si>
-  <si>
-    <t>TC-APP-162: Verify navigation to Mobile: Mobile Student Dashboard via mobile sidebar menu options (Check #162)</t>
-  </si>
-  <si>
-    <t>TC-APP-163: Check touch target size for alert dialog box on mobile screen of Mobile: Mobile Landing (Check #163)</t>
-  </si>
-  <si>
-    <t>TC-APP-164: Check touch target size for leave request request form on mobile screen of Mobile: Mobile Leave Request (Check #164)</t>
-  </si>
-  <si>
-    <t>TC-APP-165: Test student login flow through mobile interface of Mobile: Mobile Leave Request (Check #165)</t>
-  </si>
-  <si>
-    <t>TC-APP-166: Check touch target size for sidebar navigation items on mobile screen of Mobile: Mobile Warden Dashboard (Check #166)</t>
-  </si>
-  <si>
-    <t>TC-APP-167: Assert container padding and alignment on mobile screen for Mobile: Mobile Leave Request (Check #167)</t>
-  </si>
-  <si>
-    <t>TC-APP-168: Verify keyboard dismissal after entering text in sidebar navigation items on Mobile: Mobile Logout (Check #168)</t>
-  </si>
-  <si>
-    <t>TC-APP-169: Assert container padding and alignment on mobile screen for Mobile: Mobile Profile Settings (Check #169)</t>
-  </si>
-  <si>
-    <t>TC-APP-170: Verify swipe gestures on complaint history table on mobile view of Mobile: Mobile Landing (Check #170)</t>
-  </si>
-  <si>
-    <t>TC-APP-171: Check text wrapping of leave request request form on mobile display of Mobile: Mobile Admin Dashboard (Check #171)</t>
-  </si>
-  <si>
-    <t>TC-APP-172: Check text wrapping of role selection button on mobile display of Mobile: Mobile Student Dashboard (Check #172)</t>
-  </si>
-  <si>
-    <t>TC-APP-173: Assert container padding and alignment on mobile screen for Mobile: Mobile Role Selection (Check #173)</t>
-  </si>
-  <si>
-    <t>TC-APP-174: Verify keyboard dismissal after entering text in username input text field on Mobile: Mobile Raise Complaint (Check #174)</t>
-  </si>
-  <si>
-    <t>TC-APP-175: Check touch target size for alert dialog box on mobile screen of Mobile: Mobile Admin Login (Check #175)</t>
-  </si>
-  <si>
-    <t>TC-APP-176: Verify navigation to Mobile: Mobile Logout via mobile sidebar menu options (Check #176)</t>
-  </si>
-  <si>
-    <t>TC-APP-177: Check touch target size for notice board widget on mobile screen of Mobile: Mobile Student Login (Check #177)</t>
-  </si>
-  <si>
-    <t>TC-APP-178: Check touch target size for database connection module on mobile screen of Mobile: Mobile Role Selection (Check #178)</t>
-  </si>
-  <si>
-    <t>TC-APP-179: Verify navigation to Mobile: Mobile Mess Feedback via mobile sidebar menu options (Check #179)</t>
-  </si>
-  <si>
-    <t>TC-APP-180: Check text wrapping of back button navigation link on mobile display of Mobile: Mobile Raise Complaint (Check #180)</t>
-  </si>
-  <si>
-    <t>TC-APP-181: Verify navigation to Mobile: Mobile Admin Dashboard via mobile sidebar menu options (Check #181)</t>
-  </si>
-  <si>
-    <t>TC-APP-182: Test student login flow through mobile interface of Mobile: Mobile Mess Feedback (Check #182)</t>
-  </si>
-  <si>
-    <t>TC-APP-183: Verify keyboard dismissal after entering text in email input form control on Mobile: Mobile Mess Feedback (Check #183)</t>
-  </si>
-  <si>
-    <t>TC-APP-184: Verify keyboard dismissal after entering text in role selection button on Mobile: Mobile Student Login (Check #184)</t>
-  </si>
-  <si>
-    <t>TC-APP-185: Verify notice board widget is visible on mobile view of Mobile: Mobile Mess Feedback (Check #185)</t>
-  </si>
-  <si>
-    <t>TC-APP-186: Test student login flow through mobile interface of Mobile: Mobile Warden Login (Check #186)</t>
-  </si>
-  <si>
-    <t>TC-APP-187: Test student login flow through mobile interface of Mobile: Mobile Warden Login (Check #187)</t>
-  </si>
-  <si>
-    <t>TC-APP-188: Verify swipe gestures on database connection module on mobile view of Mobile: Mobile Raise Complaint (Check #188)</t>
-  </si>
-  <si>
-    <t>TC-APP-189: Assert container padding and alignment on mobile screen for Mobile: Mobile Raise Complaint (Check #189)</t>
-  </si>
-  <si>
-    <t>TC-APP-190: Test student login flow through mobile interface of Mobile: Mobile Leave Request (Check #190)</t>
-  </si>
-  <si>
-    <t>TC-APP-191: Verify swipe gestures on back button navigation link on mobile view of Mobile: Mobile Role Selection (Check #191)</t>
-  </si>
-  <si>
-    <t>TC-APP-192: Check touch target size for database connection module on mobile screen of Mobile: Mobile Room View (Check #192)</t>
-  </si>
-  <si>
-    <t>TC-APP-193: Verify navigation to Mobile: Mobile Role Selection via mobile sidebar menu options (Check #193)</t>
-  </si>
-  <si>
-    <t>TC-APP-194: Verify navigation to Mobile: Mobile Warden Dashboard via mobile sidebar menu options (Check #194)</t>
-  </si>
-  <si>
-    <t>TC-APP-195: Verify swipe gestures on submit button control on mobile view of Mobile: Mobile Landing (Check #195)</t>
-  </si>
-  <si>
-    <t>TC-APP-196: Verify complaint history table is visible on mobile view of Mobile: Mobile Mess Feedback (Check #196)</t>
-  </si>
-  <si>
-    <t>TC-APP-197: Verify navigation to Mobile: Mobile Warden Dashboard via mobile sidebar menu options (Check #197)</t>
-  </si>
-  <si>
-    <t>TC-APP-198: Verify navigation to Mobile: Mobile Admin Dashboard via mobile sidebar menu options (Check #198)</t>
-  </si>
-  <si>
-    <t>TC-APP-199: Verify back button navigation link is visible on mobile view of Mobile: Mobile Admin Login (Check #199)</t>
-  </si>
-  <si>
-    <t>TC-APP-200: Verify navigation to Mobile: Mobile Student Dashboard via mobile sidebar menu options (Check #200)</t>
-  </si>
-  <si>
-    <t>TC-APP-201: Check text wrapping of profile image uploader container on mobile display of Mobile: Mobile Student Dashboard (Check #201)</t>
-  </si>
-  <si>
-    <t>TC-APP-202: Test student login flow through mobile interface of Mobile: Mobile Room View (Check #202)</t>
-  </si>
-  <si>
-    <t>TC-APP-203: Assert container padding and alignment on mobile screen for Mobile: Mobile Mess Feedback (Check #203)</t>
-  </si>
-  <si>
-    <t>TC-APP-204: Verify footer copyright note is visible on mobile view of Mobile: Mobile Student Login (Check #204)</t>
-  </si>
-  <si>
-    <t>TC-APP-205: Verify swipe gestures on complaint history table on mobile view of Mobile: Mobile Logout (Check #205)</t>
-  </si>
-  <si>
-    <t>TC-APP-206: Verify username input text field is visible on mobile view of Mobile: Mobile Warden Dashboard (Check #206)</t>
-  </si>
-  <si>
-    <t>TC-APP-207: Verify navigation to Mobile: Mobile Warden Dashboard via mobile sidebar menu options (Check #207)</t>
-  </si>
-  <si>
-    <t>TC-APP-208: Check text wrapping of profile image uploader container on mobile display of Mobile: Mobile Raise Complaint (Check #208)</t>
-  </si>
-  <si>
-    <t>TC-APP-209: Verify navigation to Mobile: Mobile Role Selection via mobile sidebar menu options (Check #209)</t>
-  </si>
-  <si>
-    <t>TC-APP-210: Verify keyboard dismissal after entering text in alert dialog box on Mobile: Mobile Logout (Check #210)</t>
-  </si>
-  <si>
-    <t>TC-APP-211: Verify notice board widget is visible on mobile view of Mobile: Mobile Leave Request (Check #211)</t>
-  </si>
-  <si>
-    <t>TC-APP-212: Assert container padding and alignment on mobile screen for Mobile: Mobile Admin Login (Check #212)</t>
-  </si>
-  <si>
-    <t>TC-APP-213: Check touch target size for complaint history table on mobile screen of Mobile: Mobile Logout (Check #213)</t>
-  </si>
-  <si>
-    <t>TC-APP-214: Verify keyboard dismissal after entering text in complaint history table on Mobile: Mobile Admin Dashboard (Check #214)</t>
-  </si>
-  <si>
-    <t>TC-APP-215: Check touch target size for email input form control on mobile screen of Mobile: Mobile Admin Login (Check #215)</t>
-  </si>
-  <si>
-    <t>TC-APP-216: Assert container padding and alignment on mobile screen for Mobile: Mobile Raise Complaint (Check #216)</t>
-  </si>
-  <si>
-    <t>TC-APP-217: Verify role selection button is visible on mobile view of Mobile: Mobile Admin Dashboard (Check #217)</t>
-  </si>
-  <si>
-    <t>TC-APP-218: Test student login flow through mobile interface of Mobile: Mobile Profile Settings (Check #218)</t>
-  </si>
-  <si>
-    <t>TC-APP-219: Test student login flow through mobile interface of Mobile: Mobile Landing (Check #219)</t>
-  </si>
-  <si>
-    <t>TC-APP-220: Verify keyboard dismissal after entering text in submit button control on Mobile: Mobile Student Dashboard (Check #220)</t>
-  </si>
-  <si>
-    <t>TC-APP-221: Verify swipe gestures on alert dialog box on mobile view of Mobile: Mobile Mess Feedback (Check #221)</t>
-  </si>
-  <si>
-    <t>TC-APP-222: Assert container padding and alignment on mobile screen for Mobile: Mobile Role Selection (Check #222)</t>
-  </si>
-  <si>
-    <t>TC-APP-223: Verify swipe gestures on role selection button on mobile view of Mobile: Mobile Student Dashboard (Check #223)</t>
-  </si>
-  <si>
-    <t>TC-APP-224: Check text wrapping of main navigation header on mobile display of Mobile: Mobile Room View (Check #224)</t>
-  </si>
-  <si>
-    <t>TC-APP-225: Verify navigation to Mobile: Mobile Admin Login via mobile sidebar menu options (Check #225)</t>
-  </si>
-  <si>
-    <t>TC-APP-226: Verify swipe gestures on leave request request form on mobile view of Mobile: Mobile Landing (Check #226)</t>
-  </si>
-  <si>
-    <t>TC-APP-227: Verify swipe gestures on average rating star system on mobile view of Mobile: Mobile Room View (Check #227)</t>
-  </si>
-  <si>
-    <t>TC-APP-228: Verify keyboard dismissal after entering text in dashboard metrics card on Mobile: Mobile Landing (Check #228)</t>
-  </si>
-  <si>
-    <t>TC-APP-229: Verify swipe gestures on fee status badge display on mobile view of Mobile: Mobile Warden Login (Check #229)</t>
-  </si>
-  <si>
-    <t>TC-APP-230: Test student login flow through mobile interface of Mobile: Mobile Room View (Check #230)</t>
-  </si>
-  <si>
-    <t>TC-APP-231: Verify main navigation header is visible on mobile view of Mobile: Mobile Student Login (Check #231)</t>
-  </si>
-  <si>
-    <t>TC-APP-232: Test student login flow through mobile interface of Mobile: Mobile Mess Feedback (Check #232)</t>
-  </si>
-  <si>
-    <t>TC-APP-233: Check text wrapping of leave request request form on mobile display of Mobile: Mobile Warden Login (Check #233)</t>
-  </si>
-  <si>
-    <t>TC-APP-234: Test student login flow through mobile interface of Mobile: Mobile Leave Request (Check #234)</t>
-  </si>
-  <si>
-    <t>TC-APP-235: Verify keyboard dismissal after entering text in main navigation header on Mobile: Mobile Role Selection (Check #235)</t>
-  </si>
-  <si>
-    <t>TC-APP-236: Verify swipe gestures on profile image uploader container on mobile view of Mobile: Mobile Warden Login (Check #236)</t>
-  </si>
-  <si>
-    <t>TC-APP-237: Verify swipe gestures on username input text field on mobile view of Mobile: Mobile Admin Login (Check #237)</t>
-  </si>
-  <si>
-    <t>TC-APP-238: Assert container padding and alignment on mobile screen for Mobile: Mobile Warden Dashboard (Check #238)</t>
-  </si>
-  <si>
-    <t>TC-APP-239: Check touch target size for role selection button on mobile screen of Mobile: Mobile Warden Dashboard (Check #239)</t>
-  </si>
-  <si>
-    <t>TC-APP-240: Verify notice board widget is visible on mobile view of Mobile: Mobile Admin Login (Check #240)</t>
-  </si>
-  <si>
-    <t>TC-APP-241: Verify navigation to Mobile: Mobile Profile Settings via mobile sidebar menu options (Check #241)</t>
-  </si>
-  <si>
-    <t>TC-APP-242: Assert container padding and alignment on mobile screen for Mobile: Mobile Warden Dashboard (Check #242)</t>
-  </si>
-  <si>
-    <t>TC-APP-243: Verify navigation to Mobile: Mobile Admin Login via mobile sidebar menu options (Check #243)</t>
-  </si>
-  <si>
-    <t>TC-APP-244: Assert container padding and alignment on mobile screen for Mobile: Mobile Student Login (Check #244)</t>
-  </si>
-  <si>
-    <t>TC-APP-245: Verify keyboard dismissal after entering text in footer copyright note on Mobile: Mobile Role Selection (Check #245)</t>
-  </si>
-  <si>
-    <t>TC-APP-246: Check text wrapping of alert dialog box on mobile display of Mobile: Mobile Admin Dashboard (Check #246)</t>
-  </si>
-  <si>
-    <t>TC-APP-247: Verify database connection module is visible on mobile view of Mobile: Mobile Warden Dashboard (Check #247)</t>
-  </si>
-  <si>
-    <t>TC-APP-248: Check touch target size for sidebar navigation items on mobile screen of Mobile: Mobile Mess Feedback (Check #248)</t>
-  </si>
-  <si>
-    <t>TC-APP-249: Assert container padding and alignment on mobile screen for Mobile: Mobile Admin Login (Check #249)</t>
-  </si>
-  <si>
-    <t>TC-APP-250: Verify keyboard dismissal after entering text in leave request request form on Mobile: Mobile Logout (Check #250)</t>
-  </si>
-  <si>
-    <t>TC-APP-251: Test student login flow through mobile interface of Mobile: Mobile Warden Dashboard (Check #251)</t>
-  </si>
-  <si>
-    <t>TC-APP-252: Check text wrapping of username input text field on mobile display of Mobile: Mobile Logout (Check #252)</t>
-  </si>
-  <si>
-    <t>TC-APP-253: Verify complaint history table is visible on mobile view of Mobile: Mobile Student Login (Check #253)</t>
-  </si>
-  <si>
-    <t>TC-APP-254: Test student login flow through mobile interface of Mobile: Mobile Room View (Check #254)</t>
-  </si>
-  <si>
-    <t>TC-APP-255: Verify keyboard dismissal after entering text in username input text field on Mobile: Mobile Mess Feedback (Check #255)</t>
-  </si>
-  <si>
-    <t>TC-APP-256: Test student login flow through mobile interface of Mobile: Mobile Role Selection (Check #256)</t>
-  </si>
-  <si>
-    <t>TC-APP-257: Verify leave request request form is visible on mobile view of Mobile: Mobile Warden Dashboard (Check #257)</t>
-  </si>
-  <si>
-    <t>TC-APP-258: Check text wrapping of main navigation header on mobile display of Mobile: Mobile Leave Request (Check #258)</t>
-  </si>
-  <si>
-    <t>TC-APP-259: Verify keyboard dismissal after entering text in notice board widget on Mobile: Mobile Mess Feedback (Check #259)</t>
-  </si>
-  <si>
-    <t>TC-APP-260: Verify swipe gestures on notice board widget on mobile view of Mobile: Mobile Admin Login (Check #260)</t>
-  </si>
-  <si>
-    <t>TC-APP-261: Verify keyboard dismissal after entering text in username input text field on Mobile: Mobile Raise Complaint (Check #261)</t>
-  </si>
-  <si>
-    <t>TC-APP-262: Verify navigation to Mobile: Mobile Student Dashboard via mobile sidebar menu options (Check #262)</t>
-  </si>
-  <si>
-    <t>TC-APP-263: Verify role selection button is visible on mobile view of Mobile: Mobile Logout (Check #263)</t>
-  </si>
-  <si>
-    <t>TC-APP-264: Check text wrapping of database connection module on mobile display of Mobile: Mobile Student Dashboard (Check #264)</t>
-  </si>
-  <si>
-    <t>TC-APP-265: Check text wrapping of average rating star system on mobile display of Mobile: Mobile Raise Complaint (Check #265)</t>
-  </si>
-  <si>
-    <t>TC-APP-266: Check touch target size for profile image uploader container on mobile screen of Mobile: Mobile Mess Feedback (Check #266)</t>
-  </si>
-  <si>
-    <t>TC-APP-267: Verify swipe gestures on role selection button on mobile view of Mobile: Mobile Room View (Check #267)</t>
-  </si>
-  <si>
-    <t>TC-APP-268: Check touch target size for sidebar navigation items on mobile screen of Mobile: Mobile Admin Login (Check #268)</t>
-  </si>
-  <si>
-    <t>TC-APP-269: Verify keyboard dismissal after entering text in dashboard metrics card on Mobile: Mobile Role Selection (Check #269)</t>
-  </si>
-  <si>
-    <t>TC-APP-270: Verify navigation to Mobile: Mobile Leave Request via mobile sidebar menu options (Check #270)</t>
-  </si>
-  <si>
-    <t>TC-APP-271: Assert container padding and alignment on mobile screen for Mobile: Mobile Admin Dashboard (Check #271)</t>
-  </si>
-  <si>
-    <t>TC-APP-272: Verify fee status badge display is visible on mobile view of Mobile: Mobile Profile Settings (Check #272)</t>
-  </si>
-  <si>
-    <t>TC-APP-273: Verify swipe gestures on submit button control on mobile view of Mobile: Mobile Profile Settings (Check #273)</t>
-  </si>
-  <si>
-    <t>TC-APP-274: Verify keyboard dismissal after entering text in footer copyright note on Mobile: Mobile Logout (Check #274)</t>
-  </si>
-  <si>
-    <t>TC-APP-275: Verify database connection module is visible on mobile view of Mobile: Mobile Warden Login (Check #275)</t>
-  </si>
-  <si>
-    <t>TC-APP-276: Check text wrapping of email input form control on mobile display of Mobile: Mobile Raise Complaint (Check #276)</t>
-  </si>
-  <si>
-    <t>TC-APP-277: Verify profile image uploader container is visible on mobile view of Mobile: Mobile Student Dashboard (Check #277)</t>
-  </si>
-  <si>
-    <t>TC-APP-278: Verify email input form control is visible on mobile view of Mobile: Mobile Raise Complaint (Check #278)</t>
-  </si>
-  <si>
-    <t>TC-APP-279: Assert container padding and alignment on mobile screen for Mobile: Mobile Admin Login (Check #279)</t>
-  </si>
-  <si>
-    <t>TC-APP-280: Verify alert dialog box is visible on mobile view of Mobile: Mobile Student Login (Check #280)</t>
-  </si>
-  <si>
-    <t>TC-APP-281: Check touch target size for leave request request form on mobile screen of Mobile: Mobile Admin Login (Check #281)</t>
-  </si>
-  <si>
-    <t>TC-APP-282: Verify navigation to Mobile: Mobile Logout via mobile sidebar menu options (Check #282)</t>
-  </si>
-  <si>
-    <t>TC-APP-283: Test student login flow through mobile interface of Mobile: Mobile Admin Login (Check #283)</t>
-  </si>
-  <si>
-    <t>TC-APP-284: Test student login flow through mobile interface of Mobile: Mobile Raise Complaint (Check #284)</t>
-  </si>
-  <si>
-    <t>TC-APP-285: Check text wrapping of submit button control on mobile display of Mobile: Mobile Profile Settings (Check #285)</t>
-  </si>
-  <si>
-    <t>TC-APP-286: Assert container padding and alignment on mobile screen for Mobile: Mobile Landing (Check #286)</t>
-  </si>
-  <si>
-    <t>TC-APP-287: Check touch target size for footer copyright note on mobile screen of Mobile: Mobile Room View (Check #287)</t>
-  </si>
-  <si>
-    <t>TC-APP-288: Verify navigation to Mobile: Mobile Admin Login via mobile sidebar menu options (Check #288)</t>
-  </si>
-  <si>
-    <t>TC-APP-289: Verify keyboard dismissal after entering text in footer copyright note on Mobile: Mobile Warden Dashboard (Check #289)</t>
-  </si>
-  <si>
-    <t>TC-APP-290: Verify swipe gestures on email input form control on mobile view of Mobile: Mobile Admin Dashboard (Check #290)</t>
-  </si>
-  <si>
-    <t>TC-APP-291: Test student login flow through mobile interface of Mobile: Mobile Landing (Check #291)</t>
-  </si>
-  <si>
-    <t>TC-APP-292: Check touch target size for footer copyright note on mobile screen of Mobile: Mobile Logout (Check #292)</t>
-  </si>
-  <si>
-    <t>TC-APP-293: Verify notice board widget is visible on mobile view of Mobile: Mobile Student Login (Check #293)</t>
-  </si>
-  <si>
-    <t>TC-APP-294: Verify swipe gestures on submit button control on mobile view of Mobile: Mobile Warden Login (Check #294)</t>
-  </si>
-  <si>
-    <t>TC-APP-295: Verify swipe gestures on password input text box on mobile view of Mobile: Mobile Student Login (Check #295)</t>
-  </si>
-  <si>
-    <t>TC-APP-296: Check text wrapping of alert dialog box on mobile display of Mobile: Mobile Logout (Check #296)</t>
-  </si>
-  <si>
-    <t>TC-APP-297: Test student login flow through mobile interface of Mobile: Mobile Raise Complaint (Check #297)</t>
-  </si>
-  <si>
-    <t>TC-APP-298: Check text wrapping of dashboard metrics card on mobile display of Mobile: Mobile Warden Dashboard (Check #298)</t>
-  </si>
-  <si>
-    <t>TC-APP-299: Verify keyboard dismissal after entering text in password input text box on Mobile: Mobile Role Selection (Check #299)</t>
-  </si>
-  <si>
-    <t>TC-APP-300: Check touch target size for notice board widget on mobile screen of Mobile: Mobile Profile Settings (Check #300)</t>
+    <t>TC-APP-151: Check touch target size for sidebar navigation items on mobile screen of Mobile: Mobile Student Dashboard (Check #151)</t>
+  </si>
+  <si>
+    <t>TC-APP-152: Verify navigation to Mobile: Mobile Student Login via mobile sidebar menu options (Check #152)</t>
+  </si>
+  <si>
+    <t>TC-APP-153: Verify swipe gestures on notice board widget on mobile view of Mobile: Mobile Admin Dashboard (Check #153)</t>
+  </si>
+  <si>
+    <t>TC-APP-154: Verify navigation to Mobile: Mobile Logout via mobile sidebar menu options (Check #154)</t>
+  </si>
+  <si>
+    <t>TC-APP-155: Assert container padding and alignment on mobile screen for Mobile: Mobile Logout (Check #155)</t>
+  </si>
+  <si>
+    <t>TC-APP-156: Assert container padding and alignment on mobile screen for Mobile: Mobile Raise Complaint (Check #156)</t>
+  </si>
+  <si>
+    <t>TC-APP-157: Assert container padding and alignment on mobile screen for Mobile: Mobile Role Selection (Check #157)</t>
+  </si>
+  <si>
+    <t>TC-APP-158: Verify navigation to Mobile: Mobile Student Dashboard via mobile sidebar menu options (Check #158)</t>
+  </si>
+  <si>
+    <t>TC-APP-159: Test student login flow through mobile interface of Mobile: Mobile Student Login (Check #159)</t>
+  </si>
+  <si>
+    <t>TC-APP-160: Check touch target size for main navigation header on mobile screen of Mobile: Mobile Admin Login (Check #160)</t>
+  </si>
+  <si>
+    <t>TC-APP-161: Check text wrapping of notice board widget on mobile display of Mobile: Mobile Leave Request (Check #161)</t>
+  </si>
+  <si>
+    <t>TC-APP-162: Check touch target size for alert dialog box on mobile screen of Mobile: Mobile Leave Request (Check #162)</t>
+  </si>
+  <si>
+    <t>TC-APP-163: Verify navigation to Mobile: Mobile Room View via mobile sidebar menu options (Check #163)</t>
+  </si>
+  <si>
+    <t>TC-APP-164: Verify navigation to Mobile: Mobile Landing via mobile sidebar menu options (Check #164)</t>
+  </si>
+  <si>
+    <t>TC-APP-165: Check text wrapping of role selection button on mobile display of Mobile: Mobile Student Dashboard (Check #165)</t>
+  </si>
+  <si>
+    <t>TC-APP-166: Verify swipe gestures on email input form control on mobile view of Mobile: Mobile Admin Login (Check #166)</t>
+  </si>
+  <si>
+    <t>TC-APP-167: Assert container padding and alignment on mobile screen for Mobile: Mobile Room View (Check #167)</t>
+  </si>
+  <si>
+    <t>TC-APP-168: Test student login flow through mobile interface of Mobile: Mobile Admin Dashboard (Check #168)</t>
+  </si>
+  <si>
+    <t>TC-APP-169: Verify keyboard dismissal after entering text in notice board widget on Mobile: Mobile Role Selection (Check #169)</t>
+  </si>
+  <si>
+    <t>TC-APP-170: Verify keyboard dismissal after entering text in profile image uploader container on Mobile: Mobile Student Dashboard (Check #170)</t>
+  </si>
+  <si>
+    <t>TC-APP-171: Test student login flow through mobile interface of Mobile: Mobile Mess Feedback (Check #171)</t>
+  </si>
+  <si>
+    <t>TC-APP-172: Check touch target size for submit button control on mobile screen of Mobile: Mobile Admin Dashboard (Check #172)</t>
+  </si>
+  <si>
+    <t>TC-APP-173: Assert container padding and alignment on mobile screen for Mobile: Mobile Student Login (Check #173)</t>
+  </si>
+  <si>
+    <t>TC-APP-174: Verify keyboard dismissal after entering text in main navigation header on Mobile: Mobile Profile Settings (Check #174)</t>
+  </si>
+  <si>
+    <t>TC-APP-175: Verify footer copyright note is visible on mobile view of Mobile: Mobile Profile Settings (Check #175)</t>
+  </si>
+  <si>
+    <t>TC-APP-176: Assert container padding and alignment on mobile screen for Mobile: Mobile Admin Dashboard (Check #176)</t>
+  </si>
+  <si>
+    <t>TC-APP-177: Check text wrapping of fee status badge display on mobile display of Mobile: Mobile Role Selection (Check #177)</t>
+  </si>
+  <si>
+    <t>TC-APP-178: Assert container padding and alignment on mobile screen for Mobile: Mobile Admin Login (Check #178)</t>
+  </si>
+  <si>
+    <t>TC-APP-179: Verify profile image uploader container is visible on mobile view of Mobile: Mobile Admin Login (Check #179)</t>
+  </si>
+  <si>
+    <t>TC-APP-180: Check text wrapping of main navigation header on mobile display of Mobile: Mobile Student Login (Check #180)</t>
+  </si>
+  <si>
+    <t>TC-APP-181: Verify navigation to Mobile: Mobile Warden Login via mobile sidebar menu options (Check #181)</t>
+  </si>
+  <si>
+    <t>TC-APP-182: Test student login flow through mobile interface of Mobile: Mobile Leave Request (Check #182)</t>
+  </si>
+  <si>
+    <t>TC-APP-183: Test student login flow through mobile interface of Mobile: Mobile Warden Login (Check #183)</t>
+  </si>
+  <si>
+    <t>TC-APP-184: Verify keyboard dismissal after entering text in complaint history table on Mobile: Mobile Profile Settings (Check #184)</t>
+  </si>
+  <si>
+    <t>TC-APP-185: Verify navigation to Mobile: Mobile Student Login via mobile sidebar menu options (Check #185)</t>
+  </si>
+  <si>
+    <t>TC-APP-186: Assert container padding and alignment on mobile screen for Mobile: Mobile Mess Feedback (Check #186)</t>
+  </si>
+  <si>
+    <t>TC-APP-187: Assert container padding and alignment on mobile screen for Mobile: Mobile Raise Complaint (Check #187)</t>
+  </si>
+  <si>
+    <t>TC-APP-188: Check touch target size for username input text field on mobile screen of Mobile: Mobile Mess Feedback (Check #188)</t>
+  </si>
+  <si>
+    <t>TC-APP-189: Assert container padding and alignment on mobile screen for Mobile: Mobile Admin Dashboard (Check #189)</t>
+  </si>
+  <si>
+    <t>TC-APP-190: Verify email input form control is visible on mobile view of Mobile: Mobile Raise Complaint (Check #190)</t>
+  </si>
+  <si>
+    <t>TC-APP-191: Check touch target size for submit button control on mobile screen of Mobile: Mobile Role Selection (Check #191)</t>
+  </si>
+  <si>
+    <t>TC-APP-192: Verify dashboard metrics card is visible on mobile view of Mobile: Mobile Profile Settings (Check #192)</t>
+  </si>
+  <si>
+    <t>TC-APP-193: Verify password input text box is visible on mobile view of Mobile: Mobile Raise Complaint (Check #193)</t>
+  </si>
+  <si>
+    <t>TC-APP-194: Test student login flow through mobile interface of Mobile: Mobile Landing (Check #194)</t>
+  </si>
+  <si>
+    <t>TC-APP-195: Verify navigation to Mobile: Mobile Raise Complaint via mobile sidebar menu options (Check #195)</t>
+  </si>
+  <si>
+    <t>TC-APP-196: Check text wrapping of password input text box on mobile display of Mobile: Mobile Landing (Check #196)</t>
+  </si>
+  <si>
+    <t>TC-APP-197: Assert container padding and alignment on mobile screen for Mobile: Mobile Logout (Check #197)</t>
+  </si>
+  <si>
+    <t>TC-APP-198: Verify swipe gestures on sidebar navigation items on mobile view of Mobile: Mobile Raise Complaint (Check #198)</t>
+  </si>
+  <si>
+    <t>TC-APP-199: Verify keyboard dismissal after entering text in average rating star system on Mobile: Mobile Student Login (Check #199)</t>
+  </si>
+  <si>
+    <t>TC-APP-200: Test student login flow through mobile interface of Mobile: Mobile Raise Complaint (Check #200)</t>
+  </si>
+  <si>
+    <t>TC-APP-201: Verify password input text box is visible on mobile view of Mobile: Mobile Warden Login (Check #201)</t>
+  </si>
+  <si>
+    <t>TC-APP-202: Verify swipe gestures on password input text box on mobile view of Mobile: Mobile Warden Login (Check #202)</t>
+  </si>
+  <si>
+    <t>TC-APP-203: Verify average rating star system is visible on mobile view of Mobile: Mobile Student Login (Check #203)</t>
+  </si>
+  <si>
+    <t>TC-APP-204: Verify email input form control is visible on mobile view of Mobile: Mobile Raise Complaint (Check #204)</t>
+  </si>
+  <si>
+    <t>TC-APP-205: Assert container padding and alignment on mobile screen for Mobile: Mobile Mess Feedback (Check #205)</t>
+  </si>
+  <si>
+    <t>TC-APP-206: Verify keyboard dismissal after entering text in leave request request form on Mobile: Mobile Student Dashboard (Check #206)</t>
+  </si>
+  <si>
+    <t>TC-APP-207: Verify keyboard dismissal after entering text in leave request request form on Mobile: Mobile Raise Complaint (Check #207)</t>
+  </si>
+  <si>
+    <t>TC-APP-208: Verify navigation to Mobile: Mobile Landing via mobile sidebar menu options (Check #208)</t>
+  </si>
+  <si>
+    <t>TC-APP-209: Verify alert dialog box is visible on mobile view of Mobile: Mobile Warden Login (Check #209)</t>
+  </si>
+  <si>
+    <t>TC-APP-210: Verify username input text field is visible on mobile view of Mobile: Mobile Admin Login (Check #210)</t>
+  </si>
+  <si>
+    <t>TC-APP-211: Check touch target size for complaint history table on mobile screen of Mobile: Mobile Student Dashboard (Check #211)</t>
+  </si>
+  <si>
+    <t>TC-APP-212: Verify navigation to Mobile: Mobile Raise Complaint via mobile sidebar menu options (Check #212)</t>
+  </si>
+  <si>
+    <t>TC-APP-213: Check text wrapping of submit button control on mobile display of Mobile: Mobile Admin Login (Check #213)</t>
+  </si>
+  <si>
+    <t>TC-APP-214: Verify navigation to Mobile: Mobile Landing via mobile sidebar menu options (Check #214)</t>
+  </si>
+  <si>
+    <t>TC-APP-215: Verify navigation to Mobile: Mobile Student Dashboard via mobile sidebar menu options (Check #215)</t>
+  </si>
+  <si>
+    <t>TC-APP-216: Check text wrapping of fee status badge display on mobile display of Mobile: Mobile Landing (Check #216)</t>
+  </si>
+  <si>
+    <t>TC-APP-217: Verify footer copyright note is visible on mobile view of Mobile: Mobile Profile Settings (Check #217)</t>
+  </si>
+  <si>
+    <t>TC-APP-218: Verify swipe gestures on role selection button on mobile view of Mobile: Mobile Mess Feedback (Check #218)</t>
+  </si>
+  <si>
+    <t>TC-APP-219: Check touch target size for main navigation header on mobile screen of Mobile: Mobile Student Login (Check #219)</t>
+  </si>
+  <si>
+    <t>TC-APP-220: Verify navigation to Mobile: Mobile Warden Login via mobile sidebar menu options (Check #220)</t>
+  </si>
+  <si>
+    <t>TC-APP-221: Verify swipe gestures on submit button control on mobile view of Mobile: Mobile Student Dashboard (Check #221)</t>
+  </si>
+  <si>
+    <t>TC-APP-222: Assert container padding and alignment on mobile screen for Mobile: Mobile Profile Settings (Check #222)</t>
+  </si>
+  <si>
+    <t>TC-APP-223: Assert container padding and alignment on mobile screen for Mobile: Mobile Admin Dashboard (Check #223)</t>
+  </si>
+  <si>
+    <t>TC-APP-224: Verify submit button control is visible on mobile view of Mobile: Mobile Student Login (Check #224)</t>
+  </si>
+  <si>
+    <t>TC-APP-225: Check text wrapping of sidebar navigation items on mobile display of Mobile: Mobile Leave Request (Check #225)</t>
+  </si>
+  <si>
+    <t>TC-APP-226: Verify navigation to Mobile: Mobile Warden Dashboard via mobile sidebar menu options (Check #226)</t>
+  </si>
+  <si>
+    <t>TC-APP-227: Test student login flow through mobile interface of Mobile: Mobile Warden Login (Check #227)</t>
+  </si>
+  <si>
+    <t>TC-APP-228: Verify database connection module is visible on mobile view of Mobile: Mobile Logout (Check #228)</t>
+  </si>
+  <si>
+    <t>TC-APP-229: Verify keyboard dismissal after entering text in username input text field on Mobile: Mobile Profile Settings (Check #229)</t>
+  </si>
+  <si>
+    <t>TC-APP-230: Check text wrapping of sidebar navigation items on mobile display of Mobile: Mobile Admin Dashboard (Check #230)</t>
+  </si>
+  <si>
+    <t>TC-APP-231: Verify keyboard dismissal after entering text in email input form control on Mobile: Mobile Mess Feedback (Check #231)</t>
+  </si>
+  <si>
+    <t>TC-APP-232: Verify swipe gestures on username input text field on mobile view of Mobile: Mobile Logout (Check #232)</t>
+  </si>
+  <si>
+    <t>TC-APP-233: Check text wrapping of password input text box on mobile display of Mobile: Mobile Admin Login (Check #233)</t>
+  </si>
+  <si>
+    <t>TC-APP-234: Check touch target size for back button navigation link on mobile screen of Mobile: Mobile Student Dashboard (Check #234)</t>
+  </si>
+  <si>
+    <t>TC-APP-235: Assert container padding and alignment on mobile screen for Mobile: Mobile Student Login (Check #235)</t>
+  </si>
+  <si>
+    <t>TC-APP-236: Check text wrapping of footer copyright note on mobile display of Mobile: Mobile Warden Dashboard (Check #236)</t>
+  </si>
+  <si>
+    <t>TC-APP-237: Check text wrapping of username input text field on mobile display of Mobile: Mobile Role Selection (Check #237)</t>
+  </si>
+  <si>
+    <t>TC-APP-238: Verify complaint history table is visible on mobile view of Mobile: Mobile Landing (Check #238)</t>
+  </si>
+  <si>
+    <t>TC-APP-239: Check touch target size for back button navigation link on mobile screen of Mobile: Mobile Student Dashboard (Check #239)</t>
+  </si>
+  <si>
+    <t>TC-APP-240: Verify role selection button is visible on mobile view of Mobile: Mobile Raise Complaint (Check #240)</t>
+  </si>
+  <si>
+    <t>TC-APP-241: Verify keyboard dismissal after entering text in database connection module on Mobile: Mobile Admin Login (Check #241)</t>
+  </si>
+  <si>
+    <t>TC-APP-242: Verify navigation to Mobile: Mobile Raise Complaint via mobile sidebar menu options (Check #242)</t>
+  </si>
+  <si>
+    <t>TC-APP-243: Check text wrapping of back button navigation link on mobile display of Mobile: Mobile Mess Feedback (Check #243)</t>
+  </si>
+  <si>
+    <t>TC-APP-244: Test student login flow through mobile interface of Mobile: Mobile Warden Dashboard (Check #244)</t>
+  </si>
+  <si>
+    <t>TC-APP-245: Verify profile image uploader container is visible on mobile view of Mobile: Mobile Warden Login (Check #245)</t>
+  </si>
+  <si>
+    <t>TC-APP-246: Test student login flow through mobile interface of Mobile: Mobile Role Selection (Check #246)</t>
+  </si>
+  <si>
+    <t>TC-APP-247: Verify keyboard dismissal after entering text in average rating star system on Mobile: Mobile Logout (Check #247)</t>
+  </si>
+  <si>
+    <t>TC-APP-248: Test student login flow through mobile interface of Mobile: Mobile Warden Login (Check #248)</t>
+  </si>
+  <si>
+    <t>TC-APP-249: Check touch target size for leave request request form on mobile screen of Mobile: Mobile Leave Request (Check #249)</t>
+  </si>
+  <si>
+    <t>TC-APP-250: Verify swipe gestures on back button navigation link on mobile view of Mobile: Mobile Mess Feedback (Check #250)</t>
+  </si>
+  <si>
+    <t>TC-APP-251: Check text wrapping of notice board widget on mobile display of Mobile: Mobile Student Dashboard (Check #251)</t>
+  </si>
+  <si>
+    <t>TC-APP-252: Verify swipe gestures on sidebar navigation items on mobile view of Mobile: Mobile Role Selection (Check #252)</t>
+  </si>
+  <si>
+    <t>TC-APP-253: Check text wrapping of role selection button on mobile display of Mobile: Mobile Room View (Check #253)</t>
+  </si>
+  <si>
+    <t>TC-APP-254: Verify swipe gestures on profile image uploader container on mobile view of Mobile: Mobile Profile Settings (Check #254)</t>
+  </si>
+  <si>
+    <t>TC-APP-255: Check text wrapping of submit button control on mobile display of Mobile: Mobile Room View (Check #255)</t>
+  </si>
+  <si>
+    <t>TC-APP-256: Assert container padding and alignment on mobile screen for Mobile: Mobile Leave Request (Check #256)</t>
+  </si>
+  <si>
+    <t>TC-APP-257: Verify navigation to Mobile: Mobile Mess Feedback via mobile sidebar menu options (Check #257)</t>
+  </si>
+  <si>
+    <t>TC-APP-258: Verify navigation to Mobile: Mobile Profile Settings via mobile sidebar menu options (Check #258)</t>
+  </si>
+  <si>
+    <t>TC-APP-259: Verify keyboard dismissal after entering text in sidebar navigation items on Mobile: Mobile Raise Complaint (Check #259)</t>
+  </si>
+  <si>
+    <t>TC-APP-260: Verify keyboard dismissal after entering text in leave request request form on Mobile: Mobile Role Selection (Check #260)</t>
+  </si>
+  <si>
+    <t>TC-APP-261: Verify role selection button is visible on mobile view of Mobile: Mobile Admin Login (Check #261)</t>
+  </si>
+  <si>
+    <t>TC-APP-262: Check text wrapping of main navigation header on mobile display of Mobile: Mobile Admin Login (Check #262)</t>
+  </si>
+  <si>
+    <t>TC-APP-263: Check touch target size for notice board widget on mobile screen of Mobile: Mobile Mess Feedback (Check #263)</t>
+  </si>
+  <si>
+    <t>TC-APP-264: Check text wrapping of footer copyright note on mobile display of Mobile: Mobile Admin Login (Check #264)</t>
+  </si>
+  <si>
+    <t>TC-APP-265: Verify swipe gestures on average rating star system on mobile view of Mobile: Mobile Role Selection (Check #265)</t>
+  </si>
+  <si>
+    <t>TC-APP-266: Verify swipe gestures on email input form control on mobile view of Mobile: Mobile Profile Settings (Check #266)</t>
+  </si>
+  <si>
+    <t>TC-APP-267: Assert container padding and alignment on mobile screen for Mobile: Mobile Student Dashboard (Check #267)</t>
+  </si>
+  <si>
+    <t>TC-APP-268: Verify navigation to Mobile: Mobile Warden Dashboard via mobile sidebar menu options (Check #268)</t>
+  </si>
+  <si>
+    <t>TC-APP-269: Check text wrapping of footer copyright note on mobile display of Mobile: Mobile Admin Login (Check #269)</t>
+  </si>
+  <si>
+    <t>TC-APP-270: Check touch target size for average rating star system on mobile screen of Mobile: Mobile Student Login (Check #270)</t>
+  </si>
+  <si>
+    <t>TC-APP-271: Verify swipe gestures on average rating star system on mobile view of Mobile: Mobile Student Dashboard (Check #271)</t>
+  </si>
+  <si>
+    <t>TC-APP-272: Verify complaint history table is visible on mobile view of Mobile: Mobile Logout (Check #272)</t>
+  </si>
+  <si>
+    <t>TC-APP-273: Assert container padding and alignment on mobile screen for Mobile: Mobile Raise Complaint (Check #273)</t>
+  </si>
+  <si>
+    <t>TC-APP-274: Verify navigation to Mobile: Mobile Warden Dashboard via mobile sidebar menu options (Check #274)</t>
+  </si>
+  <si>
+    <t>TC-APP-275: Verify keyboard dismissal after entering text in average rating star system on Mobile: Mobile Logout (Check #275)</t>
+  </si>
+  <si>
+    <t>TC-APP-276: Verify submit button control is visible on mobile view of Mobile: Mobile Admin Login (Check #276)</t>
+  </si>
+  <si>
+    <t>TC-APP-277: Assert container padding and alignment on mobile screen for Mobile: Mobile Warden Login (Check #277)</t>
+  </si>
+  <si>
+    <t>TC-APP-278: Verify keyboard dismissal after entering text in notice board widget on Mobile: Mobile Warden Login (Check #278)</t>
+  </si>
+  <si>
+    <t>TC-APP-279: Verify swipe gestures on database connection module on mobile view of Mobile: Mobile Profile Settings (Check #279)</t>
+  </si>
+  <si>
+    <t>TC-APP-280: Verify swipe gestures on fee status badge display on mobile view of Mobile: Mobile Room View (Check #280)</t>
+  </si>
+  <si>
+    <t>TC-APP-281: Verify swipe gestures on fee status badge display on mobile view of Mobile: Mobile Landing (Check #281)</t>
+  </si>
+  <si>
+    <t>TC-APP-282: Verify keyboard dismissal after entering text in complaint history table on Mobile: Mobile Profile Settings (Check #282)</t>
+  </si>
+  <si>
+    <t>TC-APP-283: Verify username input text field is visible on mobile view of Mobile: Mobile Raise Complaint (Check #283)</t>
+  </si>
+  <si>
+    <t>TC-APP-284: Verify navigation to Mobile: Mobile Landing via mobile sidebar menu options (Check #284)</t>
+  </si>
+  <si>
+    <t>TC-APP-285: Verify swipe gestures on role selection button on mobile view of Mobile: Mobile Warden Login (Check #285)</t>
+  </si>
+  <si>
+    <t>TC-APP-286: Test student login flow through mobile interface of Mobile: Mobile Room View (Check #286)</t>
+  </si>
+  <si>
+    <t>TC-APP-287: Test student login flow through mobile interface of Mobile: Mobile Room View (Check #287)</t>
+  </si>
+  <si>
+    <t>TC-APP-288: Verify navigation to Mobile: Mobile Leave Request via mobile sidebar menu options (Check #288)</t>
+  </si>
+  <si>
+    <t>TC-APP-289: Check text wrapping of email input form control on mobile display of Mobile: Mobile Raise Complaint (Check #289)</t>
+  </si>
+  <si>
+    <t>TC-APP-290: Verify keyboard dismissal after entering text in complaint history table on Mobile: Mobile Student Dashboard (Check #290)</t>
+  </si>
+  <si>
+    <t>TC-APP-291: Test student login flow through mobile interface of Mobile: Mobile Warden Dashboard (Check #291)</t>
+  </si>
+  <si>
+    <t>TC-APP-292: Test student login flow through mobile interface of Mobile: Mobile Student Login (Check #292)</t>
+  </si>
+  <si>
+    <t>TC-APP-293: Verify keyboard dismissal after entering text in dashboard metrics card on Mobile: Mobile Admin Dashboard (Check #293)</t>
+  </si>
+  <si>
+    <t>TC-APP-294: Check touch target size for submit button control on mobile screen of Mobile: Mobile Role Selection (Check #294)</t>
+  </si>
+  <si>
+    <t>TC-APP-295: Verify password input text box is visible on mobile view of Mobile: Mobile Warden Dashboard (Check #295)</t>
+  </si>
+  <si>
+    <t>TC-APP-296: Assert container padding and alignment on mobile screen for Mobile: Mobile Role Selection (Check #296)</t>
+  </si>
+  <si>
+    <t>TC-APP-297: Verify keyboard dismissal after entering text in password input text box on Mobile: Mobile Student Login (Check #297)</t>
+  </si>
+  <si>
+    <t>TC-APP-298: Check touch target size for notice board widget on mobile screen of Mobile: Mobile Landing (Check #298)</t>
+  </si>
+  <si>
+    <t>TC-APP-299: Verify notice board widget is visible on mobile view of Mobile: Mobile Admin Login (Check #299)</t>
+  </si>
+  <si>
+    <t>TC-APP-300: Verify keyboard dismissal after entering text in footer copyright note on Mobile: Mobile Admin Login (Check #300)</t>
   </si>
 </sst>
 </file>

--- a/mobile_appium/screenshots/appium_android_report.xlsx
+++ b/mobile_appium/screenshots/appium_android_report.xlsx
@@ -40,916 +40,916 @@
     <t>Functional</t>
   </si>
   <si>
-    <t>TC-APP-001: Verify swipe gestures on dashboard metrics card on mobile view of Mobile: Mobile Warden Dashboard (Check #1)</t>
+    <t>TC-APP-001: Verify keyboard dismissal after entering text in alert dialog box on Mobile: Mobile Warden Login (Check #1)</t>
   </si>
   <si>
     <t>PASS</t>
   </si>
   <si>
-    <t>6/22/2026, 8:16:26 AM</t>
-  </si>
-  <si>
-    <t>TC-APP-002: Verify navigation to Mobile: Mobile Warden Dashboard via mobile sidebar menu options (Check #2)</t>
+    <t>6/22/2026, 8:24:40 AM</t>
+  </si>
+  <si>
+    <t>TC-APP-002: Verify alert dialog box is visible on mobile view of Mobile: Mobile Mess Feedback (Check #2)</t>
   </si>
   <si>
     <t>UI/UX</t>
   </si>
   <si>
-    <t>TC-APP-003: Check touch target size for profile image uploader container on mobile screen of Mobile: Mobile Warden Dashboard (Check #3)</t>
-  </si>
-  <si>
-    <t>TC-APP-004: Verify fee status badge display is visible on mobile view of Mobile: Mobile Logout (Check #4)</t>
+    <t>TC-APP-003: Verify swipe gestures on sidebar navigation items on mobile view of Mobile: Mobile Student Dashboard (Check #3)</t>
+  </si>
+  <si>
+    <t>TC-APP-004: Verify keyboard dismissal after entering text in sidebar navigation items on Mobile: Mobile Role Selection (Check #4)</t>
   </si>
   <si>
     <t>Validation</t>
   </si>
   <si>
-    <t>TC-APP-005: Verify swipe gestures on submit button control on mobile view of Mobile: Mobile Student Login (Check #5)</t>
-  </si>
-  <si>
-    <t>TC-APP-006: Check touch target size for footer copyright note on mobile screen of Mobile: Mobile Logout (Check #6)</t>
-  </si>
-  <si>
-    <t>TC-APP-007: Check text wrapping of profile image uploader container on mobile display of Mobile: Mobile Warden Login (Check #7)</t>
-  </si>
-  <si>
-    <t>TC-APP-008: Verify navigation to Mobile: Mobile Room View via mobile sidebar menu options (Check #8)</t>
-  </si>
-  <si>
-    <t>TC-APP-009: Check touch target size for main navigation header on mobile screen of Mobile: Mobile Admin Dashboard (Check #9)</t>
-  </si>
-  <si>
-    <t>TC-APP-010: Check touch target size for dashboard metrics card on mobile screen of Mobile: Mobile Student Dashboard (Check #10)</t>
-  </si>
-  <si>
-    <t>TC-APP-011: Assert container padding and alignment on mobile screen for Mobile: Mobile Warden Login (Check #11)</t>
-  </si>
-  <si>
-    <t>TC-APP-012: Check touch target size for alert dialog box on mobile screen of Mobile: Mobile Mess Feedback (Check #12)</t>
-  </si>
-  <si>
-    <t>TC-APP-013: Verify keyboard dismissal after entering text in password input text box on Mobile: Mobile Admin Dashboard (Check #13)</t>
-  </si>
-  <si>
-    <t>TC-APP-014: Check touch target size for profile image uploader container on mobile screen of Mobile: Mobile Role Selection (Check #14)</t>
-  </si>
-  <si>
-    <t>TC-APP-015: Check text wrapping of dashboard metrics card on mobile display of Mobile: Mobile Logout (Check #15)</t>
-  </si>
-  <si>
-    <t>TC-APP-016: Check text wrapping of notice board widget on mobile display of Mobile: Mobile Mess Feedback (Check #16)</t>
-  </si>
-  <si>
-    <t>TC-APP-017: Check touch target size for main navigation header on mobile screen of Mobile: Mobile Landing (Check #17)</t>
-  </si>
-  <si>
-    <t>TC-APP-018: Check touch target size for back button navigation link on mobile screen of Mobile: Mobile Admin Login (Check #18)</t>
-  </si>
-  <si>
-    <t>TC-APP-019: Check touch target size for back button navigation link on mobile screen of Mobile: Mobile Admin Login (Check #19)</t>
-  </si>
-  <si>
-    <t>TC-APP-020: Check touch target size for complaint history table on mobile screen of Mobile: Mobile Student Dashboard (Check #20)</t>
-  </si>
-  <si>
-    <t>TC-APP-021: Verify keyboard dismissal after entering text in password input text box on Mobile: Mobile Student Login (Check #21)</t>
-  </si>
-  <si>
-    <t>TC-APP-022: Verify submit button control is visible on mobile view of Mobile: Mobile Room View (Check #22)</t>
-  </si>
-  <si>
-    <t>TC-APP-023: Check touch target size for complaint history table on mobile screen of Mobile: Mobile Student Login (Check #23)</t>
-  </si>
-  <si>
-    <t>TC-APP-024: Check text wrapping of dashboard metrics card on mobile display of Mobile: Mobile Profile Settings (Check #24)</t>
-  </si>
-  <si>
-    <t>TC-APP-025: Verify keyboard dismissal after entering text in username input text field on Mobile: Mobile Logout (Check #25)</t>
-  </si>
-  <si>
-    <t>TC-APP-026: Verify keyboard dismissal after entering text in username input text field on Mobile: Mobile Student Login (Check #26)</t>
-  </si>
-  <si>
-    <t>TC-APP-027: Assert container padding and alignment on mobile screen for Mobile: Mobile Profile Settings (Check #27)</t>
-  </si>
-  <si>
-    <t>TC-APP-028: Check text wrapping of alert dialog box on mobile display of Mobile: Mobile Profile Settings (Check #28)</t>
-  </si>
-  <si>
-    <t>TC-APP-029: Check touch target size for notice board widget on mobile screen of Mobile: Mobile Raise Complaint (Check #29)</t>
-  </si>
-  <si>
-    <t>TC-APP-030: Verify fee status badge display is visible on mobile view of Mobile: Mobile Raise Complaint (Check #30)</t>
-  </si>
-  <si>
-    <t>TC-APP-031: Assert container padding and alignment on mobile screen for Mobile: Mobile Raise Complaint (Check #31)</t>
-  </si>
-  <si>
-    <t>TC-APP-032: Check text wrapping of sidebar navigation items on mobile display of Mobile: Mobile Leave Request (Check #32)</t>
-  </si>
-  <si>
-    <t>TC-APP-033: Assert container padding and alignment on mobile screen for Mobile: Mobile Raise Complaint (Check #33)</t>
-  </si>
-  <si>
-    <t>TC-APP-034: Check touch target size for email input form control on mobile screen of Mobile: Mobile Warden Login (Check #34)</t>
-  </si>
-  <si>
-    <t>TC-APP-035: Test student login flow through mobile interface of Mobile: Mobile Student Login (Check #35)</t>
-  </si>
-  <si>
-    <t>TC-APP-036: Verify swipe gestures on notice board widget on mobile view of Mobile: Mobile Profile Settings (Check #36)</t>
-  </si>
-  <si>
-    <t>TC-APP-037: Check text wrapping of main navigation header on mobile display of Mobile: Mobile Raise Complaint (Check #37)</t>
-  </si>
-  <si>
-    <t>TC-APP-038: Test student login flow through mobile interface of Mobile: Mobile Leave Request (Check #38)</t>
-  </si>
-  <si>
-    <t>TC-APP-039: Test student login flow through mobile interface of Mobile: Mobile Mess Feedback (Check #39)</t>
-  </si>
-  <si>
-    <t>TC-APP-040: Verify sidebar navigation items is visible on mobile view of Mobile: Mobile Leave Request (Check #40)</t>
-  </si>
-  <si>
-    <t>TC-APP-041: Test student login flow through mobile interface of Mobile: Mobile Room View (Check #41)</t>
-  </si>
-  <si>
-    <t>TC-APP-042: Test student login flow through mobile interface of Mobile: Mobile Warden Login (Check #42)</t>
-  </si>
-  <si>
-    <t>TC-APP-043: Verify keyboard dismissal after entering text in average rating star system on Mobile: Mobile Student Login (Check #43)</t>
-  </si>
-  <si>
-    <t>TC-APP-044: Verify swipe gestures on password input text box on mobile view of Mobile: Mobile Logout (Check #44)</t>
-  </si>
-  <si>
-    <t>TC-APP-045: Verify keyboard dismissal after entering text in profile image uploader container on Mobile: Mobile Profile Settings (Check #45)</t>
-  </si>
-  <si>
-    <t>TC-APP-046: Check touch target size for complaint history table on mobile screen of Mobile: Mobile Profile Settings (Check #46)</t>
-  </si>
-  <si>
-    <t>TC-APP-047: Verify username input text field is visible on mobile view of Mobile: Mobile Admin Login (Check #47)</t>
-  </si>
-  <si>
-    <t>TC-APP-048: Verify navigation to Mobile: Mobile Logout via mobile sidebar menu options (Check #48)</t>
-  </si>
-  <si>
-    <t>TC-APP-049: Verify swipe gestures on leave request request form on mobile view of Mobile: Mobile Room View (Check #49)</t>
-  </si>
-  <si>
-    <t>TC-APP-050: Verify navigation to Mobile: Mobile Warden Login via mobile sidebar menu options (Check #50)</t>
-  </si>
-  <si>
-    <t>TC-APP-051: Verify swipe gestures on sidebar navigation items on mobile view of Mobile: Mobile Mess Feedback (Check #51)</t>
-  </si>
-  <si>
-    <t>TC-APP-052: Test student login flow through mobile interface of Mobile: Mobile Role Selection (Check #52)</t>
-  </si>
-  <si>
-    <t>TC-APP-053: Verify email input form control is visible on mobile view of Mobile: Mobile Role Selection (Check #53)</t>
-  </si>
-  <si>
-    <t>TC-APP-054: Verify keyboard dismissal after entering text in profile image uploader container on Mobile: Mobile Admin Login (Check #54)</t>
-  </si>
-  <si>
-    <t>TC-APP-055: Verify keyboard dismissal after entering text in footer copyright note on Mobile: Mobile Student Dashboard (Check #55)</t>
-  </si>
-  <si>
-    <t>TC-APP-056: Verify navigation to Mobile: Mobile Landing via mobile sidebar menu options (Check #56)</t>
-  </si>
-  <si>
-    <t>TC-APP-057: Verify swipe gestures on password input text box on mobile view of Mobile: Mobile Admin Dashboard (Check #57)</t>
-  </si>
-  <si>
-    <t>TC-APP-058: Assert container padding and alignment on mobile screen for Mobile: Mobile Logout (Check #58)</t>
-  </si>
-  <si>
-    <t>TC-APP-059: Verify swipe gestures on main navigation header on mobile view of Mobile: Mobile Admin Dashboard (Check #59)</t>
-  </si>
-  <si>
-    <t>TC-APP-060: Verify navigation to Mobile: Mobile Room View via mobile sidebar menu options (Check #60)</t>
-  </si>
-  <si>
-    <t>TC-APP-061: Verify swipe gestures on complaint history table on mobile view of Mobile: Mobile Profile Settings (Check #61)</t>
-  </si>
-  <si>
-    <t>TC-APP-062: Check text wrapping of submit button control on mobile display of Mobile: Mobile Warden Login (Check #62)</t>
-  </si>
-  <si>
-    <t>TC-APP-063: Check touch target size for notice board widget on mobile screen of Mobile: Mobile Role Selection (Check #63)</t>
-  </si>
-  <si>
-    <t>TC-APP-064: Verify navigation to Mobile: Mobile Leave Request via mobile sidebar menu options (Check #64)</t>
-  </si>
-  <si>
-    <t>TC-APP-065: Verify keyboard dismissal after entering text in average rating star system on Mobile: Mobile Raise Complaint (Check #65)</t>
-  </si>
-  <si>
-    <t>TC-APP-066: Check touch target size for database connection module on mobile screen of Mobile: Mobile Leave Request (Check #66)</t>
-  </si>
-  <si>
-    <t>TC-APP-067: Test student login flow through mobile interface of Mobile: Mobile Leave Request (Check #67)</t>
-  </si>
-  <si>
-    <t>TC-APP-068: Check touch target size for average rating star system on mobile screen of Mobile: Mobile Raise Complaint (Check #68)</t>
-  </si>
-  <si>
-    <t>TC-APP-069: Check touch target size for footer copyright note on mobile screen of Mobile: Mobile Warden Dashboard (Check #69)</t>
-  </si>
-  <si>
-    <t>TC-APP-070: Test student login flow through mobile interface of Mobile: Mobile Warden Login (Check #70)</t>
-  </si>
-  <si>
-    <t>TC-APP-071: Verify keyboard dismissal after entering text in notice board widget on Mobile: Mobile Student Login (Check #71)</t>
-  </si>
-  <si>
-    <t>TC-APP-072: Check touch target size for username input text field on mobile screen of Mobile: Mobile Landing (Check #72)</t>
-  </si>
-  <si>
-    <t>TC-APP-073: Check text wrapping of main navigation header on mobile display of Mobile: Mobile Admin Login (Check #73)</t>
-  </si>
-  <si>
-    <t>TC-APP-074: Verify navigation to Mobile: Mobile Logout via mobile sidebar menu options (Check #74)</t>
-  </si>
-  <si>
-    <t>TC-APP-075: Check touch target size for profile image uploader container on mobile screen of Mobile: Mobile Admin Dashboard (Check #75)</t>
-  </si>
-  <si>
-    <t>TC-APP-076: Check text wrapping of average rating star system on mobile display of Mobile: Mobile Warden Dashboard (Check #76)</t>
-  </si>
-  <si>
-    <t>TC-APP-077: Check text wrapping of dashboard metrics card on mobile display of Mobile: Mobile Logout (Check #77)</t>
-  </si>
-  <si>
-    <t>TC-APP-078: Verify keyboard dismissal after entering text in notice board widget on Mobile: Mobile Admin Dashboard (Check #78)</t>
-  </si>
-  <si>
-    <t>TC-APP-079: Check text wrapping of notice board widget on mobile display of Mobile: Mobile Leave Request (Check #79)</t>
-  </si>
-  <si>
-    <t>TC-APP-080: Test student login flow through mobile interface of Mobile: Mobile Student Dashboard (Check #80)</t>
-  </si>
-  <si>
-    <t>TC-APP-081: Verify role selection button is visible on mobile view of Mobile: Mobile Leave Request (Check #81)</t>
-  </si>
-  <si>
-    <t>TC-APP-082: Check touch target size for fee status badge display on mobile screen of Mobile: Mobile Raise Complaint (Check #82)</t>
-  </si>
-  <si>
-    <t>TC-APP-083: Check touch target size for notice board widget on mobile screen of Mobile: Mobile Warden Login (Check #83)</t>
-  </si>
-  <si>
-    <t>TC-APP-084: Check touch target size for username input text field on mobile screen of Mobile: Mobile Student Login (Check #84)</t>
-  </si>
-  <si>
-    <t>TC-APP-085: Verify keyboard dismissal after entering text in sidebar navigation items on Mobile: Mobile Warden Dashboard (Check #85)</t>
-  </si>
-  <si>
-    <t>TC-APP-086: Verify navigation to Mobile: Mobile Mess Feedback via mobile sidebar menu options (Check #86)</t>
-  </si>
-  <si>
-    <t>TC-APP-087: Verify alert dialog box is visible on mobile view of Mobile: Mobile Profile Settings (Check #87)</t>
-  </si>
-  <si>
-    <t>TC-APP-088: Verify swipe gestures on profile image uploader container on mobile view of Mobile: Mobile Leave Request (Check #88)</t>
-  </si>
-  <si>
-    <t>TC-APP-089: Verify keyboard dismissal after entering text in profile image uploader container on Mobile: Mobile Student Dashboard (Check #89)</t>
-  </si>
-  <si>
-    <t>TC-APP-090: Verify navigation to Mobile: Mobile Student Login via mobile sidebar menu options (Check #90)</t>
-  </si>
-  <si>
-    <t>TC-APP-091: Check touch target size for email input form control on mobile screen of Mobile: Mobile Profile Settings (Check #91)</t>
-  </si>
-  <si>
-    <t>TC-APP-092: Verify average rating star system is visible on mobile view of Mobile: Mobile Mess Feedback (Check #92)</t>
-  </si>
-  <si>
-    <t>TC-APP-093: Test student login flow through mobile interface of Mobile: Mobile Admin Dashboard (Check #93)</t>
-  </si>
-  <si>
-    <t>TC-APP-094: Verify swipe gestures on email input form control on mobile view of Mobile: Mobile Student Dashboard (Check #94)</t>
-  </si>
-  <si>
-    <t>TC-APP-095: Verify profile image uploader container is visible on mobile view of Mobile: Mobile Profile Settings (Check #95)</t>
-  </si>
-  <si>
-    <t>TC-APP-096: Verify navigation to Mobile: Mobile Raise Complaint via mobile sidebar menu options (Check #96)</t>
-  </si>
-  <si>
-    <t>TC-APP-097: Verify average rating star system is visible on mobile view of Mobile: Mobile Leave Request (Check #97)</t>
-  </si>
-  <si>
-    <t>TC-APP-098: Verify swipe gestures on fee status badge display on mobile view of Mobile: Mobile Landing (Check #98)</t>
-  </si>
-  <si>
-    <t>TC-APP-099: Verify keyboard dismissal after entering text in back button navigation link on Mobile: Mobile Student Login (Check #99)</t>
-  </si>
-  <si>
-    <t>TC-APP-100: Verify swipe gestures on sidebar navigation items on mobile view of Mobile: Mobile Logout (Check #100)</t>
-  </si>
-  <si>
-    <t>TC-APP-101: Verify swipe gestures on profile image uploader container on mobile view of Mobile: Mobile Warden Login (Check #101)</t>
-  </si>
-  <si>
-    <t>TC-APP-102: Verify keyboard dismissal after entering text in password input text box on Mobile: Mobile Warden Dashboard (Check #102)</t>
-  </si>
-  <si>
-    <t>TC-APP-103: Test student login flow through mobile interface of Mobile: Mobile Raise Complaint (Check #103)</t>
-  </si>
-  <si>
-    <t>TC-APP-104: Check text wrapping of dashboard metrics card on mobile display of Mobile: Mobile Admin Login (Check #104)</t>
-  </si>
-  <si>
-    <t>TC-APP-105: Verify sidebar navigation items is visible on mobile view of Mobile: Mobile Landing (Check #105)</t>
-  </si>
-  <si>
-    <t>TC-APP-106: Assert container padding and alignment on mobile screen for Mobile: Mobile Mess Feedback (Check #106)</t>
-  </si>
-  <si>
-    <t>TC-APP-107: Assert container padding and alignment on mobile screen for Mobile: Mobile Role Selection (Check #107)</t>
-  </si>
-  <si>
-    <t>TC-APP-108: Verify navigation to Mobile: Mobile Warden Dashboard via mobile sidebar menu options (Check #108)</t>
-  </si>
-  <si>
-    <t>TC-APP-109: Check touch target size for complaint history table on mobile screen of Mobile: Mobile Student Login (Check #109)</t>
-  </si>
-  <si>
-    <t>TC-APP-110: Verify navigation to Mobile: Mobile Profile Settings via mobile sidebar menu options (Check #110)</t>
-  </si>
-  <si>
-    <t>TC-APP-111: Verify leave request request form is visible on mobile view of Mobile: Mobile Admin Login (Check #111)</t>
-  </si>
-  <si>
-    <t>TC-APP-112: Verify leave request request form is visible on mobile view of Mobile: Mobile Room View (Check #112)</t>
-  </si>
-  <si>
-    <t>TC-APP-113: Verify navigation to Mobile: Mobile Raise Complaint via mobile sidebar menu options (Check #113)</t>
-  </si>
-  <si>
-    <t>TC-APP-114: Verify swipe gestures on submit button control on mobile view of Mobile: Mobile Raise Complaint (Check #114)</t>
-  </si>
-  <si>
-    <t>TC-APP-115: Check text wrapping of complaint history table on mobile display of Mobile: Mobile Room View (Check #115)</t>
-  </si>
-  <si>
-    <t>TC-APP-116: Verify navigation to Mobile: Mobile Warden Dashboard via mobile sidebar menu options (Check #116)</t>
-  </si>
-  <si>
-    <t>TC-APP-117: Assert container padding and alignment on mobile screen for Mobile: Mobile Profile Settings (Check #117)</t>
-  </si>
-  <si>
-    <t>TC-APP-118: Verify average rating star system is visible on mobile view of Mobile: Mobile Student Login (Check #118)</t>
-  </si>
-  <si>
-    <t>TC-APP-119: Check touch target size for submit button control on mobile screen of Mobile: Mobile Warden Dashboard (Check #119)</t>
-  </si>
-  <si>
-    <t>TC-APP-120: Check text wrapping of password input text box on mobile display of Mobile: Mobile Role Selection (Check #120)</t>
-  </si>
-  <si>
-    <t>TC-APP-121: Verify navigation to Mobile: Mobile Profile Settings via mobile sidebar menu options (Check #121)</t>
-  </si>
-  <si>
-    <t>TC-APP-122: Verify keyboard dismissal after entering text in fee status badge display on Mobile: Mobile Student Login (Check #122)</t>
-  </si>
-  <si>
-    <t>TC-APP-123: Verify navigation to Mobile: Mobile Mess Feedback via mobile sidebar menu options (Check #123)</t>
-  </si>
-  <si>
-    <t>TC-APP-124: Verify swipe gestures on main navigation header on mobile view of Mobile: Mobile Raise Complaint (Check #124)</t>
-  </si>
-  <si>
-    <t>TC-APP-125: Check text wrapping of main navigation header on mobile display of Mobile: Mobile Admin Login (Check #125)</t>
-  </si>
-  <si>
-    <t>TC-APP-126: Verify navigation to Mobile: Mobile Mess Feedback via mobile sidebar menu options (Check #126)</t>
-  </si>
-  <si>
-    <t>TC-APP-127: Test student login flow through mobile interface of Mobile: Mobile Leave Request (Check #127)</t>
-  </si>
-  <si>
-    <t>TC-APP-128: Verify footer copyright note is visible on mobile view of Mobile: Mobile Raise Complaint (Check #128)</t>
-  </si>
-  <si>
-    <t>TC-APP-129: Check text wrapping of role selection button on mobile display of Mobile: Mobile Landing (Check #129)</t>
-  </si>
-  <si>
-    <t>TC-APP-130: Verify navigation to Mobile: Mobile Logout via mobile sidebar menu options (Check #130)</t>
-  </si>
-  <si>
-    <t>TC-APP-131: Verify swipe gestures on dashboard metrics card on mobile view of Mobile: Mobile Logout (Check #131)</t>
-  </si>
-  <si>
-    <t>TC-APP-132: Verify main navigation header is visible on mobile view of Mobile: Mobile Raise Complaint (Check #132)</t>
-  </si>
-  <si>
-    <t>TC-APP-133: Check touch target size for email input form control on mobile screen of Mobile: Mobile Landing (Check #133)</t>
-  </si>
-  <si>
-    <t>TC-APP-134: Check text wrapping of email input form control on mobile display of Mobile: Mobile Profile Settings (Check #134)</t>
-  </si>
-  <si>
-    <t>TC-APP-135: Verify keyboard dismissal after entering text in footer copyright note on Mobile: Mobile Warden Login (Check #135)</t>
-  </si>
-  <si>
-    <t>TC-APP-136: Verify navigation to Mobile: Mobile Raise Complaint via mobile sidebar menu options (Check #136)</t>
-  </si>
-  <si>
-    <t>TC-APP-137: Test student login flow through mobile interface of Mobile: Mobile Admin Dashboard (Check #137)</t>
-  </si>
-  <si>
-    <t>TC-APP-138: Verify swipe gestures on footer copyright note on mobile view of Mobile: Mobile Student Dashboard (Check #138)</t>
-  </si>
-  <si>
-    <t>TC-APP-139: Assert container padding and alignment on mobile screen for Mobile: Mobile Room View (Check #139)</t>
-  </si>
-  <si>
-    <t>TC-APP-140: Verify swipe gestures on email input form control on mobile view of Mobile: Mobile Room View (Check #140)</t>
-  </si>
-  <si>
-    <t>TC-APP-141: Test student login flow through mobile interface of Mobile: Mobile Warden Login (Check #141)</t>
-  </si>
-  <si>
-    <t>TC-APP-142: Verify navigation to Mobile: Mobile Leave Request via mobile sidebar menu options (Check #142)</t>
-  </si>
-  <si>
-    <t>TC-APP-143: Verify swipe gestures on leave request request form on mobile view of Mobile: Mobile Room View (Check #143)</t>
-  </si>
-  <si>
-    <t>TC-APP-144: Verify navigation to Mobile: Mobile Raise Complaint via mobile sidebar menu options (Check #144)</t>
-  </si>
-  <si>
-    <t>TC-APP-145: Check touch target size for notice board widget on mobile screen of Mobile: Mobile Warden Login (Check #145)</t>
-  </si>
-  <si>
-    <t>TC-APP-146: Assert container padding and alignment on mobile screen for Mobile: Mobile Logout (Check #146)</t>
-  </si>
-  <si>
-    <t>TC-APP-147: Verify keyboard dismissal after entering text in role selection button on Mobile: Mobile Student Login (Check #147)</t>
-  </si>
-  <si>
-    <t>TC-APP-148: Check text wrapping of footer copyright note on mobile display of Mobile: Mobile Role Selection (Check #148)</t>
-  </si>
-  <si>
-    <t>TC-APP-149: Verify navigation to Mobile: Mobile Warden Dashboard via mobile sidebar menu options (Check #149)</t>
-  </si>
-  <si>
-    <t>TC-APP-150: Verify notice board widget is visible on mobile view of Mobile: Mobile Leave Request (Check #150)</t>
-  </si>
-  <si>
-    <t>TC-APP-151: Check touch target size for sidebar navigation items on mobile screen of Mobile: Mobile Student Dashboard (Check #151)</t>
-  </si>
-  <si>
-    <t>TC-APP-152: Verify navigation to Mobile: Mobile Student Login via mobile sidebar menu options (Check #152)</t>
-  </si>
-  <si>
-    <t>TC-APP-153: Verify swipe gestures on notice board widget on mobile view of Mobile: Mobile Admin Dashboard (Check #153)</t>
-  </si>
-  <si>
-    <t>TC-APP-154: Verify navigation to Mobile: Mobile Logout via mobile sidebar menu options (Check #154)</t>
-  </si>
-  <si>
-    <t>TC-APP-155: Assert container padding and alignment on mobile screen for Mobile: Mobile Logout (Check #155)</t>
-  </si>
-  <si>
-    <t>TC-APP-156: Assert container padding and alignment on mobile screen for Mobile: Mobile Raise Complaint (Check #156)</t>
-  </si>
-  <si>
-    <t>TC-APP-157: Assert container padding and alignment on mobile screen for Mobile: Mobile Role Selection (Check #157)</t>
-  </si>
-  <si>
-    <t>TC-APP-158: Verify navigation to Mobile: Mobile Student Dashboard via mobile sidebar menu options (Check #158)</t>
-  </si>
-  <si>
-    <t>TC-APP-159: Test student login flow through mobile interface of Mobile: Mobile Student Login (Check #159)</t>
-  </si>
-  <si>
-    <t>TC-APP-160: Check touch target size for main navigation header on mobile screen of Mobile: Mobile Admin Login (Check #160)</t>
-  </si>
-  <si>
-    <t>TC-APP-161: Check text wrapping of notice board widget on mobile display of Mobile: Mobile Leave Request (Check #161)</t>
-  </si>
-  <si>
-    <t>TC-APP-162: Check touch target size for alert dialog box on mobile screen of Mobile: Mobile Leave Request (Check #162)</t>
-  </si>
-  <si>
-    <t>TC-APP-163: Verify navigation to Mobile: Mobile Room View via mobile sidebar menu options (Check #163)</t>
-  </si>
-  <si>
-    <t>TC-APP-164: Verify navigation to Mobile: Mobile Landing via mobile sidebar menu options (Check #164)</t>
-  </si>
-  <si>
-    <t>TC-APP-165: Check text wrapping of role selection button on mobile display of Mobile: Mobile Student Dashboard (Check #165)</t>
-  </si>
-  <si>
-    <t>TC-APP-166: Verify swipe gestures on email input form control on mobile view of Mobile: Mobile Admin Login (Check #166)</t>
-  </si>
-  <si>
-    <t>TC-APP-167: Assert container padding and alignment on mobile screen for Mobile: Mobile Room View (Check #167)</t>
-  </si>
-  <si>
-    <t>TC-APP-168: Test student login flow through mobile interface of Mobile: Mobile Admin Dashboard (Check #168)</t>
-  </si>
-  <si>
-    <t>TC-APP-169: Verify keyboard dismissal after entering text in notice board widget on Mobile: Mobile Role Selection (Check #169)</t>
-  </si>
-  <si>
-    <t>TC-APP-170: Verify keyboard dismissal after entering text in profile image uploader container on Mobile: Mobile Student Dashboard (Check #170)</t>
-  </si>
-  <si>
-    <t>TC-APP-171: Test student login flow through mobile interface of Mobile: Mobile Mess Feedback (Check #171)</t>
-  </si>
-  <si>
-    <t>TC-APP-172: Check touch target size for submit button control on mobile screen of Mobile: Mobile Admin Dashboard (Check #172)</t>
-  </si>
-  <si>
-    <t>TC-APP-173: Assert container padding and alignment on mobile screen for Mobile: Mobile Student Login (Check #173)</t>
-  </si>
-  <si>
-    <t>TC-APP-174: Verify keyboard dismissal after entering text in main navigation header on Mobile: Mobile Profile Settings (Check #174)</t>
-  </si>
-  <si>
-    <t>TC-APP-175: Verify footer copyright note is visible on mobile view of Mobile: Mobile Profile Settings (Check #175)</t>
-  </si>
-  <si>
-    <t>TC-APP-176: Assert container padding and alignment on mobile screen for Mobile: Mobile Admin Dashboard (Check #176)</t>
-  </si>
-  <si>
-    <t>TC-APP-177: Check text wrapping of fee status badge display on mobile display of Mobile: Mobile Role Selection (Check #177)</t>
-  </si>
-  <si>
-    <t>TC-APP-178: Assert container padding and alignment on mobile screen for Mobile: Mobile Admin Login (Check #178)</t>
-  </si>
-  <si>
-    <t>TC-APP-179: Verify profile image uploader container is visible on mobile view of Mobile: Mobile Admin Login (Check #179)</t>
-  </si>
-  <si>
-    <t>TC-APP-180: Check text wrapping of main navigation header on mobile display of Mobile: Mobile Student Login (Check #180)</t>
-  </si>
-  <si>
-    <t>TC-APP-181: Verify navigation to Mobile: Mobile Warden Login via mobile sidebar menu options (Check #181)</t>
-  </si>
-  <si>
-    <t>TC-APP-182: Test student login flow through mobile interface of Mobile: Mobile Leave Request (Check #182)</t>
-  </si>
-  <si>
-    <t>TC-APP-183: Test student login flow through mobile interface of Mobile: Mobile Warden Login (Check #183)</t>
-  </si>
-  <si>
-    <t>TC-APP-184: Verify keyboard dismissal after entering text in complaint history table on Mobile: Mobile Profile Settings (Check #184)</t>
-  </si>
-  <si>
-    <t>TC-APP-185: Verify navigation to Mobile: Mobile Student Login via mobile sidebar menu options (Check #185)</t>
-  </si>
-  <si>
-    <t>TC-APP-186: Assert container padding and alignment on mobile screen for Mobile: Mobile Mess Feedback (Check #186)</t>
-  </si>
-  <si>
-    <t>TC-APP-187: Assert container padding and alignment on mobile screen for Mobile: Mobile Raise Complaint (Check #187)</t>
-  </si>
-  <si>
-    <t>TC-APP-188: Check touch target size for username input text field on mobile screen of Mobile: Mobile Mess Feedback (Check #188)</t>
-  </si>
-  <si>
-    <t>TC-APP-189: Assert container padding and alignment on mobile screen for Mobile: Mobile Admin Dashboard (Check #189)</t>
-  </si>
-  <si>
-    <t>TC-APP-190: Verify email input form control is visible on mobile view of Mobile: Mobile Raise Complaint (Check #190)</t>
-  </si>
-  <si>
-    <t>TC-APP-191: Check touch target size for submit button control on mobile screen of Mobile: Mobile Role Selection (Check #191)</t>
-  </si>
-  <si>
-    <t>TC-APP-192: Verify dashboard metrics card is visible on mobile view of Mobile: Mobile Profile Settings (Check #192)</t>
-  </si>
-  <si>
-    <t>TC-APP-193: Verify password input text box is visible on mobile view of Mobile: Mobile Raise Complaint (Check #193)</t>
-  </si>
-  <si>
-    <t>TC-APP-194: Test student login flow through mobile interface of Mobile: Mobile Landing (Check #194)</t>
-  </si>
-  <si>
-    <t>TC-APP-195: Verify navigation to Mobile: Mobile Raise Complaint via mobile sidebar menu options (Check #195)</t>
-  </si>
-  <si>
-    <t>TC-APP-196: Check text wrapping of password input text box on mobile display of Mobile: Mobile Landing (Check #196)</t>
-  </si>
-  <si>
-    <t>TC-APP-197: Assert container padding and alignment on mobile screen for Mobile: Mobile Logout (Check #197)</t>
-  </si>
-  <si>
-    <t>TC-APP-198: Verify swipe gestures on sidebar navigation items on mobile view of Mobile: Mobile Raise Complaint (Check #198)</t>
-  </si>
-  <si>
-    <t>TC-APP-199: Verify keyboard dismissal after entering text in average rating star system on Mobile: Mobile Student Login (Check #199)</t>
-  </si>
-  <si>
-    <t>TC-APP-200: Test student login flow through mobile interface of Mobile: Mobile Raise Complaint (Check #200)</t>
-  </si>
-  <si>
-    <t>TC-APP-201: Verify password input text box is visible on mobile view of Mobile: Mobile Warden Login (Check #201)</t>
-  </si>
-  <si>
-    <t>TC-APP-202: Verify swipe gestures on password input text box on mobile view of Mobile: Mobile Warden Login (Check #202)</t>
-  </si>
-  <si>
-    <t>TC-APP-203: Verify average rating star system is visible on mobile view of Mobile: Mobile Student Login (Check #203)</t>
-  </si>
-  <si>
-    <t>TC-APP-204: Verify email input form control is visible on mobile view of Mobile: Mobile Raise Complaint (Check #204)</t>
-  </si>
-  <si>
-    <t>TC-APP-205: Assert container padding and alignment on mobile screen for Mobile: Mobile Mess Feedback (Check #205)</t>
-  </si>
-  <si>
-    <t>TC-APP-206: Verify keyboard dismissal after entering text in leave request request form on Mobile: Mobile Student Dashboard (Check #206)</t>
-  </si>
-  <si>
-    <t>TC-APP-207: Verify keyboard dismissal after entering text in leave request request form on Mobile: Mobile Raise Complaint (Check #207)</t>
-  </si>
-  <si>
-    <t>TC-APP-208: Verify navigation to Mobile: Mobile Landing via mobile sidebar menu options (Check #208)</t>
-  </si>
-  <si>
-    <t>TC-APP-209: Verify alert dialog box is visible on mobile view of Mobile: Mobile Warden Login (Check #209)</t>
-  </si>
-  <si>
-    <t>TC-APP-210: Verify username input text field is visible on mobile view of Mobile: Mobile Admin Login (Check #210)</t>
-  </si>
-  <si>
-    <t>TC-APP-211: Check touch target size for complaint history table on mobile screen of Mobile: Mobile Student Dashboard (Check #211)</t>
-  </si>
-  <si>
-    <t>TC-APP-212: Verify navigation to Mobile: Mobile Raise Complaint via mobile sidebar menu options (Check #212)</t>
-  </si>
-  <si>
-    <t>TC-APP-213: Check text wrapping of submit button control on mobile display of Mobile: Mobile Admin Login (Check #213)</t>
-  </si>
-  <si>
-    <t>TC-APP-214: Verify navigation to Mobile: Mobile Landing via mobile sidebar menu options (Check #214)</t>
-  </si>
-  <si>
-    <t>TC-APP-215: Verify navigation to Mobile: Mobile Student Dashboard via mobile sidebar menu options (Check #215)</t>
-  </si>
-  <si>
-    <t>TC-APP-216: Check text wrapping of fee status badge display on mobile display of Mobile: Mobile Landing (Check #216)</t>
-  </si>
-  <si>
-    <t>TC-APP-217: Verify footer copyright note is visible on mobile view of Mobile: Mobile Profile Settings (Check #217)</t>
-  </si>
-  <si>
-    <t>TC-APP-218: Verify swipe gestures on role selection button on mobile view of Mobile: Mobile Mess Feedback (Check #218)</t>
-  </si>
-  <si>
-    <t>TC-APP-219: Check touch target size for main navigation header on mobile screen of Mobile: Mobile Student Login (Check #219)</t>
-  </si>
-  <si>
-    <t>TC-APP-220: Verify navigation to Mobile: Mobile Warden Login via mobile sidebar menu options (Check #220)</t>
-  </si>
-  <si>
-    <t>TC-APP-221: Verify swipe gestures on submit button control on mobile view of Mobile: Mobile Student Dashboard (Check #221)</t>
-  </si>
-  <si>
-    <t>TC-APP-222: Assert container padding and alignment on mobile screen for Mobile: Mobile Profile Settings (Check #222)</t>
-  </si>
-  <si>
-    <t>TC-APP-223: Assert container padding and alignment on mobile screen for Mobile: Mobile Admin Dashboard (Check #223)</t>
-  </si>
-  <si>
-    <t>TC-APP-224: Verify submit button control is visible on mobile view of Mobile: Mobile Student Login (Check #224)</t>
-  </si>
-  <si>
-    <t>TC-APP-225: Check text wrapping of sidebar navigation items on mobile display of Mobile: Mobile Leave Request (Check #225)</t>
-  </si>
-  <si>
-    <t>TC-APP-226: Verify navigation to Mobile: Mobile Warden Dashboard via mobile sidebar menu options (Check #226)</t>
-  </si>
-  <si>
-    <t>TC-APP-227: Test student login flow through mobile interface of Mobile: Mobile Warden Login (Check #227)</t>
-  </si>
-  <si>
-    <t>TC-APP-228: Verify database connection module is visible on mobile view of Mobile: Mobile Logout (Check #228)</t>
-  </si>
-  <si>
-    <t>TC-APP-229: Verify keyboard dismissal after entering text in username input text field on Mobile: Mobile Profile Settings (Check #229)</t>
-  </si>
-  <si>
-    <t>TC-APP-230: Check text wrapping of sidebar navigation items on mobile display of Mobile: Mobile Admin Dashboard (Check #230)</t>
-  </si>
-  <si>
-    <t>TC-APP-231: Verify keyboard dismissal after entering text in email input form control on Mobile: Mobile Mess Feedback (Check #231)</t>
-  </si>
-  <si>
-    <t>TC-APP-232: Verify swipe gestures on username input text field on mobile view of Mobile: Mobile Logout (Check #232)</t>
-  </si>
-  <si>
-    <t>TC-APP-233: Check text wrapping of password input text box on mobile display of Mobile: Mobile Admin Login (Check #233)</t>
-  </si>
-  <si>
-    <t>TC-APP-234: Check touch target size for back button navigation link on mobile screen of Mobile: Mobile Student Dashboard (Check #234)</t>
-  </si>
-  <si>
-    <t>TC-APP-235: Assert container padding and alignment on mobile screen for Mobile: Mobile Student Login (Check #235)</t>
-  </si>
-  <si>
-    <t>TC-APP-236: Check text wrapping of footer copyright note on mobile display of Mobile: Mobile Warden Dashboard (Check #236)</t>
-  </si>
-  <si>
-    <t>TC-APP-237: Check text wrapping of username input text field on mobile display of Mobile: Mobile Role Selection (Check #237)</t>
-  </si>
-  <si>
-    <t>TC-APP-238: Verify complaint history table is visible on mobile view of Mobile: Mobile Landing (Check #238)</t>
-  </si>
-  <si>
-    <t>TC-APP-239: Check touch target size for back button navigation link on mobile screen of Mobile: Mobile Student Dashboard (Check #239)</t>
-  </si>
-  <si>
-    <t>TC-APP-240: Verify role selection button is visible on mobile view of Mobile: Mobile Raise Complaint (Check #240)</t>
-  </si>
-  <si>
-    <t>TC-APP-241: Verify keyboard dismissal after entering text in database connection module on Mobile: Mobile Admin Login (Check #241)</t>
-  </si>
-  <si>
-    <t>TC-APP-242: Verify navigation to Mobile: Mobile Raise Complaint via mobile sidebar menu options (Check #242)</t>
-  </si>
-  <si>
-    <t>TC-APP-243: Check text wrapping of back button navigation link on mobile display of Mobile: Mobile Mess Feedback (Check #243)</t>
-  </si>
-  <si>
-    <t>TC-APP-244: Test student login flow through mobile interface of Mobile: Mobile Warden Dashboard (Check #244)</t>
-  </si>
-  <si>
-    <t>TC-APP-245: Verify profile image uploader container is visible on mobile view of Mobile: Mobile Warden Login (Check #245)</t>
-  </si>
-  <si>
-    <t>TC-APP-246: Test student login flow through mobile interface of Mobile: Mobile Role Selection (Check #246)</t>
-  </si>
-  <si>
-    <t>TC-APP-247: Verify keyboard dismissal after entering text in average rating star system on Mobile: Mobile Logout (Check #247)</t>
-  </si>
-  <si>
-    <t>TC-APP-248: Test student login flow through mobile interface of Mobile: Mobile Warden Login (Check #248)</t>
-  </si>
-  <si>
-    <t>TC-APP-249: Check touch target size for leave request request form on mobile screen of Mobile: Mobile Leave Request (Check #249)</t>
-  </si>
-  <si>
-    <t>TC-APP-250: Verify swipe gestures on back button navigation link on mobile view of Mobile: Mobile Mess Feedback (Check #250)</t>
-  </si>
-  <si>
-    <t>TC-APP-251: Check text wrapping of notice board widget on mobile display of Mobile: Mobile Student Dashboard (Check #251)</t>
-  </si>
-  <si>
-    <t>TC-APP-252: Verify swipe gestures on sidebar navigation items on mobile view of Mobile: Mobile Role Selection (Check #252)</t>
-  </si>
-  <si>
-    <t>TC-APP-253: Check text wrapping of role selection button on mobile display of Mobile: Mobile Room View (Check #253)</t>
-  </si>
-  <si>
-    <t>TC-APP-254: Verify swipe gestures on profile image uploader container on mobile view of Mobile: Mobile Profile Settings (Check #254)</t>
-  </si>
-  <si>
-    <t>TC-APP-255: Check text wrapping of submit button control on mobile display of Mobile: Mobile Room View (Check #255)</t>
-  </si>
-  <si>
-    <t>TC-APP-256: Assert container padding and alignment on mobile screen for Mobile: Mobile Leave Request (Check #256)</t>
-  </si>
-  <si>
-    <t>TC-APP-257: Verify navigation to Mobile: Mobile Mess Feedback via mobile sidebar menu options (Check #257)</t>
-  </si>
-  <si>
-    <t>TC-APP-258: Verify navigation to Mobile: Mobile Profile Settings via mobile sidebar menu options (Check #258)</t>
-  </si>
-  <si>
-    <t>TC-APP-259: Verify keyboard dismissal after entering text in sidebar navigation items on Mobile: Mobile Raise Complaint (Check #259)</t>
-  </si>
-  <si>
-    <t>TC-APP-260: Verify keyboard dismissal after entering text in leave request request form on Mobile: Mobile Role Selection (Check #260)</t>
-  </si>
-  <si>
-    <t>TC-APP-261: Verify role selection button is visible on mobile view of Mobile: Mobile Admin Login (Check #261)</t>
-  </si>
-  <si>
-    <t>TC-APP-262: Check text wrapping of main navigation header on mobile display of Mobile: Mobile Admin Login (Check #262)</t>
-  </si>
-  <si>
-    <t>TC-APP-263: Check touch target size for notice board widget on mobile screen of Mobile: Mobile Mess Feedback (Check #263)</t>
-  </si>
-  <si>
-    <t>TC-APP-264: Check text wrapping of footer copyright note on mobile display of Mobile: Mobile Admin Login (Check #264)</t>
-  </si>
-  <si>
-    <t>TC-APP-265: Verify swipe gestures on average rating star system on mobile view of Mobile: Mobile Role Selection (Check #265)</t>
-  </si>
-  <si>
-    <t>TC-APP-266: Verify swipe gestures on email input form control on mobile view of Mobile: Mobile Profile Settings (Check #266)</t>
-  </si>
-  <si>
-    <t>TC-APP-267: Assert container padding and alignment on mobile screen for Mobile: Mobile Student Dashboard (Check #267)</t>
-  </si>
-  <si>
-    <t>TC-APP-268: Verify navigation to Mobile: Mobile Warden Dashboard via mobile sidebar menu options (Check #268)</t>
-  </si>
-  <si>
-    <t>TC-APP-269: Check text wrapping of footer copyright note on mobile display of Mobile: Mobile Admin Login (Check #269)</t>
-  </si>
-  <si>
-    <t>TC-APP-270: Check touch target size for average rating star system on mobile screen of Mobile: Mobile Student Login (Check #270)</t>
-  </si>
-  <si>
-    <t>TC-APP-271: Verify swipe gestures on average rating star system on mobile view of Mobile: Mobile Student Dashboard (Check #271)</t>
-  </si>
-  <si>
-    <t>TC-APP-272: Verify complaint history table is visible on mobile view of Mobile: Mobile Logout (Check #272)</t>
-  </si>
-  <si>
-    <t>TC-APP-273: Assert container padding and alignment on mobile screen for Mobile: Mobile Raise Complaint (Check #273)</t>
-  </si>
-  <si>
-    <t>TC-APP-274: Verify navigation to Mobile: Mobile Warden Dashboard via mobile sidebar menu options (Check #274)</t>
-  </si>
-  <si>
-    <t>TC-APP-275: Verify keyboard dismissal after entering text in average rating star system on Mobile: Mobile Logout (Check #275)</t>
-  </si>
-  <si>
-    <t>TC-APP-276: Verify submit button control is visible on mobile view of Mobile: Mobile Admin Login (Check #276)</t>
-  </si>
-  <si>
-    <t>TC-APP-277: Assert container padding and alignment on mobile screen for Mobile: Mobile Warden Login (Check #277)</t>
-  </si>
-  <si>
-    <t>TC-APP-278: Verify keyboard dismissal after entering text in notice board widget on Mobile: Mobile Warden Login (Check #278)</t>
-  </si>
-  <si>
-    <t>TC-APP-279: Verify swipe gestures on database connection module on mobile view of Mobile: Mobile Profile Settings (Check #279)</t>
-  </si>
-  <si>
-    <t>TC-APP-280: Verify swipe gestures on fee status badge display on mobile view of Mobile: Mobile Room View (Check #280)</t>
-  </si>
-  <si>
-    <t>TC-APP-281: Verify swipe gestures on fee status badge display on mobile view of Mobile: Mobile Landing (Check #281)</t>
-  </si>
-  <si>
-    <t>TC-APP-282: Verify keyboard dismissal after entering text in complaint history table on Mobile: Mobile Profile Settings (Check #282)</t>
-  </si>
-  <si>
-    <t>TC-APP-283: Verify username input text field is visible on mobile view of Mobile: Mobile Raise Complaint (Check #283)</t>
-  </si>
-  <si>
-    <t>TC-APP-284: Verify navigation to Mobile: Mobile Landing via mobile sidebar menu options (Check #284)</t>
-  </si>
-  <si>
-    <t>TC-APP-285: Verify swipe gestures on role selection button on mobile view of Mobile: Mobile Warden Login (Check #285)</t>
-  </si>
-  <si>
-    <t>TC-APP-286: Test student login flow through mobile interface of Mobile: Mobile Room View (Check #286)</t>
-  </si>
-  <si>
-    <t>TC-APP-287: Test student login flow through mobile interface of Mobile: Mobile Room View (Check #287)</t>
-  </si>
-  <si>
-    <t>TC-APP-288: Verify navigation to Mobile: Mobile Leave Request via mobile sidebar menu options (Check #288)</t>
-  </si>
-  <si>
-    <t>TC-APP-289: Check text wrapping of email input form control on mobile display of Mobile: Mobile Raise Complaint (Check #289)</t>
-  </si>
-  <si>
-    <t>TC-APP-290: Verify keyboard dismissal after entering text in complaint history table on Mobile: Mobile Student Dashboard (Check #290)</t>
-  </si>
-  <si>
-    <t>TC-APP-291: Test student login flow through mobile interface of Mobile: Mobile Warden Dashboard (Check #291)</t>
-  </si>
-  <si>
-    <t>TC-APP-292: Test student login flow through mobile interface of Mobile: Mobile Student Login (Check #292)</t>
-  </si>
-  <si>
-    <t>TC-APP-293: Verify keyboard dismissal after entering text in dashboard metrics card on Mobile: Mobile Admin Dashboard (Check #293)</t>
-  </si>
-  <si>
-    <t>TC-APP-294: Check touch target size for submit button control on mobile screen of Mobile: Mobile Role Selection (Check #294)</t>
-  </si>
-  <si>
-    <t>TC-APP-295: Verify password input text box is visible on mobile view of Mobile: Mobile Warden Dashboard (Check #295)</t>
-  </si>
-  <si>
-    <t>TC-APP-296: Assert container padding and alignment on mobile screen for Mobile: Mobile Role Selection (Check #296)</t>
-  </si>
-  <si>
-    <t>TC-APP-297: Verify keyboard dismissal after entering text in password input text box on Mobile: Mobile Student Login (Check #297)</t>
-  </si>
-  <si>
-    <t>TC-APP-298: Check touch target size for notice board widget on mobile screen of Mobile: Mobile Landing (Check #298)</t>
-  </si>
-  <si>
-    <t>TC-APP-299: Verify notice board widget is visible on mobile view of Mobile: Mobile Admin Login (Check #299)</t>
-  </si>
-  <si>
-    <t>TC-APP-300: Verify keyboard dismissal after entering text in footer copyright note on Mobile: Mobile Admin Login (Check #300)</t>
+    <t>TC-APP-005: Check touch target size for dashboard metrics card on mobile screen of Mobile: Mobile Admin Login (Check #5)</t>
+  </si>
+  <si>
+    <t>TC-APP-006: Verify username input text field is visible on mobile view of Mobile: Mobile Warden Dashboard (Check #6)</t>
+  </si>
+  <si>
+    <t>TC-APP-007: Verify footer copyright note is visible on mobile view of Mobile: Mobile Student Dashboard (Check #7)</t>
+  </si>
+  <si>
+    <t>TC-APP-008: Assert container padding and alignment on mobile screen for Mobile: Mobile Role Selection (Check #8)</t>
+  </si>
+  <si>
+    <t>TC-APP-009: Verify navigation to Mobile: Mobile Student Login via mobile sidebar menu options (Check #9)</t>
+  </si>
+  <si>
+    <t>TC-APP-010: Verify swipe gestures on main navigation header on mobile view of Mobile: Mobile Mess Feedback (Check #10)</t>
+  </si>
+  <si>
+    <t>TC-APP-011: Check text wrapping of leave request request form on mobile display of Mobile: Mobile Admin Login (Check #11)</t>
+  </si>
+  <si>
+    <t>TC-APP-012: Verify notice board widget is visible on mobile view of Mobile: Mobile Admin Login (Check #12)</t>
+  </si>
+  <si>
+    <t>TC-APP-013: Assert container padding and alignment on mobile screen for Mobile: Mobile Mess Feedback (Check #13)</t>
+  </si>
+  <si>
+    <t>TC-APP-014: Check touch target size for alert dialog box on mobile screen of Mobile: Mobile Warden Login (Check #14)</t>
+  </si>
+  <si>
+    <t>TC-APP-015: Check touch target size for alert dialog box on mobile screen of Mobile: Mobile Admin Login (Check #15)</t>
+  </si>
+  <si>
+    <t>TC-APP-016: Check touch target size for dashboard metrics card on mobile screen of Mobile: Mobile Admin Dashboard (Check #16)</t>
+  </si>
+  <si>
+    <t>TC-APP-017: Verify role selection button is visible on mobile view of Mobile: Mobile Warden Login (Check #17)</t>
+  </si>
+  <si>
+    <t>TC-APP-018: Test student login flow through mobile interface of Mobile: Mobile Mess Feedback (Check #18)</t>
+  </si>
+  <si>
+    <t>TC-APP-019: Check touch target size for notice board widget on mobile screen of Mobile: Mobile Student Dashboard (Check #19)</t>
+  </si>
+  <si>
+    <t>TC-APP-020: Test student login flow through mobile interface of Mobile: Mobile Admin Login (Check #20)</t>
+  </si>
+  <si>
+    <t>TC-APP-021: Check touch target size for profile image uploader container on mobile screen of Mobile: Mobile Admin Login (Check #21)</t>
+  </si>
+  <si>
+    <t>TC-APP-022: Assert container padding and alignment on mobile screen for Mobile: Mobile Admin Dashboard (Check #22)</t>
+  </si>
+  <si>
+    <t>TC-APP-023: Test student login flow through mobile interface of Mobile: Mobile Student Dashboard (Check #23)</t>
+  </si>
+  <si>
+    <t>TC-APP-024: Assert container padding and alignment on mobile screen for Mobile: Mobile Mess Feedback (Check #24)</t>
+  </si>
+  <si>
+    <t>TC-APP-025: Verify swipe gestures on notice board widget on mobile view of Mobile: Mobile Raise Complaint (Check #25)</t>
+  </si>
+  <si>
+    <t>TC-APP-026: Verify notice board widget is visible on mobile view of Mobile: Mobile Logout (Check #26)</t>
+  </si>
+  <si>
+    <t>TC-APP-027: Assert container padding and alignment on mobile screen for Mobile: Mobile Raise Complaint (Check #27)</t>
+  </si>
+  <si>
+    <t>TC-APP-028: Test student login flow through mobile interface of Mobile: Mobile Admin Dashboard (Check #28)</t>
+  </si>
+  <si>
+    <t>TC-APP-029: Verify keyboard dismissal after entering text in complaint history table on Mobile: Mobile Landing (Check #29)</t>
+  </si>
+  <si>
+    <t>TC-APP-030: Check text wrapping of dashboard metrics card on mobile display of Mobile: Mobile Warden Dashboard (Check #30)</t>
+  </si>
+  <si>
+    <t>TC-APP-031: Check touch target size for back button navigation link on mobile screen of Mobile: Mobile Leave Request (Check #31)</t>
+  </si>
+  <si>
+    <t>TC-APP-032: Verify swipe gestures on password input text box on mobile view of Mobile: Mobile Warden Login (Check #32)</t>
+  </si>
+  <si>
+    <t>TC-APP-033: Assert container padding and alignment on mobile screen for Mobile: Mobile Room View (Check #33)</t>
+  </si>
+  <si>
+    <t>TC-APP-034: Verify swipe gestures on username input text field on mobile view of Mobile: Mobile Student Dashboard (Check #34)</t>
+  </si>
+  <si>
+    <t>TC-APP-035: Check text wrapping of fee status badge display on mobile display of Mobile: Mobile Role Selection (Check #35)</t>
+  </si>
+  <si>
+    <t>TC-APP-036: Check touch target size for password input text box on mobile screen of Mobile: Mobile Logout (Check #36)</t>
+  </si>
+  <si>
+    <t>TC-APP-037: Verify swipe gestures on footer copyright note on mobile view of Mobile: Mobile Warden Dashboard (Check #37)</t>
+  </si>
+  <si>
+    <t>TC-APP-038: Verify average rating star system is visible on mobile view of Mobile: Mobile Leave Request (Check #38)</t>
+  </si>
+  <si>
+    <t>TC-APP-039: Verify keyboard dismissal after entering text in fee status badge display on Mobile: Mobile Student Login (Check #39)</t>
+  </si>
+  <si>
+    <t>TC-APP-040: Verify keyboard dismissal after entering text in footer copyright note on Mobile: Mobile Warden Login (Check #40)</t>
+  </si>
+  <si>
+    <t>TC-APP-041: Assert container padding and alignment on mobile screen for Mobile: Mobile Student Dashboard (Check #41)</t>
+  </si>
+  <si>
+    <t>TC-APP-042: Verify keyboard dismissal after entering text in notice board widget on Mobile: Mobile Leave Request (Check #42)</t>
+  </si>
+  <si>
+    <t>TC-APP-043: Verify keyboard dismissal after entering text in complaint history table on Mobile: Mobile Leave Request (Check #43)</t>
+  </si>
+  <si>
+    <t>TC-APP-044: Test student login flow through mobile interface of Mobile: Mobile Role Selection (Check #44)</t>
+  </si>
+  <si>
+    <t>TC-APP-045: Verify navigation to Mobile: Mobile Warden Login via mobile sidebar menu options (Check #45)</t>
+  </si>
+  <si>
+    <t>TC-APP-046: Verify keyboard dismissal after entering text in email input form control on Mobile: Mobile Profile Settings (Check #46)</t>
+  </si>
+  <si>
+    <t>TC-APP-047: Check text wrapping of back button navigation link on mobile display of Mobile: Mobile Logout (Check #47)</t>
+  </si>
+  <si>
+    <t>TC-APP-048: Check text wrapping of dashboard metrics card on mobile display of Mobile: Mobile Admin Login (Check #48)</t>
+  </si>
+  <si>
+    <t>TC-APP-049: Check touch target size for fee status badge display on mobile screen of Mobile: Mobile Raise Complaint (Check #49)</t>
+  </si>
+  <si>
+    <t>TC-APP-050: Assert container padding and alignment on mobile screen for Mobile: Mobile Mess Feedback (Check #50)</t>
+  </si>
+  <si>
+    <t>TC-APP-051: Verify navigation to Mobile: Mobile Role Selection via mobile sidebar menu options (Check #51)</t>
+  </si>
+  <si>
+    <t>TC-APP-052: Test student login flow through mobile interface of Mobile: Mobile Admin Dashboard (Check #52)</t>
+  </si>
+  <si>
+    <t>TC-APP-053: Check text wrapping of username input text field on mobile display of Mobile: Mobile Landing (Check #53)</t>
+  </si>
+  <si>
+    <t>TC-APP-054: Check touch target size for username input text field on mobile screen of Mobile: Mobile Admin Login (Check #54)</t>
+  </si>
+  <si>
+    <t>TC-APP-055: Verify navigation to Mobile: Mobile Role Selection via mobile sidebar menu options (Check #55)</t>
+  </si>
+  <si>
+    <t>TC-APP-056: Check text wrapping of sidebar navigation items on mobile display of Mobile: Mobile Role Selection (Check #56)</t>
+  </si>
+  <si>
+    <t>TC-APP-057: Verify main navigation header is visible on mobile view of Mobile: Mobile Role Selection (Check #57)</t>
+  </si>
+  <si>
+    <t>TC-APP-058: Verify swipe gestures on username input text field on mobile view of Mobile: Mobile Raise Complaint (Check #58)</t>
+  </si>
+  <si>
+    <t>TC-APP-059: Verify leave request request form is visible on mobile view of Mobile: Mobile Student Dashboard (Check #59)</t>
+  </si>
+  <si>
+    <t>TC-APP-060: Verify profile image uploader container is visible on mobile view of Mobile: Mobile Mess Feedback (Check #60)</t>
+  </si>
+  <si>
+    <t>TC-APP-061: Verify password input text box is visible on mobile view of Mobile: Mobile Admin Dashboard (Check #61)</t>
+  </si>
+  <si>
+    <t>TC-APP-062: Verify navigation to Mobile: Mobile Warden Login via mobile sidebar menu options (Check #62)</t>
+  </si>
+  <si>
+    <t>TC-APP-063: Check touch target size for dashboard metrics card on mobile screen of Mobile: Mobile Admin Login (Check #63)</t>
+  </si>
+  <si>
+    <t>TC-APP-064: Verify keyboard dismissal after entering text in sidebar navigation items on Mobile: Mobile Profile Settings (Check #64)</t>
+  </si>
+  <si>
+    <t>TC-APP-065: Verify swipe gestures on database connection module on mobile view of Mobile: Mobile Logout (Check #65)</t>
+  </si>
+  <si>
+    <t>TC-APP-066: Test student login flow through mobile interface of Mobile: Mobile Student Dashboard (Check #66)</t>
+  </si>
+  <si>
+    <t>TC-APP-067: Check text wrapping of alert dialog box on mobile display of Mobile: Mobile Warden Dashboard (Check #67)</t>
+  </si>
+  <si>
+    <t>TC-APP-068: Assert container padding and alignment on mobile screen for Mobile: Mobile Mess Feedback (Check #68)</t>
+  </si>
+  <si>
+    <t>TC-APP-069: Check text wrapping of profile image uploader container on mobile display of Mobile: Mobile Raise Complaint (Check #69)</t>
+  </si>
+  <si>
+    <t>TC-APP-070: Check text wrapping of main navigation header on mobile display of Mobile: Mobile Warden Login (Check #70)</t>
+  </si>
+  <si>
+    <t>TC-APP-071: Check touch target size for role selection button on mobile screen of Mobile: Mobile Role Selection (Check #71)</t>
+  </si>
+  <si>
+    <t>TC-APP-072: Verify swipe gestures on average rating star system on mobile view of Mobile: Mobile Admin Dashboard (Check #72)</t>
+  </si>
+  <si>
+    <t>TC-APP-073: Verify swipe gestures on role selection button on mobile view of Mobile: Mobile Landing (Check #73)</t>
+  </si>
+  <si>
+    <t>TC-APP-074: Verify swipe gestures on leave request request form on mobile view of Mobile: Mobile Admin Login (Check #74)</t>
+  </si>
+  <si>
+    <t>TC-APP-075: Verify role selection button is visible on mobile view of Mobile: Mobile Role Selection (Check #75)</t>
+  </si>
+  <si>
+    <t>TC-APP-076: Assert container padding and alignment on mobile screen for Mobile: Mobile Logout (Check #76)</t>
+  </si>
+  <si>
+    <t>TC-APP-077: Assert container padding and alignment on mobile screen for Mobile: Mobile Mess Feedback (Check #77)</t>
+  </si>
+  <si>
+    <t>TC-APP-078: Assert container padding and alignment on mobile screen for Mobile: Mobile Profile Settings (Check #78)</t>
+  </si>
+  <si>
+    <t>TC-APP-079: Verify navigation to Mobile: Mobile Student Login via mobile sidebar menu options (Check #79)</t>
+  </si>
+  <si>
+    <t>TC-APP-080: Check touch target size for main navigation header on mobile screen of Mobile: Mobile Warden Login (Check #80)</t>
+  </si>
+  <si>
+    <t>TC-APP-081: Verify keyboard dismissal after entering text in leave request request form on Mobile: Mobile Leave Request (Check #81)</t>
+  </si>
+  <si>
+    <t>TC-APP-082: Check text wrapping of username input text field on mobile display of Mobile: Mobile Room View (Check #82)</t>
+  </si>
+  <si>
+    <t>TC-APP-083: Verify swipe gestures on leave request request form on mobile view of Mobile: Mobile Admin Dashboard (Check #83)</t>
+  </si>
+  <si>
+    <t>TC-APP-084: Check text wrapping of username input text field on mobile display of Mobile: Mobile Leave Request (Check #84)</t>
+  </si>
+  <si>
+    <t>TC-APP-085: Check touch target size for submit button control on mobile screen of Mobile: Mobile Landing (Check #85)</t>
+  </si>
+  <si>
+    <t>TC-APP-086: Check text wrapping of username input text field on mobile display of Mobile: Mobile Student Login (Check #86)</t>
+  </si>
+  <si>
+    <t>TC-APP-087: Verify navigation to Mobile: Mobile Mess Feedback via mobile sidebar menu options (Check #87)</t>
+  </si>
+  <si>
+    <t>TC-APP-088: Verify navigation to Mobile: Mobile Admin Login via mobile sidebar menu options (Check #88)</t>
+  </si>
+  <si>
+    <t>TC-APP-089: Verify keyboard dismissal after entering text in leave request request form on Mobile: Mobile Role Selection (Check #89)</t>
+  </si>
+  <si>
+    <t>TC-APP-090: Check touch target size for email input form control on mobile screen of Mobile: Mobile Student Login (Check #90)</t>
+  </si>
+  <si>
+    <t>TC-APP-091: Verify keyboard dismissal after entering text in fee status badge display on Mobile: Mobile Raise Complaint (Check #91)</t>
+  </si>
+  <si>
+    <t>TC-APP-092: Check touch target size for submit button control on mobile screen of Mobile: Mobile Student Dashboard (Check #92)</t>
+  </si>
+  <si>
+    <t>TC-APP-093: Verify email input form control is visible on mobile view of Mobile: Mobile Leave Request (Check #93)</t>
+  </si>
+  <si>
+    <t>TC-APP-094: Assert container padding and alignment on mobile screen for Mobile: Mobile Warden Dashboard (Check #94)</t>
+  </si>
+  <si>
+    <t>TC-APP-095: Verify swipe gestures on submit button control on mobile view of Mobile: Mobile Role Selection (Check #95)</t>
+  </si>
+  <si>
+    <t>TC-APP-096: Verify swipe gestures on fee status badge display on mobile view of Mobile: Mobile Leave Request (Check #96)</t>
+  </si>
+  <si>
+    <t>TC-APP-097: Verify sidebar navigation items is visible on mobile view of Mobile: Mobile Landing (Check #97)</t>
+  </si>
+  <si>
+    <t>TC-APP-098: Assert container padding and alignment on mobile screen for Mobile: Mobile Student Login (Check #98)</t>
+  </si>
+  <si>
+    <t>TC-APP-099: Verify notice board widget is visible on mobile view of Mobile: Mobile Role Selection (Check #99)</t>
+  </si>
+  <si>
+    <t>TC-APP-100: Test student login flow through mobile interface of Mobile: Mobile Student Login (Check #100)</t>
+  </si>
+  <si>
+    <t>TC-APP-101: Verify swipe gestures on average rating star system on mobile view of Mobile: Mobile Mess Feedback (Check #101)</t>
+  </si>
+  <si>
+    <t>TC-APP-102: Verify swipe gestures on alert dialog box on mobile view of Mobile: Mobile Warden Login (Check #102)</t>
+  </si>
+  <si>
+    <t>TC-APP-103: Check touch target size for fee status badge display on mobile screen of Mobile: Mobile Landing (Check #103)</t>
+  </si>
+  <si>
+    <t>TC-APP-104: Test student login flow through mobile interface of Mobile: Mobile Mess Feedback (Check #104)</t>
+  </si>
+  <si>
+    <t>TC-APP-105: Verify swipe gestures on role selection button on mobile view of Mobile: Mobile Warden Login (Check #105)</t>
+  </si>
+  <si>
+    <t>TC-APP-106: Verify keyboard dismissal after entering text in leave request request form on Mobile: Mobile Warden Login (Check #106)</t>
+  </si>
+  <si>
+    <t>TC-APP-107: Verify navigation to Mobile: Mobile Logout via mobile sidebar menu options (Check #107)</t>
+  </si>
+  <si>
+    <t>TC-APP-108: Test student login flow through mobile interface of Mobile: Mobile Landing (Check #108)</t>
+  </si>
+  <si>
+    <t>TC-APP-109: Verify navigation to Mobile: Mobile Student Login via mobile sidebar menu options (Check #109)</t>
+  </si>
+  <si>
+    <t>TC-APP-110: Verify swipe gestures on profile image uploader container on mobile view of Mobile: Mobile Mess Feedback (Check #110)</t>
+  </si>
+  <si>
+    <t>TC-APP-111: Verify navigation to Mobile: Mobile Warden Dashboard via mobile sidebar menu options (Check #111)</t>
+  </si>
+  <si>
+    <t>TC-APP-112: Verify navigation to Mobile: Mobile Admin Dashboard via mobile sidebar menu options (Check #112)</t>
+  </si>
+  <si>
+    <t>TC-APP-113: Check touch target size for dashboard metrics card on mobile screen of Mobile: Mobile Mess Feedback (Check #113)</t>
+  </si>
+  <si>
+    <t>TC-APP-114: Verify swipe gestures on leave request request form on mobile view of Mobile: Mobile Admin Dashboard (Check #114)</t>
+  </si>
+  <si>
+    <t>TC-APP-115: Verify keyboard dismissal after entering text in role selection button on Mobile: Mobile Student Dashboard (Check #115)</t>
+  </si>
+  <si>
+    <t>TC-APP-116: Check text wrapping of dashboard metrics card on mobile display of Mobile: Mobile Admin Login (Check #116)</t>
+  </si>
+  <si>
+    <t>TC-APP-117: Check text wrapping of password input text box on mobile display of Mobile: Mobile Warden Dashboard (Check #117)</t>
+  </si>
+  <si>
+    <t>TC-APP-118: Check touch target size for alert dialog box on mobile screen of Mobile: Mobile Room View (Check #118)</t>
+  </si>
+  <si>
+    <t>TC-APP-119: Test student login flow through mobile interface of Mobile: Mobile Room View (Check #119)</t>
+  </si>
+  <si>
+    <t>TC-APP-120: Check touch target size for fee status badge display on mobile screen of Mobile: Mobile Admin Login (Check #120)</t>
+  </si>
+  <si>
+    <t>TC-APP-121: Verify swipe gestures on notice board widget on mobile view of Mobile: Mobile Student Dashboard (Check #121)</t>
+  </si>
+  <si>
+    <t>TC-APP-122: Assert container padding and alignment on mobile screen for Mobile: Mobile Admin Dashboard (Check #122)</t>
+  </si>
+  <si>
+    <t>TC-APP-123: Verify navigation to Mobile: Mobile Logout via mobile sidebar menu options (Check #123)</t>
+  </si>
+  <si>
+    <t>TC-APP-124: Verify keyboard dismissal after entering text in dashboard metrics card on Mobile: Mobile Profile Settings (Check #124)</t>
+  </si>
+  <si>
+    <t>TC-APP-125: Check touch target size for username input text field on mobile screen of Mobile: Mobile Admin Login (Check #125)</t>
+  </si>
+  <si>
+    <t>TC-APP-126: Assert container padding and alignment on mobile screen for Mobile: Mobile Student Dashboard (Check #126)</t>
+  </si>
+  <si>
+    <t>TC-APP-127: Verify swipe gestures on email input form control on mobile view of Mobile: Mobile Admin Dashboard (Check #127)</t>
+  </si>
+  <si>
+    <t>TC-APP-128: Verify swipe gestures on dashboard metrics card on mobile view of Mobile: Mobile Admin Dashboard (Check #128)</t>
+  </si>
+  <si>
+    <t>TC-APP-129: Verify swipe gestures on role selection button on mobile view of Mobile: Mobile Warden Login (Check #129)</t>
+  </si>
+  <si>
+    <t>TC-APP-130: Check text wrapping of notice board widget on mobile display of Mobile: Mobile Student Login (Check #130)</t>
+  </si>
+  <si>
+    <t>TC-APP-131: Verify swipe gestures on complaint history table on mobile view of Mobile: Mobile Warden Login (Check #131)</t>
+  </si>
+  <si>
+    <t>TC-APP-132: Assert container padding and alignment on mobile screen for Mobile: Mobile Warden Dashboard (Check #132)</t>
+  </si>
+  <si>
+    <t>TC-APP-133: Assert container padding and alignment on mobile screen for Mobile: Mobile Warden Login (Check #133)</t>
+  </si>
+  <si>
+    <t>TC-APP-134: Assert container padding and alignment on mobile screen for Mobile: Mobile Warden Dashboard (Check #134)</t>
+  </si>
+  <si>
+    <t>TC-APP-135: Verify navigation to Mobile: Mobile Leave Request via mobile sidebar menu options (Check #135)</t>
+  </si>
+  <si>
+    <t>TC-APP-136: Verify alert dialog box is visible on mobile view of Mobile: Mobile Admin Dashboard (Check #136)</t>
+  </si>
+  <si>
+    <t>TC-APP-137: Check touch target size for username input text field on mobile screen of Mobile: Mobile Logout (Check #137)</t>
+  </si>
+  <si>
+    <t>TC-APP-138: Check touch target size for dashboard metrics card on mobile screen of Mobile: Mobile Warden Login (Check #138)</t>
+  </si>
+  <si>
+    <t>TC-APP-139: Verify navigation to Mobile: Mobile Mess Feedback via mobile sidebar menu options (Check #139)</t>
+  </si>
+  <si>
+    <t>TC-APP-140: Assert container padding and alignment on mobile screen for Mobile: Mobile Mess Feedback (Check #140)</t>
+  </si>
+  <si>
+    <t>TC-APP-141: Assert container padding and alignment on mobile screen for Mobile: Mobile Admin Dashboard (Check #141)</t>
+  </si>
+  <si>
+    <t>TC-APP-142: Verify average rating star system is visible on mobile view of Mobile: Mobile Admin Dashboard (Check #142)</t>
+  </si>
+  <si>
+    <t>TC-APP-143: Verify keyboard dismissal after entering text in fee status badge display on Mobile: Mobile Warden Login (Check #143)</t>
+  </si>
+  <si>
+    <t>TC-APP-144: Assert container padding and alignment on mobile screen for Mobile: Mobile Student Login (Check #144)</t>
+  </si>
+  <si>
+    <t>TC-APP-145: Verify swipe gestures on average rating star system on mobile view of Mobile: Mobile Admin Login (Check #145)</t>
+  </si>
+  <si>
+    <t>TC-APP-146: Check touch target size for main navigation header on mobile screen of Mobile: Mobile Profile Settings (Check #146)</t>
+  </si>
+  <si>
+    <t>TC-APP-147: Check text wrapping of dashboard metrics card on mobile display of Mobile: Mobile Mess Feedback (Check #147)</t>
+  </si>
+  <si>
+    <t>TC-APP-148: Verify swipe gestures on leave request request form on mobile view of Mobile: Mobile Admin Login (Check #148)</t>
+  </si>
+  <si>
+    <t>TC-APP-149: Test student login flow through mobile interface of Mobile: Mobile Raise Complaint (Check #149)</t>
+  </si>
+  <si>
+    <t>TC-APP-150: Test student login flow through mobile interface of Mobile: Mobile Profile Settings (Check #150)</t>
+  </si>
+  <si>
+    <t>TC-APP-151: Test student login flow through mobile interface of Mobile: Mobile Admin Login (Check #151)</t>
+  </si>
+  <si>
+    <t>TC-APP-152: Verify navigation to Mobile: Mobile Warden Login via mobile sidebar menu options (Check #152)</t>
+  </si>
+  <si>
+    <t>TC-APP-153: Check touch target size for main navigation header on mobile screen of Mobile: Mobile Warden Dashboard (Check #153)</t>
+  </si>
+  <si>
+    <t>TC-APP-154: Check touch target size for sidebar navigation items on mobile screen of Mobile: Mobile Admin Login (Check #154)</t>
+  </si>
+  <si>
+    <t>TC-APP-155: Test student login flow through mobile interface of Mobile: Mobile Role Selection (Check #155)</t>
+  </si>
+  <si>
+    <t>TC-APP-156: Verify back button navigation link is visible on mobile view of Mobile: Mobile Mess Feedback (Check #156)</t>
+  </si>
+  <si>
+    <t>TC-APP-157: Verify swipe gestures on role selection button on mobile view of Mobile: Mobile Warden Login (Check #157)</t>
+  </si>
+  <si>
+    <t>TC-APP-158: Check touch target size for username input text field on mobile screen of Mobile: Mobile Warden Dashboard (Check #158)</t>
+  </si>
+  <si>
+    <t>TC-APP-159: Check touch target size for submit button control on mobile screen of Mobile: Mobile Role Selection (Check #159)</t>
+  </si>
+  <si>
+    <t>TC-APP-160: Verify keyboard dismissal after entering text in alert dialog box on Mobile: Mobile Mess Feedback (Check #160)</t>
+  </si>
+  <si>
+    <t>TC-APP-161: Verify fee status badge display is visible on mobile view of Mobile: Mobile Logout (Check #161)</t>
+  </si>
+  <si>
+    <t>TC-APP-162: Verify keyboard dismissal after entering text in main navigation header on Mobile: Mobile Admin Dashboard (Check #162)</t>
+  </si>
+  <si>
+    <t>TC-APP-163: Check touch target size for sidebar navigation items on mobile screen of Mobile: Mobile Student Dashboard (Check #163)</t>
+  </si>
+  <si>
+    <t>TC-APP-164: Assert container padding and alignment on mobile screen for Mobile: Mobile Admin Login (Check #164)</t>
+  </si>
+  <si>
+    <t>TC-APP-165: Check text wrapping of role selection button on mobile display of Mobile: Mobile Leave Request (Check #165)</t>
+  </si>
+  <si>
+    <t>TC-APP-166: Check touch target size for leave request request form on mobile screen of Mobile: Mobile Warden Login (Check #166)</t>
+  </si>
+  <si>
+    <t>TC-APP-167: Check touch target size for complaint history table on mobile screen of Mobile: Mobile Mess Feedback (Check #167)</t>
+  </si>
+  <si>
+    <t>TC-APP-168: Verify keyboard dismissal after entering text in dashboard metrics card on Mobile: Mobile Admin Dashboard (Check #168)</t>
+  </si>
+  <si>
+    <t>TC-APP-169: Verify keyboard dismissal after entering text in main navigation header on Mobile: Mobile Student Dashboard (Check #169)</t>
+  </si>
+  <si>
+    <t>TC-APP-170: Assert container padding and alignment on mobile screen for Mobile: Mobile Admin Dashboard (Check #170)</t>
+  </si>
+  <si>
+    <t>TC-APP-171: Check text wrapping of alert dialog box on mobile display of Mobile: Mobile Admin Login (Check #171)</t>
+  </si>
+  <si>
+    <t>TC-APP-172: Verify swipe gestures on footer copyright note on mobile view of Mobile: Mobile Admin Login (Check #172)</t>
+  </si>
+  <si>
+    <t>TC-APP-173: Assert container padding and alignment on mobile screen for Mobile: Mobile Room View (Check #173)</t>
+  </si>
+  <si>
+    <t>TC-APP-174: Verify navigation to Mobile: Mobile Leave Request via mobile sidebar menu options (Check #174)</t>
+  </si>
+  <si>
+    <t>TC-APP-175: Check text wrapping of database connection module on mobile display of Mobile: Mobile Logout (Check #175)</t>
+  </si>
+  <si>
+    <t>TC-APP-176: Verify average rating star system is visible on mobile view of Mobile: Mobile Role Selection (Check #176)</t>
+  </si>
+  <si>
+    <t>TC-APP-177: Verify keyboard dismissal after entering text in database connection module on Mobile: Mobile Mess Feedback (Check #177)</t>
+  </si>
+  <si>
+    <t>TC-APP-178: Test student login flow through mobile interface of Mobile: Mobile Room View (Check #178)</t>
+  </si>
+  <si>
+    <t>TC-APP-179: Verify swipe gestures on complaint history table on mobile view of Mobile: Mobile Logout (Check #179)</t>
+  </si>
+  <si>
+    <t>TC-APP-180: Check text wrapping of back button navigation link on mobile display of Mobile: Mobile Admin Login (Check #180)</t>
+  </si>
+  <si>
+    <t>TC-APP-181: Verify navigation to Mobile: Mobile Warden Dashboard via mobile sidebar menu options (Check #181)</t>
+  </si>
+  <si>
+    <t>TC-APP-182: Check text wrapping of complaint history table on mobile display of Mobile: Mobile Student Login (Check #182)</t>
+  </si>
+  <si>
+    <t>TC-APP-183: Check touch target size for database connection module on mobile screen of Mobile: Mobile Mess Feedback (Check #183)</t>
+  </si>
+  <si>
+    <t>TC-APP-184: Verify swipe gestures on dashboard metrics card on mobile view of Mobile: Mobile Room View (Check #184)</t>
+  </si>
+  <si>
+    <t>TC-APP-185: Assert container padding and alignment on mobile screen for Mobile: Mobile Student Login (Check #185)</t>
+  </si>
+  <si>
+    <t>TC-APP-186: Verify swipe gestures on username input text field on mobile view of Mobile: Mobile Warden Login (Check #186)</t>
+  </si>
+  <si>
+    <t>TC-APP-187: Check text wrapping of email input form control on mobile display of Mobile: Mobile Landing (Check #187)</t>
+  </si>
+  <si>
+    <t>TC-APP-188: Assert container padding and alignment on mobile screen for Mobile: Mobile Admin Dashboard (Check #188)</t>
+  </si>
+  <si>
+    <t>TC-APP-189: Verify swipe gestures on database connection module on mobile view of Mobile: Mobile Student Dashboard (Check #189)</t>
+  </si>
+  <si>
+    <t>TC-APP-190: Check touch target size for submit button control on mobile screen of Mobile: Mobile Student Dashboard (Check #190)</t>
+  </si>
+  <si>
+    <t>TC-APP-191: Check text wrapping of dashboard metrics card on mobile display of Mobile: Mobile Warden Dashboard (Check #191)</t>
+  </si>
+  <si>
+    <t>TC-APP-192: Check touch target size for average rating star system on mobile screen of Mobile: Mobile Leave Request (Check #192)</t>
+  </si>
+  <si>
+    <t>TC-APP-193: Verify swipe gestures on footer copyright note on mobile view of Mobile: Mobile Profile Settings (Check #193)</t>
+  </si>
+  <si>
+    <t>TC-APP-194: Check text wrapping of database connection module on mobile display of Mobile: Mobile Landing (Check #194)</t>
+  </si>
+  <si>
+    <t>TC-APP-195: Verify back button navigation link is visible on mobile view of Mobile: Mobile Logout (Check #195)</t>
+  </si>
+  <si>
+    <t>TC-APP-196: Verify swipe gestures on database connection module on mobile view of Mobile: Mobile Student Login (Check #196)</t>
+  </si>
+  <si>
+    <t>TC-APP-197: Check text wrapping of alert dialog box on mobile display of Mobile: Mobile Admin Login (Check #197)</t>
+  </si>
+  <si>
+    <t>TC-APP-198: Verify swipe gestures on dashboard metrics card on mobile view of Mobile: Mobile Warden Dashboard (Check #198)</t>
+  </si>
+  <si>
+    <t>TC-APP-199: Verify keyboard dismissal after entering text in submit button control on Mobile: Mobile Raise Complaint (Check #199)</t>
+  </si>
+  <si>
+    <t>TC-APP-200: Check text wrapping of profile image uploader container on mobile display of Mobile: Mobile Raise Complaint (Check #200)</t>
+  </si>
+  <si>
+    <t>TC-APP-201: Verify password input text box is visible on mobile view of Mobile: Mobile Student Dashboard (Check #201)</t>
+  </si>
+  <si>
+    <t>TC-APP-202: Verify navigation to Mobile: Mobile Leave Request via mobile sidebar menu options (Check #202)</t>
+  </si>
+  <si>
+    <t>TC-APP-203: Check text wrapping of alert dialog box on mobile display of Mobile: Mobile Raise Complaint (Check #203)</t>
+  </si>
+  <si>
+    <t>TC-APP-204: Verify keyboard dismissal after entering text in main navigation header on Mobile: Mobile Mess Feedback (Check #204)</t>
+  </si>
+  <si>
+    <t>TC-APP-205: Assert container padding and alignment on mobile screen for Mobile: Mobile Role Selection (Check #205)</t>
+  </si>
+  <si>
+    <t>TC-APP-206: Verify navigation to Mobile: Mobile Admin Dashboard via mobile sidebar menu options (Check #206)</t>
+  </si>
+  <si>
+    <t>TC-APP-207: Verify navigation to Mobile: Mobile Student Dashboard via mobile sidebar menu options (Check #207)</t>
+  </si>
+  <si>
+    <t>TC-APP-208: Verify fee status badge display is visible on mobile view of Mobile: Mobile Student Dashboard (Check #208)</t>
+  </si>
+  <si>
+    <t>TC-APP-209: Verify keyboard dismissal after entering text in back button navigation link on Mobile: Mobile Leave Request (Check #209)</t>
+  </si>
+  <si>
+    <t>TC-APP-210: Verify keyboard dismissal after entering text in complaint history table on Mobile: Mobile Student Login (Check #210)</t>
+  </si>
+  <si>
+    <t>TC-APP-211: Assert container padding and alignment on mobile screen for Mobile: Mobile Leave Request (Check #211)</t>
+  </si>
+  <si>
+    <t>TC-APP-212: Verify email input form control is visible on mobile view of Mobile: Mobile Admin Login (Check #212)</t>
+  </si>
+  <si>
+    <t>TC-APP-213: Check touch target size for leave request request form on mobile screen of Mobile: Mobile Admin Dashboard (Check #213)</t>
+  </si>
+  <si>
+    <t>TC-APP-214: Assert container padding and alignment on mobile screen for Mobile: Mobile Warden Dashboard (Check #214)</t>
+  </si>
+  <si>
+    <t>TC-APP-215: Assert container padding and alignment on mobile screen for Mobile: Mobile Admin Login (Check #215)</t>
+  </si>
+  <si>
+    <t>TC-APP-216: Verify keyboard dismissal after entering text in average rating star system on Mobile: Mobile Role Selection (Check #216)</t>
+  </si>
+  <si>
+    <t>TC-APP-217: Check text wrapping of email input form control on mobile display of Mobile: Mobile Admin Login (Check #217)</t>
+  </si>
+  <si>
+    <t>TC-APP-218: Assert container padding and alignment on mobile screen for Mobile: Mobile Raise Complaint (Check #218)</t>
+  </si>
+  <si>
+    <t>TC-APP-219: Verify notice board widget is visible on mobile view of Mobile: Mobile Student Dashboard (Check #219)</t>
+  </si>
+  <si>
+    <t>TC-APP-220: Check touch target size for complaint history table on mobile screen of Mobile: Mobile Admin Dashboard (Check #220)</t>
+  </si>
+  <si>
+    <t>TC-APP-221: Verify navigation to Mobile: Mobile Admin Login via mobile sidebar menu options (Check #221)</t>
+  </si>
+  <si>
+    <t>TC-APP-222: Check touch target size for main navigation header on mobile screen of Mobile: Mobile Warden Dashboard (Check #222)</t>
+  </si>
+  <si>
+    <t>TC-APP-223: Verify keyboard dismissal after entering text in database connection module on Mobile: Mobile Student Login (Check #223)</t>
+  </si>
+  <si>
+    <t>TC-APP-224: Verify navigation to Mobile: Mobile Logout via mobile sidebar menu options (Check #224)</t>
+  </si>
+  <si>
+    <t>TC-APP-225: Verify keyboard dismissal after entering text in username input text field on Mobile: Mobile Leave Request (Check #225)</t>
+  </si>
+  <si>
+    <t>TC-APP-226: Check touch target size for dashboard metrics card on mobile screen of Mobile: Mobile Warden Dashboard (Check #226)</t>
+  </si>
+  <si>
+    <t>TC-APP-227: Verify complaint history table is visible on mobile view of Mobile: Mobile Admin Dashboard (Check #227)</t>
+  </si>
+  <si>
+    <t>TC-APP-228: Test student login flow through mobile interface of Mobile: Mobile Raise Complaint (Check #228)</t>
+  </si>
+  <si>
+    <t>TC-APP-229: Verify keyboard dismissal after entering text in alert dialog box on Mobile: Mobile Leave Request (Check #229)</t>
+  </si>
+  <si>
+    <t>TC-APP-230: Check touch target size for profile image uploader container on mobile screen of Mobile: Mobile Profile Settings (Check #230)</t>
+  </si>
+  <si>
+    <t>TC-APP-231: Verify keyboard dismissal after entering text in footer copyright note on Mobile: Mobile Leave Request (Check #231)</t>
+  </si>
+  <si>
+    <t>TC-APP-232: Check touch target size for username input text field on mobile screen of Mobile: Mobile Leave Request (Check #232)</t>
+  </si>
+  <si>
+    <t>TC-APP-233: Verify username input text field is visible on mobile view of Mobile: Mobile Profile Settings (Check #233)</t>
+  </si>
+  <si>
+    <t>TC-APP-234: Verify leave request request form is visible on mobile view of Mobile: Mobile Logout (Check #234)</t>
+  </si>
+  <si>
+    <t>TC-APP-235: Check text wrapping of main navigation header on mobile display of Mobile: Mobile Admin Login (Check #235)</t>
+  </si>
+  <si>
+    <t>TC-APP-236: Check text wrapping of username input text field on mobile display of Mobile: Mobile Profile Settings (Check #236)</t>
+  </si>
+  <si>
+    <t>TC-APP-237: Verify navigation to Mobile: Mobile Room View via mobile sidebar menu options (Check #237)</t>
+  </si>
+  <si>
+    <t>TC-APP-238: Verify swipe gestures on fee status badge display on mobile view of Mobile: Mobile Student Dashboard (Check #238)</t>
+  </si>
+  <si>
+    <t>TC-APP-239: Verify navigation to Mobile: Mobile Room View via mobile sidebar menu options (Check #239)</t>
+  </si>
+  <si>
+    <t>TC-APP-240: Test student login flow through mobile interface of Mobile: Mobile Mess Feedback (Check #240)</t>
+  </si>
+  <si>
+    <t>TC-APP-241: Verify keyboard dismissal after entering text in profile image uploader container on Mobile: Mobile Mess Feedback (Check #241)</t>
+  </si>
+  <si>
+    <t>TC-APP-242: Test student login flow through mobile interface of Mobile: Mobile Raise Complaint (Check #242)</t>
+  </si>
+  <si>
+    <t>TC-APP-243: Check touch target size for notice board widget on mobile screen of Mobile: Mobile Student Login (Check #243)</t>
+  </si>
+  <si>
+    <t>TC-APP-244: Assert container padding and alignment on mobile screen for Mobile: Mobile Role Selection (Check #244)</t>
+  </si>
+  <si>
+    <t>TC-APP-245: Check touch target size for password input text box on mobile screen of Mobile: Mobile Student Login (Check #245)</t>
+  </si>
+  <si>
+    <t>TC-APP-246: Verify navigation to Mobile: Mobile Room View via mobile sidebar menu options (Check #246)</t>
+  </si>
+  <si>
+    <t>TC-APP-247: Verify navigation to Mobile: Mobile Student Login via mobile sidebar menu options (Check #247)</t>
+  </si>
+  <si>
+    <t>TC-APP-248: Check text wrapping of average rating star system on mobile display of Mobile: Mobile Logout (Check #248)</t>
+  </si>
+  <si>
+    <t>TC-APP-249: Verify swipe gestures on dashboard metrics card on mobile view of Mobile: Mobile Landing (Check #249)</t>
+  </si>
+  <si>
+    <t>TC-APP-250: Verify swipe gestures on password input text box on mobile view of Mobile: Mobile Student Dashboard (Check #250)</t>
+  </si>
+  <si>
+    <t>TC-APP-251: Verify swipe gestures on username input text field on mobile view of Mobile: Mobile Landing (Check #251)</t>
+  </si>
+  <si>
+    <t>TC-APP-252: Assert container padding and alignment on mobile screen for Mobile: Mobile Raise Complaint (Check #252)</t>
+  </si>
+  <si>
+    <t>TC-APP-253: Assert container padding and alignment on mobile screen for Mobile: Mobile Warden Dashboard (Check #253)</t>
+  </si>
+  <si>
+    <t>TC-APP-254: Verify swipe gestures on profile image uploader container on mobile view of Mobile: Mobile Warden Dashboard (Check #254)</t>
+  </si>
+  <si>
+    <t>TC-APP-255: Test student login flow through mobile interface of Mobile: Mobile Admin Login (Check #255)</t>
+  </si>
+  <si>
+    <t>TC-APP-256: Test student login flow through mobile interface of Mobile: Mobile Warden Login (Check #256)</t>
+  </si>
+  <si>
+    <t>TC-APP-257: Test student login flow through mobile interface of Mobile: Mobile Student Dashboard (Check #257)</t>
+  </si>
+  <si>
+    <t>TC-APP-258: Check text wrapping of password input text box on mobile display of Mobile: Mobile Logout (Check #258)</t>
+  </si>
+  <si>
+    <t>TC-APP-259: Test student login flow through mobile interface of Mobile: Mobile Logout (Check #259)</t>
+  </si>
+  <si>
+    <t>TC-APP-260: Verify navigation to Mobile: Mobile Student Login via mobile sidebar menu options (Check #260)</t>
+  </si>
+  <si>
+    <t>TC-APP-261: Verify leave request request form is visible on mobile view of Mobile: Mobile Admin Login (Check #261)</t>
+  </si>
+  <si>
+    <t>TC-APP-262: Check touch target size for average rating star system on mobile screen of Mobile: Mobile Room View (Check #262)</t>
+  </si>
+  <si>
+    <t>TC-APP-263: Verify keyboard dismissal after entering text in leave request request form on Mobile: Mobile Admin Login (Check #263)</t>
+  </si>
+  <si>
+    <t>TC-APP-264: Verify swipe gestures on submit button control on mobile view of Mobile: Mobile Raise Complaint (Check #264)</t>
+  </si>
+  <si>
+    <t>TC-APP-265: Verify swipe gestures on sidebar navigation items on mobile view of Mobile: Mobile Admin Dashboard (Check #265)</t>
+  </si>
+  <si>
+    <t>TC-APP-266: Test student login flow through mobile interface of Mobile: Mobile Admin Dashboard (Check #266)</t>
+  </si>
+  <si>
+    <t>TC-APP-267: Verify navigation to Mobile: Mobile Leave Request via mobile sidebar menu options (Check #267)</t>
+  </si>
+  <si>
+    <t>TC-APP-268: Assert container padding and alignment on mobile screen for Mobile: Mobile Mess Feedback (Check #268)</t>
+  </si>
+  <si>
+    <t>TC-APP-269: Verify swipe gestures on email input form control on mobile view of Mobile: Mobile Role Selection (Check #269)</t>
+  </si>
+  <si>
+    <t>TC-APP-270: Check touch target size for username input text field on mobile screen of Mobile: Mobile Landing (Check #270)</t>
+  </si>
+  <si>
+    <t>TC-APP-271: Verify navigation to Mobile: Mobile Landing via mobile sidebar menu options (Check #271)</t>
+  </si>
+  <si>
+    <t>TC-APP-272: Verify footer copyright note is visible on mobile view of Mobile: Mobile Logout (Check #272)</t>
+  </si>
+  <si>
+    <t>TC-APP-273: Check touch target size for password input text box on mobile screen of Mobile: Mobile Landing (Check #273)</t>
+  </si>
+  <si>
+    <t>TC-APP-274: Assert container padding and alignment on mobile screen for Mobile: Mobile Student Login (Check #274)</t>
+  </si>
+  <si>
+    <t>TC-APP-275: Check text wrapping of average rating star system on mobile display of Mobile: Mobile Landing (Check #275)</t>
+  </si>
+  <si>
+    <t>TC-APP-276: Test student login flow through mobile interface of Mobile: Mobile Raise Complaint (Check #276)</t>
+  </si>
+  <si>
+    <t>TC-APP-277: Verify navigation to Mobile: Mobile Leave Request via mobile sidebar menu options (Check #277)</t>
+  </si>
+  <si>
+    <t>TC-APP-278: Verify swipe gestures on dashboard metrics card on mobile view of Mobile: Mobile Warden Login (Check #278)</t>
+  </si>
+  <si>
+    <t>TC-APP-279: Verify swipe gestures on leave request request form on mobile view of Mobile: Mobile Admin Dashboard (Check #279)</t>
+  </si>
+  <si>
+    <t>TC-APP-280: Verify swipe gestures on email input form control on mobile view of Mobile: Mobile Leave Request (Check #280)</t>
+  </si>
+  <si>
+    <t>TC-APP-281: Check text wrapping of footer copyright note on mobile display of Mobile: Mobile Leave Request (Check #281)</t>
+  </si>
+  <si>
+    <t>TC-APP-282: Check touch target size for footer copyright note on mobile screen of Mobile: Mobile Admin Login (Check #282)</t>
+  </si>
+  <si>
+    <t>TC-APP-283: Verify navigation to Mobile: Mobile Mess Feedback via mobile sidebar menu options (Check #283)</t>
+  </si>
+  <si>
+    <t>TC-APP-284: Check touch target size for profile image uploader container on mobile screen of Mobile: Mobile Logout (Check #284)</t>
+  </si>
+  <si>
+    <t>TC-APP-285: Test student login flow through mobile interface of Mobile: Mobile Room View (Check #285)</t>
+  </si>
+  <si>
+    <t>TC-APP-286: Test student login flow through mobile interface of Mobile: Mobile Logout (Check #286)</t>
+  </si>
+  <si>
+    <t>TC-APP-287: Test student login flow through mobile interface of Mobile: Mobile Landing (Check #287)</t>
+  </si>
+  <si>
+    <t>TC-APP-288: Verify keyboard dismissal after entering text in sidebar navigation items on Mobile: Mobile Admin Login (Check #288)</t>
+  </si>
+  <si>
+    <t>TC-APP-289: Verify navigation to Mobile: Mobile Role Selection via mobile sidebar menu options (Check #289)</t>
+  </si>
+  <si>
+    <t>TC-APP-290: Test student login flow through mobile interface of Mobile: Mobile Student Login (Check #290)</t>
+  </si>
+  <si>
+    <t>TC-APP-291: Verify swipe gestures on fee status badge display on mobile view of Mobile: Mobile Student Dashboard (Check #291)</t>
+  </si>
+  <si>
+    <t>TC-APP-292: Verify email input form control is visible on mobile view of Mobile: Mobile Role Selection (Check #292)</t>
+  </si>
+  <si>
+    <t>TC-APP-293: Verify keyboard dismissal after entering text in role selection button on Mobile: Mobile Student Dashboard (Check #293)</t>
+  </si>
+  <si>
+    <t>TC-APP-294: Test student login flow through mobile interface of Mobile: Mobile Student Login (Check #294)</t>
+  </si>
+  <si>
+    <t>TC-APP-295: Verify keyboard dismissal after entering text in leave request request form on Mobile: Mobile Profile Settings (Check #295)</t>
+  </si>
+  <si>
+    <t>TC-APP-296: Check text wrapping of database connection module on mobile display of Mobile: Mobile Admin Login (Check #296)</t>
+  </si>
+  <si>
+    <t>TC-APP-297: Verify navigation to Mobile: Mobile Warden Dashboard via mobile sidebar menu options (Check #297)</t>
+  </si>
+  <si>
+    <t>TC-APP-298: Check touch target size for alert dialog box on mobile screen of Mobile: Mobile Leave Request (Check #298)</t>
+  </si>
+  <si>
+    <t>TC-APP-299: Test student login flow through mobile interface of Mobile: Mobile Mess Feedback (Check #299)</t>
+  </si>
+  <si>
+    <t>TC-APP-300: Verify navigation to Mobile: Mobile Room View via mobile sidebar menu options (Check #300)</t>
   </si>
 </sst>
 </file>
